--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
@@ -207,7 +207,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (5bd7164)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (5bd7164) at 2026-10-02T15:08:37.131Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (5bd7164) at 2026-10-02T15:29:52.846Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3523,7 +3523,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:39.729Z</t>
+    <t>2026-10-02T15:29:54.637Z</t>
   </si>
   <si>
     <t>13 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -3535,7 +3535,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:39.766Z</t>
+    <t>2026-10-02T15:29:54.670Z</t>
   </si>
   <si>
     <t>7 requirements, 11 test cases, 5 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -13872,7 +13872,7 @@
         <v>1054</v>
       </c>
       <c r="E2" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -13990,7 +13990,7 @@
         <v>1054</v>
       </c>
       <c r="E8" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -14008,7 +14008,7 @@
         <v>1054</v>
       </c>
       <c r="E9" s="2">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -14026,7 +14026,7 @@
         <v>1054</v>
       </c>
       <c r="E10" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -14044,7 +14044,7 @@
         <v>1054</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -14062,7 +14062,7 @@
         <v>1054</v>
       </c>
       <c r="E12" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -14080,7 +14080,7 @@
         <v>1054</v>
       </c>
       <c r="E13" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -14158,7 +14158,7 @@
         <v>1054</v>
       </c>
       <c r="E17" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -14176,7 +14176,7 @@
         <v>1054</v>
       </c>
       <c r="E18" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -14234,7 +14234,7 @@
         <v>1054</v>
       </c>
       <c r="E21" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -14272,7 +14272,7 @@
         <v>1054</v>
       </c>
       <c r="E23" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -14290,7 +14290,7 @@
         <v>1054</v>
       </c>
       <c r="E24" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -14308,7 +14308,7 @@
         <v>1054</v>
       </c>
       <c r="E25" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -14326,7 +14326,7 @@
         <v>1054</v>
       </c>
       <c r="E26" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -14344,7 +14344,7 @@
         <v>1054</v>
       </c>
       <c r="E27" s="2">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -14362,7 +14362,7 @@
         <v>1054</v>
       </c>
       <c r="E28" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -14380,7 +14380,7 @@
         <v>1054</v>
       </c>
       <c r="E29" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -14398,7 +14398,7 @@
         <v>1054</v>
       </c>
       <c r="E30" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -14416,7 +14416,7 @@
         <v>1054</v>
       </c>
       <c r="E31" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -14454,7 +14454,7 @@
         <v>1054</v>
       </c>
       <c r="E33" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -14472,7 +14472,7 @@
         <v>1054</v>
       </c>
       <c r="E34" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -14530,7 +14530,7 @@
         <v>1054</v>
       </c>
       <c r="E37" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -14568,7 +14568,7 @@
         <v>1054</v>
       </c>
       <c r="E39" s="2">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -14684,7 +14684,7 @@
         <v>1054</v>
       </c>
       <c r="E45" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -14702,7 +14702,7 @@
         <v>1054</v>
       </c>
       <c r="E46" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -14758,7 +14758,7 @@
         <v>1054</v>
       </c>
       <c r="E49" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -14776,7 +14776,7 @@
         <v>1054</v>
       </c>
       <c r="E50" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -14794,7 +14794,7 @@
         <v>1054</v>
       </c>
       <c r="E51" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -14930,7 +14930,7 @@
         <v>1054</v>
       </c>
       <c r="E58" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -14968,7 +14968,7 @@
         <v>1054</v>
       </c>
       <c r="E60" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -15066,7 +15066,7 @@
         <v>1054</v>
       </c>
       <c r="E65" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -15084,7 +15084,7 @@
         <v>1054</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -15102,7 +15102,7 @@
         <v>1054</v>
       </c>
       <c r="E67" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -15160,7 +15160,7 @@
         <v>1054</v>
       </c>
       <c r="E70" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -15178,7 +15178,7 @@
         <v>1054</v>
       </c>
       <c r="E71" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -15234,7 +15234,7 @@
         <v>1054</v>
       </c>
       <c r="E74" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -15252,7 +15252,7 @@
         <v>1054</v>
       </c>
       <c r="E75" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -15288,7 +15288,7 @@
         <v>1054</v>
       </c>
       <c r="E77" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -15364,7 +15364,7 @@
         <v>1054</v>
       </c>
       <c r="E81" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -15382,7 +15382,7 @@
         <v>1054</v>
       </c>
       <c r="E82" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -15460,7 +15460,7 @@
         <v>1054</v>
       </c>
       <c r="E86" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -15478,7 +15478,7 @@
         <v>1054</v>
       </c>
       <c r="E87" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -15514,7 +15514,7 @@
         <v>1054</v>
       </c>
       <c r="E89" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -15532,7 +15532,7 @@
         <v>1054</v>
       </c>
       <c r="E90" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -15570,7 +15570,7 @@
         <v>1054</v>
       </c>
       <c r="E92" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -15608,7 +15608,7 @@
         <v>1054</v>
       </c>
       <c r="E94" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -15686,7 +15686,7 @@
         <v>1054</v>
       </c>
       <c r="E98" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -15804,7 +15804,7 @@
         <v>1054</v>
       </c>
       <c r="E104" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -15842,7 +15842,7 @@
         <v>1054</v>
       </c>
       <c r="E106" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -15980,7 +15980,7 @@
         <v>1054</v>
       </c>
       <c r="E113" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -16076,7 +16076,7 @@
         <v>1054</v>
       </c>
       <c r="E118" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -16112,7 +16112,7 @@
         <v>1054</v>
       </c>
       <c r="E120" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -16130,7 +16130,7 @@
         <v>1054</v>
       </c>
       <c r="E121" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -16148,7 +16148,7 @@
         <v>1054</v>
       </c>
       <c r="E122" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -16184,7 +16184,7 @@
         <v>1054</v>
       </c>
       <c r="E124" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -16220,7 +16220,7 @@
         <v>1054</v>
       </c>
       <c r="E126" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -16238,7 +16238,7 @@
         <v>1057</v>
       </c>
       <c r="E127" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -16256,7 +16256,7 @@
         <v>1054</v>
       </c>
       <c r="E128" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -16274,7 +16274,7 @@
         <v>1054</v>
       </c>
       <c r="E129" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -16292,7 +16292,7 @@
         <v>1054</v>
       </c>
       <c r="E130" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -16310,7 +16310,7 @@
         <v>1054</v>
       </c>
       <c r="E131" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -16328,7 +16328,7 @@
         <v>1054</v>
       </c>
       <c r="E132" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -16404,7 +16404,7 @@
         <v>1054</v>
       </c>
       <c r="E136" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -16422,7 +16422,7 @@
         <v>1054</v>
       </c>
       <c r="E137" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F137" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
@@ -12,9 +12,11 @@
     <sheet sheetId="6" name="Defects" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Coverage" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Attribute coverage" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Approvals" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Skills" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Hand-overs" state="visible" r:id="rId14"/>
+    <sheet sheetId="9" name="Traceability by story" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Traceability matrix" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Approvals" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Skills" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Hand-overs" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -73,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3881" uniqueCount="1225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5660" uniqueCount="1599">
   <si>
     <t>Metric</t>
   </si>
@@ -210,7 +212,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (5bd7164) at 2026-10-02T16:18:37.849Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (5bd7164) at 2026-10-02T19:27:56.968Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3316,6 +3318,12 @@
     <t>Severity</t>
   </si>
   <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>Jira defect</t>
+  </si>
+  <si>
     <t>Expected</t>
   </si>
   <si>
@@ -3334,6 +3342,12 @@
     <t>A 15-night stay in Paris is rejected: returns 200 instead of 400</t>
   </si>
   <si>
+    <t>AQPI-34</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-34 in the platform</t>
+  </si>
+  <si>
     <t>400</t>
   </si>
   <si>
@@ -3502,6 +3516,1116 @@
     <t>Prefix of the Idempotency-Key sent with a reservation (the full key is 8 to 64 characters)</t>
   </si>
   <si>
+    <t>Jira item</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>epic</t>
+  </si>
+  <si>
+    <t>[Epic 8] Release 2.0 – Booking Rule Changes and Free Cancellation</t>
+  </si>
+  <si>
+    <t>designed, not executed</t>
+  </si>
+  <si>
+    <t>AQPI-33</t>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>10.1 Shorten the cart hold to 20 minutes</t>
+  </si>
+  <si>
+    <t>verified</t>
+  </si>
+  <si>
+    <t>10.2 Limit Paris stays to 14 nights</t>
+  </si>
+  <si>
+    <t>failing</t>
+  </si>
+  <si>
+    <t>AQPI-35</t>
+  </si>
+  <si>
+    <t>10.3 Allow up to 5 confirmation resends</t>
+  </si>
+  <si>
+    <t>AQPI-36</t>
+  </si>
+  <si>
+    <t>10.4 Cancel a reservation free of charge</t>
+  </si>
+  <si>
+    <t>Jira</t>
+  </si>
+  <si>
+    <t>Requirement text</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Test case</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>Test data</t>
+  </si>
+  <si>
+    <t>Script</t>
+  </si>
+  <si>
+    <t>Defect</t>
+  </si>
+  <si>
+    <t>AQPI-1</t>
+  </si>
+  <si>
+    <t>BR-003</t>
+  </si>
+  <si>
+    <t>TD-F-001</t>
+  </si>
+  <si>
+    <t>br-003-price-disclosed.spec.js</t>
+  </si>
+  <si>
+    <t>BR-008</t>
+  </si>
+  <si>
+    <t>TD-F-002</t>
+  </si>
+  <si>
+    <t>AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27</t>
+  </si>
+  <si>
+    <t>BR-009</t>
+  </si>
+  <si>
+    <t>TD-F-003</t>
+  </si>
+  <si>
+    <t>BR-010</t>
+  </si>
+  <si>
+    <t>TD-F-004</t>
+  </si>
+  <si>
+    <t>BR-011</t>
+  </si>
+  <si>
+    <t>TD-F-005</t>
+  </si>
+  <si>
+    <t>BR-012</t>
+  </si>
+  <si>
+    <t>TD-F-006</t>
+  </si>
+  <si>
+    <t>AQPI-3</t>
+  </si>
+  <si>
+    <t>BR-013</t>
+  </si>
+  <si>
+    <t>TD-F-007</t>
+  </si>
+  <si>
+    <t>br-013-hotel-search.spec.js</t>
+  </si>
+  <si>
+    <t>BR-014</t>
+  </si>
+  <si>
+    <t>TD-F-008</t>
+  </si>
+  <si>
+    <t>br-014-search-criteria-kept.spec.js</t>
+  </si>
+  <si>
+    <t>BR-015</t>
+  </si>
+  <si>
+    <t>TD-F-009</t>
+  </si>
+  <si>
+    <t>br-015-search-date-validation.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-010</t>
+  </si>
+  <si>
+    <t>TD-F-011</t>
+  </si>
+  <si>
+    <t>BR-016</t>
+  </si>
+  <si>
+    <t>TD-N-001</t>
+  </si>
+  <si>
+    <t>br-016-no-availability.spec.js</t>
+  </si>
+  <si>
+    <t>BR-017</t>
+  </si>
+  <si>
+    <t>TD-F-012</t>
+  </si>
+  <si>
+    <t>BR-018</t>
+  </si>
+  <si>
+    <t>TD-F-013</t>
+  </si>
+  <si>
+    <t>BR-019</t>
+  </si>
+  <si>
+    <t>TD-F-014</t>
+  </si>
+  <si>
+    <t>AQPI-4</t>
+  </si>
+  <si>
+    <t>BR-020</t>
+  </si>
+  <si>
+    <t>TD-F-015</t>
+  </si>
+  <si>
+    <t>br-020-search-form.spec.js</t>
+  </si>
+  <si>
+    <t>BR-021</t>
+  </si>
+  <si>
+    <t>TD-F-016</t>
+  </si>
+  <si>
+    <t>br-021-field-level-messages.spec.js</t>
+  </si>
+  <si>
+    <t>BR-022</t>
+  </si>
+  <si>
+    <t>TD-F-017</t>
+  </si>
+  <si>
+    <t>BR-024</t>
+  </si>
+  <si>
+    <t>TD-F-018</t>
+  </si>
+  <si>
+    <t>AQPI-5</t>
+  </si>
+  <si>
+    <t>BR-025</t>
+  </si>
+  <si>
+    <t>TD-F-019</t>
+  </si>
+  <si>
+    <t>br-025-no-availability.spec.js</t>
+  </si>
+  <si>
+    <t>BR-026</t>
+  </si>
+  <si>
+    <t>TD-F-020</t>
+  </si>
+  <si>
+    <t>BR-027</t>
+  </si>
+  <si>
+    <t>TD-F-021</t>
+  </si>
+  <si>
+    <t>br-027-search-session.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-7</t>
+  </si>
+  <si>
+    <t>BR-028</t>
+  </si>
+  <si>
+    <t>TD-N-002</t>
+  </si>
+  <si>
+    <t>br-028-result-content.spec.js</t>
+  </si>
+  <si>
+    <t>BR-029</t>
+  </si>
+  <si>
+    <t>TD-F-022</t>
+  </si>
+  <si>
+    <t>br-029-fee-disclosure.spec.js</t>
+  </si>
+  <si>
+    <t>BR-030</t>
+  </si>
+  <si>
+    <t>TD-F-023</t>
+  </si>
+  <si>
+    <t>br-030-unavailable-not-bookable.spec.js</t>
+  </si>
+  <si>
+    <t>BR-031</t>
+  </si>
+  <si>
+    <t>TD-F-024</t>
+  </si>
+  <si>
+    <t>br-031-pagination.spec.js</t>
+  </si>
+  <si>
+    <t>BR-032</t>
+  </si>
+  <si>
+    <t>TD-F-025</t>
+  </si>
+  <si>
+    <t>br-032-starting-price.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-8</t>
+  </si>
+  <si>
+    <t>BR-033</t>
+  </si>
+  <si>
+    <t>TD-F-026</t>
+  </si>
+  <si>
+    <t>br-033-result-filters.spec.js</t>
+  </si>
+  <si>
+    <t>BR-034</t>
+  </si>
+  <si>
+    <t>TD-F-027</t>
+  </si>
+  <si>
+    <t>br-034-result-sorting.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-028</t>
+  </si>
+  <si>
+    <t>BR-035</t>
+  </si>
+  <si>
+    <t>TD-F-029</t>
+  </si>
+  <si>
+    <t>BR-036</t>
+  </si>
+  <si>
+    <t>TD-F-030</t>
+  </si>
+  <si>
+    <t>br-036-filter-reset.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-9</t>
+  </si>
+  <si>
+    <t>BR-037</t>
+  </si>
+  <si>
+    <t>TD-F-031</t>
+  </si>
+  <si>
+    <t>br-037-hotel-details.spec.js</t>
+  </si>
+  <si>
+    <t>BR-038</t>
+  </si>
+  <si>
+    <t>TD-F-032</t>
+  </si>
+  <si>
+    <t>BR-039</t>
+  </si>
+  <si>
+    <t>TD-F-033</t>
+  </si>
+  <si>
+    <t>BR-040</t>
+  </si>
+  <si>
+    <t>TD-F-034</t>
+  </si>
+  <si>
+    <t>br-040-rate-conditions.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-11</t>
+  </si>
+  <si>
+    <t>BR-041</t>
+  </si>
+  <si>
+    <t>TD-F-035</t>
+  </si>
+  <si>
+    <t>BR-042</t>
+  </si>
+  <si>
+    <t>TD-F-036</t>
+  </si>
+  <si>
+    <t>br-042-offer-exclusion.spec.js</t>
+  </si>
+  <si>
+    <t>BR-043</t>
+  </si>
+  <si>
+    <t>TD-F-037</t>
+  </si>
+  <si>
+    <t>br-043-offer-reason-codes.spec.js</t>
+  </si>
+  <si>
+    <t>BR-044</t>
+  </si>
+  <si>
+    <t>TD-F-038</t>
+  </si>
+  <si>
+    <t>BR-045</t>
+  </si>
+  <si>
+    <t>TD-F-039</t>
+  </si>
+  <si>
+    <t>BR-046</t>
+  </si>
+  <si>
+    <t>TD-F-040</t>
+  </si>
+  <si>
+    <t>BR-047</t>
+  </si>
+  <si>
+    <t>TD-F-041</t>
+  </si>
+  <si>
+    <t>AQPI-12</t>
+  </si>
+  <si>
+    <t>BR-048</t>
+  </si>
+  <si>
+    <t>TD-F-042</t>
+  </si>
+  <si>
+    <t>br-048-offer-content.spec.js</t>
+  </si>
+  <si>
+    <t>BR-049</t>
+  </si>
+  <si>
+    <t>TD-F-043</t>
+  </si>
+  <si>
+    <t>br-049-offer-interaction.spec.js</t>
+  </si>
+  <si>
+    <t>BR-050</t>
+  </si>
+  <si>
+    <t>TD-F-044</t>
+  </si>
+  <si>
+    <t>br-050-offer-content.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-13</t>
+  </si>
+  <si>
+    <t>BR-052</t>
+  </si>
+  <si>
+    <t>TD-F-045</t>
+  </si>
+  <si>
+    <t>BR-053</t>
+  </si>
+  <si>
+    <t>TD-F-046</t>
+  </si>
+  <si>
+    <t>br-053-proceed-without-offers.spec.js</t>
+  </si>
+  <si>
+    <t>BR-054</t>
+  </si>
+  <si>
+    <t>TD-F-047</t>
+  </si>
+  <si>
+    <t>br-054-consent-personalization.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-15</t>
+  </si>
+  <si>
+    <t>BR-055</t>
+  </si>
+  <si>
+    <t>TD-F-048</t>
+  </si>
+  <si>
+    <t>br-055-cart-contents.spec.js</t>
+  </si>
+  <si>
+    <t>BR-056</t>
+  </si>
+  <si>
+    <t>TD-F-049</t>
+  </si>
+  <si>
+    <t>BR-057</t>
+  </si>
+  <si>
+    <t>TD-F-050</t>
+  </si>
+  <si>
+    <t>BR-058</t>
+  </si>
+  <si>
+    <t>TD-F-051</t>
+  </si>
+  <si>
+    <t>BR-059</t>
+  </si>
+  <si>
+    <t>TD-F-052</t>
+  </si>
+  <si>
+    <t>AQPI-16</t>
+  </si>
+  <si>
+    <t>BR-060</t>
+  </si>
+  <si>
+    <t>TD-F-053</t>
+  </si>
+  <si>
+    <t>BR-061</t>
+  </si>
+  <si>
+    <t>TD-F-054</t>
+  </si>
+  <si>
+    <t>br-061-ancillary-quantity.spec.js</t>
+  </si>
+  <si>
+    <t>BR-062</t>
+  </si>
+  <si>
+    <t>TD-F-055</t>
+  </si>
+  <si>
+    <t>br-062-ancillary-removal.spec.js</t>
+  </si>
+  <si>
+    <t>BR-063</t>
+  </si>
+  <si>
+    <t>TD-F-056</t>
+  </si>
+  <si>
+    <t>AQPI-17</t>
+  </si>
+  <si>
+    <t>BR-064</t>
+  </si>
+  <si>
+    <t>TD-F-057</t>
+  </si>
+  <si>
+    <t>br-064-itemized-total.spec.js</t>
+  </si>
+  <si>
+    <t>BR-065</t>
+  </si>
+  <si>
+    <t>TD-F-058</t>
+  </si>
+  <si>
+    <t>BR-066</t>
+  </si>
+  <si>
+    <t>TD-F-059</t>
+  </si>
+  <si>
+    <t>BR-067</t>
+  </si>
+  <si>
+    <t>TD-F-060</t>
+  </si>
+  <si>
+    <t>BR-068</t>
+  </si>
+  <si>
+    <t>TD-F-061</t>
+  </si>
+  <si>
+    <t>AQPI-19</t>
+  </si>
+  <si>
+    <t>BR-069</t>
+  </si>
+  <si>
+    <t>TD-F-062</t>
+  </si>
+  <si>
+    <t>br-069-checkout-fields.spec.js</t>
+  </si>
+  <si>
+    <t>BR-070</t>
+  </si>
+  <si>
+    <t>TD-N-003</t>
+  </si>
+  <si>
+    <t>br-070-guest-validation.spec.js</t>
+  </si>
+  <si>
+    <t>BR-071</t>
+  </si>
+  <si>
+    <t>TD-F-063</t>
+  </si>
+  <si>
+    <t>br-071-privacy-consent.spec.js</t>
+  </si>
+  <si>
+    <t>BR-072</t>
+  </si>
+  <si>
+    <t>TD-F-064</t>
+  </si>
+  <si>
+    <t>BR-073</t>
+  </si>
+  <si>
+    <t>TD-F-065</t>
+  </si>
+  <si>
+    <t>BR-074</t>
+  </si>
+  <si>
+    <t>TD-F-066</t>
+  </si>
+  <si>
+    <t>br-074-support-masking.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-20</t>
+  </si>
+  <si>
+    <t>BR-075</t>
+  </si>
+  <si>
+    <t>TD-F-067</t>
+  </si>
+  <si>
+    <t>br-075-amount-before-auth.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-068</t>
+  </si>
+  <si>
+    <t>BR-076</t>
+  </si>
+  <si>
+    <t>TD-F-069</t>
+  </si>
+  <si>
+    <t>BR-077</t>
+  </si>
+  <si>
+    <t>TD-F-070</t>
+  </si>
+  <si>
+    <t>br-077-payment-outcomes.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-071</t>
+  </si>
+  <si>
+    <t>TD-F-072</t>
+  </si>
+  <si>
+    <t>BR-078</t>
+  </si>
+  <si>
+    <t>TD-F-073</t>
+  </si>
+  <si>
+    <t>br-078-no-card-data.spec.js</t>
+  </si>
+  <si>
+    <t>BR-079</t>
+  </si>
+  <si>
+    <t>TD-F-074</t>
+  </si>
+  <si>
+    <t>BR-080</t>
+  </si>
+  <si>
+    <t>TD-F-075</t>
+  </si>
+  <si>
+    <t>AQPI-21</t>
+  </si>
+  <si>
+    <t>BR-081</t>
+  </si>
+  <si>
+    <t>TD-F-076</t>
+  </si>
+  <si>
+    <t>br-081-one-reservation.spec.js</t>
+  </si>
+  <si>
+    <t>BR-082</t>
+  </si>
+  <si>
+    <t>TD-F-077</t>
+  </si>
+  <si>
+    <t>br-082-idempotent-reservation.spec.js</t>
+  </si>
+  <si>
+    <t>BR-083</t>
+  </si>
+  <si>
+    <t>TD-F-078</t>
+  </si>
+  <si>
+    <t>br-083-reconcilable.spec.js</t>
+  </si>
+  <si>
+    <t>BR-084</t>
+  </si>
+  <si>
+    <t>TD-F-079</t>
+  </si>
+  <si>
+    <t>BR-085</t>
+  </si>
+  <si>
+    <t>TD-F-080</t>
+  </si>
+  <si>
+    <t>BR-086</t>
+  </si>
+  <si>
+    <t>TD-F-081</t>
+  </si>
+  <si>
+    <t>AQPI-22</t>
+  </si>
+  <si>
+    <t>BR-087</t>
+  </si>
+  <si>
+    <t>TD-F-082</t>
+  </si>
+  <si>
+    <t>br-087-booking-outcome.spec.js</t>
+  </si>
+  <si>
+    <t>BR-088</t>
+  </si>
+  <si>
+    <t>TD-F-083</t>
+  </si>
+  <si>
+    <t>br-088-no-false-confirmation.spec.js</t>
+  </si>
+  <si>
+    <t>BR-089</t>
+  </si>
+  <si>
+    <t>TD-F-084</t>
+  </si>
+  <si>
+    <t>br-089-unknown-state.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-24</t>
+  </si>
+  <si>
+    <t>BR-090</t>
+  </si>
+  <si>
+    <t>TD-F-085</t>
+  </si>
+  <si>
+    <t>br-090-confirmation-content.spec.js</t>
+  </si>
+  <si>
+    <t>BR-091</t>
+  </si>
+  <si>
+    <t>TD-F-086</t>
+  </si>
+  <si>
+    <t>br-091-confirmation-content.spec.js</t>
+  </si>
+  <si>
+    <t>BR-093</t>
+  </si>
+  <si>
+    <t>TD-F-087</t>
+  </si>
+  <si>
+    <t>BR-094</t>
+  </si>
+  <si>
+    <t>TD-F-088</t>
+  </si>
+  <si>
+    <t>br-094-confirmation-content.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-25</t>
+  </si>
+  <si>
+    <t>BR-095</t>
+  </si>
+  <si>
+    <t>TD-F-089</t>
+  </si>
+  <si>
+    <t>BR-096</t>
+  </si>
+  <si>
+    <t>TD-F-090</t>
+  </si>
+  <si>
+    <t>br-096-email-failure-isolated.spec.js</t>
+  </si>
+  <si>
+    <t>BR-097</t>
+  </si>
+  <si>
+    <t>TD-F-091</t>
+  </si>
+  <si>
+    <t>BR-098</t>
+  </si>
+  <si>
+    <t>TD-F-092</t>
+  </si>
+  <si>
+    <t>BR-099</t>
+  </si>
+  <si>
+    <t>TD-F-093</t>
+  </si>
+  <si>
+    <t>AQPI-26</t>
+  </si>
+  <si>
+    <t>BR-100</t>
+  </si>
+  <si>
+    <t>TD-F-094</t>
+  </si>
+  <si>
+    <t>br-100-resend-generic.spec.js</t>
+  </si>
+  <si>
+    <t>BR-101</t>
+  </si>
+  <si>
+    <t>TD-F-095</t>
+  </si>
+  <si>
+    <t>BR-102</t>
+  </si>
+  <si>
+    <t>TD-F-096</t>
+  </si>
+  <si>
+    <t>AQPI-28</t>
+  </si>
+  <si>
+    <t>BR-103</t>
+  </si>
+  <si>
+    <t>TD-F-097</t>
+  </si>
+  <si>
+    <t>BR-104</t>
+  </si>
+  <si>
+    <t>TD-F-098</t>
+  </si>
+  <si>
+    <t>BR-105</t>
+  </si>
+  <si>
+    <t>TD-F-099</t>
+  </si>
+  <si>
+    <t>BR-106</t>
+  </si>
+  <si>
+    <t>TD-F-100</t>
+  </si>
+  <si>
+    <t>br-106-support-masking.spec.js</t>
+  </si>
+  <si>
+    <t>BR-107</t>
+  </si>
+  <si>
+    <t>TD-F-101</t>
+  </si>
+  <si>
+    <t>AQPI-29</t>
+  </si>
+  <si>
+    <t>BR-108</t>
+  </si>
+  <si>
+    <t>TD-F-102</t>
+  </si>
+  <si>
+    <t>br-108-correlation-id.spec.js</t>
+  </si>
+  <si>
+    <t>BR-109</t>
+  </si>
+  <si>
+    <t>TD-F-103</t>
+  </si>
+  <si>
+    <t>BR-111</t>
+  </si>
+  <si>
+    <t>TD-F-104</t>
+  </si>
+  <si>
+    <t>BR-112</t>
+  </si>
+  <si>
+    <t>TD-F-105</t>
+  </si>
+  <si>
+    <t>BR-113</t>
+  </si>
+  <si>
+    <t>TD-F-106</t>
+  </si>
+  <si>
+    <t>AQPI-30</t>
+  </si>
+  <si>
+    <t>BR-115</t>
+  </si>
+  <si>
+    <t>TD-F-107</t>
+  </si>
+  <si>
+    <t>BR-116</t>
+  </si>
+  <si>
+    <t>TD-F-108</t>
+  </si>
+  <si>
+    <t>BR-117</t>
+  </si>
+  <si>
+    <t>TD-N-004</t>
+  </si>
+  <si>
+    <t>br-117-email-accessible.spec.js</t>
+  </si>
+  <si>
+    <t>AQPI-31</t>
+  </si>
+  <si>
+    <t>BR-119</t>
+  </si>
+  <si>
+    <t>TD-F-109</t>
+  </si>
+  <si>
+    <t>BR-120</t>
+  </si>
+  <si>
+    <t>TD-F-110</t>
+  </si>
+  <si>
+    <t>BR-121</t>
+  </si>
+  <si>
+    <t>TD-F-111</t>
+  </si>
+  <si>
+    <t>BR-122</t>
+  </si>
+  <si>
+    <t>TD-F-112</t>
+  </si>
+  <si>
+    <t>br-122-cart-expiry.spec.js</t>
+  </si>
+  <si>
+    <t>cart-service/src/main/resources/cart-service.yml</t>
+  </si>
+  <si>
+    <t>BR-123</t>
+  </si>
+  <si>
+    <t>TD-F-113</t>
+  </si>
+  <si>
+    <t>br-123-price-change-ack.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-114</t>
+  </si>
+  <si>
+    <t>BR-124</t>
+  </si>
+  <si>
+    <t>TD-F-115</t>
+  </si>
+  <si>
+    <t>br-124-resend-limit.spec.js</t>
+  </si>
+  <si>
+    <t>reservation-service/src/main/resources/reservation-service.yml</t>
+  </si>
+  <si>
+    <t>BR-125</t>
+  </si>
+  <si>
+    <t>TD-F-116</t>
+  </si>
+  <si>
+    <t>br-125-idempotency-key.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-117</t>
+  </si>
+  <si>
+    <t>TD-F-118</t>
+  </si>
+  <si>
+    <t>BR-126</t>
+  </si>
+  <si>
+    <t>TD-F-119</t>
+  </si>
+  <si>
+    <t>br-126-stay-length-limit.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-120</t>
+  </si>
+  <si>
+    <t>TD-F-121</t>
+  </si>
+  <si>
+    <t>TD-F-122</t>
+  </si>
+  <si>
+    <t>search-service/src/main/resources/search-service.yml</t>
+  </si>
+  <si>
+    <t>BR-127</t>
+  </si>
+  <si>
+    <t>TD-F-123</t>
+  </si>
+  <si>
+    <t>br-127-occupancy-limits.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-124</t>
+  </si>
+  <si>
+    <t>TD-F-125</t>
+  </si>
+  <si>
+    <t>TD-F-126</t>
+  </si>
+  <si>
+    <t>BR-128</t>
+  </si>
+  <si>
+    <t>TD-F-127</t>
+  </si>
+  <si>
+    <t>br-128-advance-horizon.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-128</t>
+  </si>
+  <si>
+    <t>BR-129</t>
+  </si>
+  <si>
+    <t>TD-F-129</t>
+  </si>
+  <si>
+    <t>BR-130</t>
+  </si>
+  <si>
+    <t>TD-F-130</t>
+  </si>
+  <si>
+    <t>BR-131</t>
+  </si>
+  <si>
+    <t>TD-F-131</t>
+  </si>
+  <si>
+    <t>br-131-free-cancellation.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-132</t>
+  </si>
+  <si>
+    <t>BR-132</t>
+  </si>
+  <si>
+    <t>TD-F-133</t>
+  </si>
+  <si>
+    <t>br-132-cancellation-outcome.spec.js</t>
+  </si>
+  <si>
     <t>Gate</t>
   </si>
   <si>
@@ -3526,7 +4650,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T16:18:39.671Z</t>
+    <t>2026-10-02T19:28:01.166Z</t>
   </si>
   <si>
     <t>13 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -3538,7 +4662,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-02T16:18:39.703Z</t>
+    <t>2026-10-02T19:28:01.200Z</t>
   </si>
   <si>
     <t>7 requirements, 11 test cases, 5 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -4402,6 +5526,5637 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M138"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M117" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M130" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L137" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M137" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -4414,189 +11169,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1137</v>
+        <v>1511</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1138</v>
+        <v>1512</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1139</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1140</v>
+        <v>1514</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1141</v>
+        <v>1515</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1142</v>
+        <v>1516</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1143</v>
+        <v>1517</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1144</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1145</v>
+        <v>1519</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1146</v>
+        <v>1520</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1147</v>
+        <v>1521</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1148</v>
+        <v>1522</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1149</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1150</v>
+        <v>1524</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1151</v>
+        <v>1525</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1152</v>
+        <v>1526</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1153</v>
+        <v>1527</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1154</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1155</v>
+        <v>1529</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1156</v>
+        <v>1530</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1157</v>
+        <v>1531</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1158</v>
+        <v>1532</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1159</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1160</v>
+        <v>1534</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1161</v>
+        <v>1535</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1162</v>
+        <v>1536</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1163</v>
+        <v>1537</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1164</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1165</v>
+        <v>1539</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1166</v>
+        <v>1540</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1167</v>
+        <v>1541</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1168</v>
+        <v>1542</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1169</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1170</v>
+        <v>1544</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1171</v>
+        <v>1545</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1172</v>
+        <v>1546</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1173</v>
+        <v>1547</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1174</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1175</v>
+        <v>1549</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1176</v>
+        <v>1550</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1177</v>
+        <v>1551</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1178</v>
+        <v>1552</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1179</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1180</v>
+        <v>1554</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1181</v>
+        <v>1555</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1182</v>
+        <v>1556</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1183</v>
+        <v>1557</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1184</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1185</v>
+        <v>1559</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1186</v>
+        <v>1560</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1187</v>
+        <v>1561</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1188</v>
+        <v>1562</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1189</v>
+        <v>1563</v>
       </c>
     </row>
   </sheetData>
@@ -4605,7 +11360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -4619,203 +11374,203 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1190</v>
+        <v>1564</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1191</v>
+        <v>1565</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1192</v>
+        <v>1566</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1193</v>
+        <v>1567</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1194</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1195</v>
+        <v>1569</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1196</v>
+        <v>1570</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1198</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1165</v>
+        <v>1539</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1199</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1200</v>
+        <v>1574</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1155</v>
+        <v>1529</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1201</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1202</v>
+        <v>1576</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1185</v>
+        <v>1559</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1203</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1204</v>
+        <v>1578</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1205</v>
+        <v>1579</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1206</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1207</v>
+        <v>1581</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1208</v>
+        <v>1582</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1209</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1210</v>
+        <v>1584</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1211</v>
+        <v>1585</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1212</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1213</v>
+        <v>1587</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1214</v>
+        <v>1588</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1215</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1216</v>
+        <v>1590</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1217</v>
+        <v>1591</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1218</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1219</v>
+        <v>1593</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1220</v>
+        <v>1594</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1221</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1222</v>
+        <v>1596</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1223</v>
+        <v>1597</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1197</v>
+        <v>1571</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>351</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1224</v>
+        <v>1598</v>
       </c>
     </row>
   </sheetData>
@@ -13875,7 +20630,7 @@
         <v>1055</v>
       </c>
       <c r="E2" s="2">
-        <v>567</v>
+        <v>670</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -13993,7 +20748,7 @@
         <v>1055</v>
       </c>
       <c r="E8" s="2">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -14011,7 +20766,7 @@
         <v>1055</v>
       </c>
       <c r="E9" s="2">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -14029,7 +20784,7 @@
         <v>1055</v>
       </c>
       <c r="E10" s="2">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -14047,7 +20802,7 @@
         <v>1055</v>
       </c>
       <c r="E11" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -14065,7 +20820,7 @@
         <v>1055</v>
       </c>
       <c r="E12" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -14083,7 +20838,7 @@
         <v>1055</v>
       </c>
       <c r="E13" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -14161,7 +20916,7 @@
         <v>1055</v>
       </c>
       <c r="E17" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -14179,7 +20934,7 @@
         <v>1055</v>
       </c>
       <c r="E18" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -14237,7 +20992,7 @@
         <v>1055</v>
       </c>
       <c r="E21" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -14275,7 +21030,7 @@
         <v>1055</v>
       </c>
       <c r="E23" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -14293,7 +21048,7 @@
         <v>1055</v>
       </c>
       <c r="E24" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -14311,7 +21066,7 @@
         <v>1055</v>
       </c>
       <c r="E25" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -14329,7 +21084,7 @@
         <v>1055</v>
       </c>
       <c r="E26" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -14365,7 +21120,7 @@
         <v>1055</v>
       </c>
       <c r="E28" s="2">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -14383,7 +21138,7 @@
         <v>1055</v>
       </c>
       <c r="E29" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -14401,7 +21156,7 @@
         <v>1055</v>
       </c>
       <c r="E30" s="2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -14419,7 +21174,7 @@
         <v>1055</v>
       </c>
       <c r="E31" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -14457,7 +21212,7 @@
         <v>1055</v>
       </c>
       <c r="E33" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -14475,7 +21230,7 @@
         <v>1055</v>
       </c>
       <c r="E34" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -14533,7 +21288,7 @@
         <v>1055</v>
       </c>
       <c r="E37" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -14571,7 +21326,7 @@
         <v>1055</v>
       </c>
       <c r="E39" s="2">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -14589,7 +21344,7 @@
         <v>1055</v>
       </c>
       <c r="E40" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -14687,7 +21442,7 @@
         <v>1055</v>
       </c>
       <c r="E45" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -14705,7 +21460,7 @@
         <v>1055</v>
       </c>
       <c r="E46" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -14723,7 +21478,7 @@
         <v>1055</v>
       </c>
       <c r="E47" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -14761,7 +21516,7 @@
         <v>1055</v>
       </c>
       <c r="E49" s="2">
-        <v>226</v>
+        <v>276</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -14779,7 +21534,7 @@
         <v>1055</v>
       </c>
       <c r="E50" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -14797,7 +21552,7 @@
         <v>1055</v>
       </c>
       <c r="E51" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -14915,7 +21670,7 @@
         <v>1055</v>
       </c>
       <c r="E57" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -14971,7 +21726,7 @@
         <v>1055</v>
       </c>
       <c r="E60" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -15069,7 +21824,7 @@
         <v>1055</v>
       </c>
       <c r="E65" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -15087,7 +21842,7 @@
         <v>1055</v>
       </c>
       <c r="E66" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -15105,7 +21860,7 @@
         <v>1055</v>
       </c>
       <c r="E67" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -15163,7 +21918,7 @@
         <v>1055</v>
       </c>
       <c r="E70" s="2">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -15181,7 +21936,7 @@
         <v>1055</v>
       </c>
       <c r="E71" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -15199,7 +21954,7 @@
         <v>1055</v>
       </c>
       <c r="E72" s="2">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -15237,7 +21992,7 @@
         <v>1055</v>
       </c>
       <c r="E74" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -15255,7 +22010,7 @@
         <v>1055</v>
       </c>
       <c r="E75" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -15273,7 +22028,7 @@
         <v>1055</v>
       </c>
       <c r="E76" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -15291,7 +22046,7 @@
         <v>1055</v>
       </c>
       <c r="E77" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -15349,7 +22104,7 @@
         <v>1055</v>
       </c>
       <c r="E80" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -15367,7 +22122,7 @@
         <v>1055</v>
       </c>
       <c r="E81" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -15385,7 +22140,7 @@
         <v>1055</v>
       </c>
       <c r="E82" s="2">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -15463,7 +22218,7 @@
         <v>1055</v>
       </c>
       <c r="E86" s="2">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -15481,7 +22236,7 @@
         <v>1055</v>
       </c>
       <c r="E87" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -15499,7 +22254,7 @@
         <v>1055</v>
       </c>
       <c r="E88" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -15517,7 +22272,7 @@
         <v>1055</v>
       </c>
       <c r="E89" s="2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -15535,7 +22290,7 @@
         <v>1055</v>
       </c>
       <c r="E90" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -15573,7 +22328,7 @@
         <v>1055</v>
       </c>
       <c r="E92" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -15611,7 +22366,7 @@
         <v>1055</v>
       </c>
       <c r="E94" s="2">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -15689,7 +22444,7 @@
         <v>1055</v>
       </c>
       <c r="E98" s="2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -15807,7 +22562,7 @@
         <v>1055</v>
       </c>
       <c r="E104" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -15845,7 +22600,7 @@
         <v>1055</v>
       </c>
       <c r="E106" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -15983,7 +22738,7 @@
         <v>1055</v>
       </c>
       <c r="E113" s="2">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -16079,7 +22834,7 @@
         <v>1055</v>
       </c>
       <c r="E118" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -16115,7 +22870,7 @@
         <v>1055</v>
       </c>
       <c r="E120" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -16151,7 +22906,7 @@
         <v>1055</v>
       </c>
       <c r="E122" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -16187,7 +22942,7 @@
         <v>1055</v>
       </c>
       <c r="E124" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -16205,7 +22960,7 @@
         <v>1055</v>
       </c>
       <c r="E125" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -16223,7 +22978,7 @@
         <v>1055</v>
       </c>
       <c r="E126" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -16259,7 +23014,7 @@
         <v>1055</v>
       </c>
       <c r="E128" s="2">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -16277,7 +23032,7 @@
         <v>1055</v>
       </c>
       <c r="E129" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -16295,7 +23050,7 @@
         <v>1055</v>
       </c>
       <c r="E130" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -16313,7 +23068,7 @@
         <v>1055</v>
       </c>
       <c r="E131" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -16331,7 +23086,7 @@
         <v>1055</v>
       </c>
       <c r="E132" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -16349,7 +23104,7 @@
         <v>1055</v>
       </c>
       <c r="E133" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -16407,7 +23162,7 @@
         <v>1055</v>
       </c>
       <c r="E136" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -16425,7 +23180,7 @@
         <v>1055</v>
       </c>
       <c r="E137" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -16455,18 +23210,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -16477,16 +23234,16 @@
         <v>1060</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1063</v>
@@ -16494,33 +23251,45 @@
       <c r="I1" s="1" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>1068</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>317</v>
       </c>
     </row>
@@ -16548,16 +23317,16 @@
         <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>348</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -16586,7 +23355,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16609,7 +23378,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16632,7 +23401,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16655,7 +23424,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16678,7 +23447,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16701,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16724,7 +23493,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16747,7 +23516,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16770,7 +23539,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16793,7 +23562,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16816,7 +23585,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16839,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16862,7 +23631,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16885,7 +23654,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16908,7 +23677,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16931,7 +23700,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16954,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16977,7 +23746,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17000,7 +23769,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17023,7 +23792,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17046,7 +23815,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17069,7 +23838,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17092,7 +23861,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17115,7 +23884,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17138,7 +23907,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17161,7 +23930,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17184,7 +23953,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17207,7 +23976,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17230,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17253,7 +24022,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17276,7 +24045,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17299,7 +24068,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17322,7 +24091,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17345,7 +24114,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17368,7 +24137,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17391,7 +24160,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17414,7 +24183,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17437,7 +24206,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17460,7 +24229,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17483,7 +24252,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17506,7 +24275,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17529,7 +24298,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17552,7 +24321,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17575,7 +24344,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17598,7 +24367,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17621,7 +24390,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17644,7 +24413,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17667,7 +24436,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17690,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17713,7 +24482,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17736,7 +24505,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17759,7 +24528,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17782,7 +24551,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17805,7 +24574,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17828,7 +24597,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17851,7 +24620,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17874,7 +24643,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17897,7 +24666,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17920,7 +24689,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17943,7 +24712,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17966,7 +24735,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17989,7 +24758,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18012,7 +24781,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18035,7 +24804,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18058,7 +24827,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18081,7 +24850,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18104,7 +24873,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18127,7 +24896,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18150,7 +24919,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18173,7 +24942,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18196,7 +24965,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18219,7 +24988,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18242,7 +25011,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18265,7 +25034,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18288,7 +25057,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18311,7 +25080,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18334,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18357,7 +25126,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18380,7 +25149,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18403,7 +25172,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18426,7 +25195,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18449,7 +25218,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18472,7 +25241,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18495,7 +25264,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18518,7 +25287,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18541,7 +25310,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18564,7 +25333,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18587,7 +25356,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18610,7 +25379,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18633,7 +25402,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18656,7 +25425,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18679,7 +25448,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18702,7 +25471,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18725,7 +25494,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18748,7 +25517,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18771,7 +25540,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18794,7 +25563,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18817,7 +25586,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18840,7 +25609,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18863,7 +25632,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18886,7 +25655,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18909,7 +25678,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18932,7 +25701,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18955,7 +25724,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18978,7 +25747,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19001,7 +25770,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19024,7 +25793,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19047,7 +25816,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19070,7 +25839,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19093,7 +25862,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19116,7 +25885,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19139,7 +25908,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19162,7 +25931,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19185,7 +25954,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19208,7 +25977,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19231,7 +26000,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19254,7 +26023,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19277,7 +26046,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19300,7 +26069,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19323,7 +26092,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19346,7 +26115,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19369,7 +26138,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19392,7 +26161,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19415,7 +26184,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19438,7 +26207,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19461,7 +26230,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19484,7 +26253,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19507,7 +26276,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19530,7 +26299,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19553,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19576,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="133" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19599,7 +26368,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
   </sheetData>
@@ -19621,13 +26390,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -19635,212 +26404,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1091</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1000</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>351</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>631</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>683</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>351</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
     </row>
   </sheetData>
@@ -19851,65 +26620,226 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="80" customWidth="1"/>
+    <col min="1" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1128</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1130</v>
+        <v>351</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E2" s="2" t="s">
         <v>1132</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1134</v>
+        <v>39</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>1136</v>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>1137</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
@@ -10,13 +10,14 @@
     <sheet sheetId="4" name="Test Cases" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Execution" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Defects" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Coverage" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Attribute coverage" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Traceability by story" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Traceability matrix" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Approvals" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Skills" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Hand-overs" state="visible" r:id="rId16"/>
+    <sheet sheetId="7" name="Fixed and certified" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Coverage" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Attribute coverage" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Traceability by story" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Traceability matrix" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Approvals" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Skills" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Hand-overs" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5956" uniqueCount="1677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6007" uniqueCount="1703">
   <si>
     <t>Metric</t>
   </si>
@@ -167,7 +168,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (24215dc) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 10 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 82 passed and 1 failed (pass rate 98.8%). 1 defect(s) were raised from real failures: DEF-001 A 15-night stay in Paris is rejected: returns 200 instead of 400.</t>
+    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 10 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 79 passed and 4 failed (pass rate 95.2%). 4 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-007 A 15-night stay in Paris is rejected: returns 200 instead of 400; DEF-008 Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused: returns 200 instead of 409.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -206,13 +207,13 @@
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (24215dc)</t>
+    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (24215dc) at 2026-10-02T19:44:12.281Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-02T20:05:18.310Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2927,7 +2928,7 @@
     <t>functional, automation</t>
   </si>
   <si>
-    <t>AQPI-33, REQ-122, BR-122</t>
+    <t>AQPI-15, AQPI-33, REQ-122, BR-122</t>
   </si>
   <si>
     <t>Changed</t>
@@ -2959,7 +2960,7 @@
     <t>Revalidation requires acknowledgement; first submit HTTP 409 PRICE_CHANGE_REQUIRES_ACKNOWLEDGEMENT; after acknowledging HTTP 201</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-123, BR-123</t>
+    <t>AQPI-17, REQ-123, BR-123</t>
   </si>
   <si>
     <t>TC-F-114</t>
@@ -2998,7 +2999,7 @@
     <t>First 5 resends HTTP 202, the next HTTP 429; still one reservation</t>
   </si>
   <si>
-    <t>AQPI-35, REQ-124, BR-124</t>
+    <t>AQPI-26, AQPI-35, REQ-124, BR-124</t>
   </si>
   <si>
     <t>v2 (CYC-4): name was "The 4th resend within 24 hours is refused"; expected was "First 3 resends HTTP 202, the next HTTP 429; still one reservation"</t>
@@ -3020,7 +3021,7 @@
     <t>HTTP 400 IDEMPOTENCY_KEY_REQUIRED</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml, REQ-125, BR-125</t>
+    <t>AQPI-21, REQ-125, BR-125</t>
   </si>
   <si>
     <t>TC-F-117</t>
@@ -3070,7 +3071,7 @@
     <t>HTTP 200 with a searchId</t>
   </si>
   <si>
-    <t>AQPI-34, REQ-126, BR-126</t>
+    <t>AQPI-4, AQPI-34, REQ-126, BR-126</t>
   </si>
   <si>
     <t>v2 (CYC-4): re-designed because a rule it depends on changed; case text unchanged</t>
@@ -3145,7 +3146,7 @@
     <t>occupancy.adults=4; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-127, BR-127</t>
+    <t>AQPI-4, REQ-127, BR-127</t>
   </si>
   <si>
     <t>TC-F-124</t>
@@ -3217,7 +3218,7 @@
     <t>stay.checkInOffsetDays=500; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-128, BR-128</t>
+    <t>AQPI-4, REQ-128, BR-128</t>
   </si>
   <si>
     <t>TC-F-128</t>
@@ -3504,6 +3505,54 @@
     <t>DEF-001</t>
   </si>
   <si>
+    <t>A price change within 1% does not need acknowledgement: returns true instead of false</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>AQPI-17</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-17 in the platform</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>expect(rv.body.requiresAcknowledgement).toBe(false);</t>
+  </si>
+  <si>
+    <t>still open</t>
+  </si>
+  <si>
+    <t>DEF-002</t>
+  </si>
+  <si>
+    <t>A key shorter than 8 characters is refused: returns 201 instead of 400</t>
+  </si>
+  <si>
+    <t>AQPI-21</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-21 in the platform</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>expect(r.status).toBe(400);</t>
+  </si>
+  <si>
+    <t>DEF-007</t>
+  </si>
+  <si>
     <t>A 15-night stay in Paris is rejected: returns 200 instead of 400</t>
   </si>
   <si>
@@ -3513,13 +3562,55 @@
     <t>not raised in Jira; linked to AQPI-34 in the platform</t>
   </si>
   <si>
-    <t>400</t>
-  </si>
-  <si>
     <t>200</t>
   </si>
   <si>
-    <t>expect(r.status).toBe(400);</t>
+    <t>DEF-008</t>
+  </si>
+  <si>
+    <t>Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused: returns 200 instead of 409</t>
+  </si>
+  <si>
+    <t>AQPI-25</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-25 in the platform</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>expect(over.status).toBe(409);</t>
+  </si>
+  <si>
+    <t>First seen</t>
+  </si>
+  <si>
+    <t>Retested in</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>DEF-003</t>
+  </si>
+  <si>
+    <t>9 rooms in one search are rejected: returns 200 instead of 400</t>
+  </si>
+  <si>
+    <t>AQPI-4</t>
+  </si>
+  <si>
+    <t>CYC-1</t>
+  </si>
+  <si>
+    <t>CYC-4</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Fixed in build demo/hotel-booking-platform-v2; TC-F-126 re-run in CYC-4 passed, so DEF-003 (first seen in CYC-1) is certified closed.</t>
   </si>
   <si>
     <t>Text</t>
@@ -3747,9 +3838,6 @@
     <t>8.1 Generate confirmation message</t>
   </si>
   <si>
-    <t>AQPI-25</t>
-  </si>
-  <si>
     <t>8.2 Send and track confirmation email</t>
   </si>
   <si>
@@ -3897,9 +3985,6 @@
     <t>TD-F-014</t>
   </si>
   <si>
-    <t>AQPI-4</t>
-  </si>
-  <si>
     <t>BR-020</t>
   </si>
   <si>
@@ -4254,9 +4339,6 @@
     <t>TD-F-056</t>
   </si>
   <si>
-    <t>AQPI-17</t>
-  </si>
-  <si>
     <t>BR-064</t>
   </si>
   <si>
@@ -4398,9 +4480,6 @@
     <t>TD-F-075</t>
   </si>
   <si>
-    <t>AQPI-21</t>
-  </si>
-  <si>
     <t>BR-081</t>
   </si>
   <si>
@@ -4680,6 +4759,9 @@
     <t>TD-F-111</t>
   </si>
   <si>
+    <t>AQPI-15, AQPI-33</t>
+  </si>
+  <si>
     <t>BR-122</t>
   </si>
   <si>
@@ -4689,9 +4771,6 @@
     <t>br-122-cart-expiry.spec.js</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml</t>
-  </si>
-  <si>
     <t>BR-123</t>
   </si>
   <si>
@@ -4704,6 +4783,9 @@
     <t>TD-F-114</t>
   </si>
   <si>
+    <t>AQPI-26, AQPI-35</t>
+  </si>
+  <si>
     <t>BR-124</t>
   </si>
   <si>
@@ -4713,9 +4795,6 @@
     <t>br-124-resend-limit.spec.js</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml</t>
-  </si>
-  <si>
     <t>BR-125</t>
   </si>
   <si>
@@ -4731,6 +4810,9 @@
     <t>TD-F-118</t>
   </si>
   <si>
+    <t>AQPI-4, AQPI-34</t>
+  </si>
+  <si>
     <t>BR-126</t>
   </si>
   <si>
@@ -4749,9 +4831,6 @@
     <t>TD-F-122</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml</t>
-  </si>
-  <si>
     <t>BR-127</t>
   </si>
   <si>
@@ -4893,7 +4972,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T19:44:22.405Z</t>
+    <t>2026-10-02T20:05:20.214Z</t>
   </si>
   <si>
     <t>33 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -4905,7 +4984,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-02T19:44:22.445Z</t>
+    <t>2026-10-02T20:05:20.255Z</t>
   </si>
   <si>
     <t>13 requirements, 18 test cases, 10 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -5702,7 +5781,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5710,7 +5789,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5718,7 +5797,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="2">
-        <v>98.8</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5734,7 +5813,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5742,7 +5821,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>46.4</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5768,6 +5847,411 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E9" s="2">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M145"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -5787,19 +6271,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1207</v>
+        <v>1236</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1208</v>
+        <v>1237</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1209</v>
+        <v>1238</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1210</v>
+        <v>1239</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>337</v>
@@ -5808,19 +6292,19 @@
         <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1211</v>
+        <v>1240</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1212</v>
+        <v>1241</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1213</v>
+        <v>1242</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1104</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1214</v>
+        <v>1243</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1114</v>
@@ -5828,7 +6312,7 @@
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1215</v>
+        <v>1244</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>57</v>
@@ -5837,7 +6321,7 @@
         <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1216</v>
+        <v>1245</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>349</v>
@@ -5852,10 +6336,10 @@
         <v>360</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1217</v>
+        <v>1246</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1218</v>
+        <v>1247</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1107</v>
@@ -5869,7 +6353,7 @@
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1215</v>
+        <v>1244</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>67</v>
@@ -5878,7 +6362,7 @@
         <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1219</v>
+        <v>1248</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>364</v>
@@ -5893,7 +6377,7 @@
         <v>373</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1220</v>
+        <v>1249</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -5908,7 +6392,7 @@
     </row>
     <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1221</v>
+        <v>1250</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>69</v>
@@ -5917,7 +6401,7 @@
         <v>70</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1222</v>
+        <v>1251</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>374</v>
@@ -5932,7 +6416,7 @@
         <v>373</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1223</v>
+        <v>1252</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -5947,7 +6431,7 @@
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1221</v>
+        <v>1250</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>72</v>
@@ -5956,7 +6440,7 @@
         <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1224</v>
+        <v>1253</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>378</v>
@@ -5971,7 +6455,7 @@
         <v>373</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1225</v>
+        <v>1254</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -5986,7 +6470,7 @@
     </row>
     <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1221</v>
+        <v>1250</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>74</v>
@@ -5995,7 +6479,7 @@
         <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1226</v>
+        <v>1255</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>382</v>
@@ -6010,7 +6494,7 @@
         <v>373</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1227</v>
+        <v>1256</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -6025,7 +6509,7 @@
     </row>
     <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1221</v>
+        <v>1250</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>76</v>
@@ -6034,7 +6518,7 @@
         <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1228</v>
+        <v>1257</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>386</v>
@@ -6049,7 +6533,7 @@
         <v>373</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1229</v>
+        <v>1258</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -6064,7 +6548,7 @@
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>78</v>
@@ -6073,7 +6557,7 @@
         <v>79</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1231</v>
+        <v>1260</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>390</v>
@@ -6088,10 +6572,10 @@
         <v>360</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1232</v>
+        <v>1261</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1233</v>
+        <v>1262</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1107</v>
@@ -6105,7 +6589,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>80</v>
@@ -6114,7 +6598,7 @@
         <v>81</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1234</v>
+        <v>1263</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>398</v>
@@ -6129,10 +6613,10 @@
         <v>360</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1235</v>
+        <v>1264</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1236</v>
+        <v>1265</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1107</v>
@@ -6146,7 +6630,7 @@
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>82</v>
@@ -6155,7 +6639,7 @@
         <v>83</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1237</v>
+        <v>1266</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>404</v>
@@ -6170,10 +6654,10 @@
         <v>360</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1238</v>
+        <v>1267</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1239</v>
+        <v>1268</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1107</v>
@@ -6187,7 +6671,7 @@
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>82</v>
@@ -6196,7 +6680,7 @@
         <v>83</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1237</v>
+        <v>1266</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>411</v>
@@ -6211,10 +6695,10 @@
         <v>360</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1240</v>
+        <v>1269</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1239</v>
+        <v>1268</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1107</v>
@@ -6228,7 +6712,7 @@
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>82</v>
@@ -6237,7 +6721,7 @@
         <v>83</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1237</v>
+        <v>1266</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>417</v>
@@ -6252,10 +6736,10 @@
         <v>360</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1241</v>
+        <v>1270</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1239</v>
+        <v>1268</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1107</v>
@@ -6269,7 +6753,7 @@
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>84</v>
@@ -6278,7 +6762,7 @@
         <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1242</v>
+        <v>1271</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>423</v>
@@ -6293,10 +6777,10 @@
         <v>360</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1243</v>
+        <v>1272</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1244</v>
+        <v>1273</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1107</v>
@@ -6310,7 +6794,7 @@
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>87</v>
@@ -6319,7 +6803,7 @@
         <v>88</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1245</v>
+        <v>1274</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>432</v>
@@ -6334,7 +6818,7 @@
         <v>373</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1246</v>
+        <v>1275</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -6349,7 +6833,7 @@
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>89</v>
@@ -6358,7 +6842,7 @@
         <v>90</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1247</v>
+        <v>1276</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>436</v>
@@ -6373,7 +6857,7 @@
         <v>373</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1248</v>
+        <v>1277</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -6388,7 +6872,7 @@
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>91</v>
@@ -6397,7 +6881,7 @@
         <v>92</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1249</v>
+        <v>1278</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>440</v>
@@ -6412,7 +6896,7 @@
         <v>373</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1250</v>
+        <v>1279</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -6427,7 +6911,7 @@
     </row>
     <row r="17" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1251</v>
+        <v>1151</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>93</v>
@@ -6436,7 +6920,7 @@
         <v>94</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1252</v>
+        <v>1280</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>444</v>
@@ -6451,10 +6935,10 @@
         <v>360</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1253</v>
+        <v>1281</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1254</v>
+        <v>1282</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1107</v>
@@ -6468,7 +6952,7 @@
     </row>
     <row r="18" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1251</v>
+        <v>1151</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>95</v>
@@ -6477,7 +6961,7 @@
         <v>96</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1255</v>
+        <v>1283</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>450</v>
@@ -6492,10 +6976,10 @@
         <v>360</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1256</v>
+        <v>1284</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1257</v>
+        <v>1285</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1107</v>
@@ -6509,7 +6993,7 @@
     </row>
     <row r="19" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1251</v>
+        <v>1151</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>97</v>
@@ -6518,7 +7002,7 @@
         <v>98</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1258</v>
+        <v>1286</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>457</v>
@@ -6533,7 +7017,7 @@
         <v>373</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1259</v>
+        <v>1287</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -6548,7 +7032,7 @@
     </row>
     <row r="20" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>1251</v>
+        <v>1151</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>101</v>
@@ -6557,7 +7041,7 @@
         <v>102</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1260</v>
+        <v>1288</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>461</v>
@@ -6572,7 +7056,7 @@
         <v>373</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1261</v>
+        <v>1289</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -6587,7 +7071,7 @@
     </row>
     <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1262</v>
+        <v>1290</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>103</v>
@@ -6596,7 +7080,7 @@
         <v>104</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1263</v>
+        <v>1291</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>465</v>
@@ -6611,10 +7095,10 @@
         <v>360</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1264</v>
+        <v>1292</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1265</v>
+        <v>1293</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>1107</v>
@@ -6628,7 +7112,7 @@
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1262</v>
+        <v>1290</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>105</v>
@@ -6637,7 +7121,7 @@
         <v>106</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1266</v>
+        <v>1294</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>467</v>
@@ -6652,7 +7136,7 @@
         <v>373</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1267</v>
+        <v>1295</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
@@ -6667,7 +7151,7 @@
     </row>
     <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1262</v>
+        <v>1290</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>107</v>
@@ -6676,7 +7160,7 @@
         <v>108</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1268</v>
+        <v>1296</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>471</v>
@@ -6691,10 +7175,10 @@
         <v>360</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1269</v>
+        <v>1297</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1270</v>
+        <v>1298</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>1107</v>
@@ -6708,7 +7192,7 @@
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1271</v>
+        <v>1299</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>109</v>
@@ -6717,7 +7201,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1272</v>
+        <v>1300</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>477</v>
@@ -6732,10 +7216,10 @@
         <v>360</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1273</v>
+        <v>1301</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1274</v>
+        <v>1302</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1107</v>
@@ -6749,7 +7233,7 @@
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1271</v>
+        <v>1299</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>111</v>
@@ -6758,7 +7242,7 @@
         <v>112</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1275</v>
+        <v>1303</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>483</v>
@@ -6773,10 +7257,10 @@
         <v>360</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1276</v>
+        <v>1304</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1277</v>
+        <v>1305</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1107</v>
@@ -6790,7 +7274,7 @@
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>1271</v>
+        <v>1299</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>113</v>
@@ -6799,7 +7283,7 @@
         <v>114</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1278</v>
+        <v>1306</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>488</v>
@@ -6814,10 +7298,10 @@
         <v>360</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1279</v>
+        <v>1307</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1280</v>
+        <v>1308</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1107</v>
@@ -6831,7 +7315,7 @@
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>1271</v>
+        <v>1299</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>115</v>
@@ -6840,7 +7324,7 @@
         <v>116</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1281</v>
+        <v>1309</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>496</v>
@@ -6855,10 +7339,10 @@
         <v>360</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1282</v>
+        <v>1310</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1283</v>
+        <v>1311</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1107</v>
@@ -6872,7 +7356,7 @@
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>1271</v>
+        <v>1299</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>117</v>
@@ -6881,7 +7365,7 @@
         <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1284</v>
+        <v>1312</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>502</v>
@@ -6896,10 +7380,10 @@
         <v>360</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1285</v>
+        <v>1313</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1286</v>
+        <v>1314</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1107</v>
@@ -6913,7 +7397,7 @@
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1287</v>
+        <v>1315</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>119</v>
@@ -6922,7 +7406,7 @@
         <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1288</v>
+        <v>1316</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>509</v>
@@ -6937,10 +7421,10 @@
         <v>360</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1289</v>
+        <v>1317</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1290</v>
+        <v>1318</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1107</v>
@@ -6954,7 +7438,7 @@
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1287</v>
+        <v>1315</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>121</v>
@@ -6963,7 +7447,7 @@
         <v>122</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1291</v>
+        <v>1319</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>515</v>
@@ -6978,10 +7462,10 @@
         <v>360</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1292</v>
+        <v>1320</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>1293</v>
+        <v>1321</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>1107</v>
@@ -6995,7 +7479,7 @@
     </row>
     <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1287</v>
+        <v>1315</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>121</v>
@@ -7004,7 +7488,7 @@
         <v>122</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1291</v>
+        <v>1319</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>521</v>
@@ -7019,10 +7503,10 @@
         <v>360</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1294</v>
+        <v>1322</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1293</v>
+        <v>1321</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>1107</v>
@@ -7036,7 +7520,7 @@
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>1287</v>
+        <v>1315</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>123</v>
@@ -7045,7 +7529,7 @@
         <v>124</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1295</v>
+        <v>1323</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>526</v>
@@ -7060,7 +7544,7 @@
         <v>373</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1296</v>
+        <v>1324</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
@@ -7075,7 +7559,7 @@
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1287</v>
+        <v>1315</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>125</v>
@@ -7084,7 +7568,7 @@
         <v>126</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1297</v>
+        <v>1325</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>530</v>
@@ -7099,10 +7583,10 @@
         <v>360</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1298</v>
+        <v>1326</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>1299</v>
+        <v>1327</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>1107</v>
@@ -7116,7 +7600,7 @@
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1300</v>
+        <v>1328</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>127</v>
@@ -7125,7 +7609,7 @@
         <v>128</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1301</v>
+        <v>1329</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>536</v>
@@ -7140,10 +7624,10 @@
         <v>360</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1302</v>
+        <v>1330</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1303</v>
+        <v>1331</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1107</v>
@@ -7157,7 +7641,7 @@
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1300</v>
+        <v>1328</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>129</v>
@@ -7166,7 +7650,7 @@
         <v>130</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1304</v>
+        <v>1332</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>542</v>
@@ -7181,7 +7665,7 @@
         <v>373</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1305</v>
+        <v>1333</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
@@ -7196,7 +7680,7 @@
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>1300</v>
+        <v>1328</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>131</v>
@@ -7205,7 +7689,7 @@
         <v>132</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1306</v>
+        <v>1334</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>546</v>
@@ -7220,7 +7704,7 @@
         <v>373</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1307</v>
+        <v>1335</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -7235,7 +7719,7 @@
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1300</v>
+        <v>1328</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>133</v>
@@ -7244,7 +7728,7 @@
         <v>134</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1308</v>
+        <v>1336</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>550</v>
@@ -7259,10 +7743,10 @@
         <v>360</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1309</v>
+        <v>1337</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>1310</v>
+        <v>1338</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>1107</v>
@@ -7276,7 +7760,7 @@
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>1311</v>
+        <v>1339</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>135</v>
@@ -7285,7 +7769,7 @@
         <v>136</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1312</v>
+        <v>1340</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>556</v>
@@ -7300,7 +7784,7 @@
         <v>373</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1313</v>
+        <v>1341</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -7315,7 +7799,7 @@
     </row>
     <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1311</v>
+        <v>1339</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>137</v>
@@ -7324,7 +7808,7 @@
         <v>138</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1314</v>
+        <v>1342</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>560</v>
@@ -7339,10 +7823,10 @@
         <v>360</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1315</v>
+        <v>1343</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>1316</v>
+        <v>1344</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>1107</v>
@@ -7356,7 +7840,7 @@
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>1311</v>
+        <v>1339</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>139</v>
@@ -7365,7 +7849,7 @@
         <v>140</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1317</v>
+        <v>1345</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>566</v>
@@ -7380,10 +7864,10 @@
         <v>360</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1318</v>
+        <v>1346</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1319</v>
+        <v>1347</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1107</v>
@@ -7397,7 +7881,7 @@
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1311</v>
+        <v>1339</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>141</v>
@@ -7406,7 +7890,7 @@
         <v>142</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1320</v>
+        <v>1348</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>572</v>
@@ -7421,7 +7905,7 @@
         <v>373</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1321</v>
+        <v>1349</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
@@ -7436,7 +7920,7 @@
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>1311</v>
+        <v>1339</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>143</v>
@@ -7445,7 +7929,7 @@
         <v>144</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1322</v>
+        <v>1350</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>576</v>
@@ -7460,7 +7944,7 @@
         <v>373</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1323</v>
+        <v>1351</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
@@ -7475,7 +7959,7 @@
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>1311</v>
+        <v>1339</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>145</v>
@@ -7484,7 +7968,7 @@
         <v>146</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1324</v>
+        <v>1352</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>580</v>
@@ -7499,7 +7983,7 @@
         <v>373</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1325</v>
+        <v>1353</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
@@ -7514,7 +7998,7 @@
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>1311</v>
+        <v>1339</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>147</v>
@@ -7523,7 +8007,7 @@
         <v>148</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1326</v>
+        <v>1354</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>584</v>
@@ -7538,7 +8022,7 @@
         <v>373</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1327</v>
+        <v>1355</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -7553,7 +8037,7 @@
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1328</v>
+        <v>1356</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>149</v>
@@ -7562,7 +8046,7 @@
         <v>150</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1329</v>
+        <v>1357</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>588</v>
@@ -7577,10 +8061,10 @@
         <v>360</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1330</v>
+        <v>1358</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>1331</v>
+        <v>1359</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>1107</v>
@@ -7594,7 +8078,7 @@
     </row>
     <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>1328</v>
+        <v>1356</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>151</v>
@@ -7603,7 +8087,7 @@
         <v>152</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1332</v>
+        <v>1360</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>593</v>
@@ -7618,10 +8102,10 @@
         <v>360</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1333</v>
+        <v>1361</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>1334</v>
+        <v>1362</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>1107</v>
@@ -7635,7 +8119,7 @@
     </row>
     <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>1328</v>
+        <v>1356</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>153</v>
@@ -7644,7 +8128,7 @@
         <v>154</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1335</v>
+        <v>1363</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>599</v>
@@ -7659,10 +8143,10 @@
         <v>360</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1336</v>
+        <v>1364</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>1337</v>
+        <v>1365</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>1107</v>
@@ -7676,7 +8160,7 @@
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>1338</v>
+        <v>1366</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>157</v>
@@ -7685,7 +8169,7 @@
         <v>158</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1339</v>
+        <v>1367</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>601</v>
@@ -7700,7 +8184,7 @@
         <v>373</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1340</v>
+        <v>1368</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
@@ -7715,7 +8199,7 @@
     </row>
     <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>1338</v>
+        <v>1366</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>159</v>
@@ -7724,7 +8208,7 @@
         <v>160</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1341</v>
+        <v>1369</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>605</v>
@@ -7739,10 +8223,10 @@
         <v>360</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1342</v>
+        <v>1370</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>1343</v>
+        <v>1371</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>1107</v>
@@ -7756,7 +8240,7 @@
     </row>
     <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>1338</v>
+        <v>1366</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>161</v>
@@ -7765,7 +8249,7 @@
         <v>162</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1344</v>
+        <v>1372</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>611</v>
@@ -7780,10 +8264,10 @@
         <v>360</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1345</v>
+        <v>1373</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1346</v>
+        <v>1374</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1107</v>
@@ -7797,7 +8281,7 @@
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1347</v>
+        <v>1375</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>163</v>
@@ -7806,7 +8290,7 @@
         <v>164</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1348</v>
+        <v>1376</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>617</v>
@@ -7821,10 +8305,10 @@
         <v>360</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1349</v>
+        <v>1377</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>1350</v>
+        <v>1378</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>1107</v>
@@ -7838,7 +8322,7 @@
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>1347</v>
+        <v>1375</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>165</v>
@@ -7847,7 +8331,7 @@
         <v>166</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1351</v>
+        <v>1379</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>623</v>
@@ -7862,7 +8346,7 @@
         <v>373</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1352</v>
+        <v>1380</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
@@ -7877,7 +8361,7 @@
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1347</v>
+        <v>1375</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>167</v>
@@ -7886,7 +8370,7 @@
         <v>168</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1353</v>
+        <v>1381</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>627</v>
@@ -7901,7 +8385,7 @@
         <v>373</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1354</v>
+        <v>1382</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -7916,7 +8400,7 @@
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>1347</v>
+        <v>1375</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>169</v>
@@ -7925,7 +8409,7 @@
         <v>170</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1355</v>
+        <v>1383</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>631</v>
@@ -7940,7 +8424,7 @@
         <v>373</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1356</v>
+        <v>1384</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -7955,7 +8439,7 @@
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>1347</v>
+        <v>1375</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>171</v>
@@ -7964,7 +8448,7 @@
         <v>172</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1357</v>
+        <v>1385</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>635</v>
@@ -7979,7 +8463,7 @@
         <v>373</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1358</v>
+        <v>1386</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -7994,7 +8478,7 @@
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>1359</v>
+        <v>1387</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>173</v>
@@ -8003,7 +8487,7 @@
         <v>174</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1360</v>
+        <v>1388</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>639</v>
@@ -8018,7 +8502,7 @@
         <v>373</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1361</v>
+        <v>1389</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -8033,7 +8517,7 @@
     </row>
     <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>1359</v>
+        <v>1387</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>175</v>
@@ -8042,7 +8526,7 @@
         <v>176</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1362</v>
+        <v>1390</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>643</v>
@@ -8057,10 +8541,10 @@
         <v>360</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1363</v>
+        <v>1391</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1364</v>
+        <v>1392</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>1107</v>
@@ -8074,7 +8558,7 @@
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>1359</v>
+        <v>1387</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>177</v>
@@ -8083,7 +8567,7 @@
         <v>178</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1365</v>
+        <v>1393</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>650</v>
@@ -8098,10 +8582,10 @@
         <v>360</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1366</v>
+        <v>1394</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1367</v>
+        <v>1395</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1107</v>
@@ -8115,7 +8599,7 @@
     </row>
     <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>1359</v>
+        <v>1387</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>179</v>
@@ -8124,7 +8608,7 @@
         <v>180</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1368</v>
+        <v>1396</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>657</v>
@@ -8139,7 +8623,7 @@
         <v>373</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1369</v>
+        <v>1397</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
@@ -8154,7 +8638,7 @@
     </row>
     <row r="60" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>1370</v>
+        <v>1122</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>181</v>
@@ -8163,7 +8647,7 @@
         <v>182</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1371</v>
+        <v>1398</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>661</v>
@@ -8178,10 +8662,10 @@
         <v>360</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1372</v>
+        <v>1399</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1373</v>
+        <v>1400</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>1107</v>
@@ -8195,7 +8679,7 @@
     </row>
     <row r="61" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>1370</v>
+        <v>1122</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>183</v>
@@ -8204,7 +8688,7 @@
         <v>184</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1374</v>
+        <v>1401</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>667</v>
@@ -8219,7 +8703,7 @@
         <v>373</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1375</v>
+        <v>1402</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
@@ -8234,7 +8718,7 @@
     </row>
     <row r="62" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>1370</v>
+        <v>1122</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>185</v>
@@ -8243,7 +8727,7 @@
         <v>186</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1376</v>
+        <v>1403</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>671</v>
@@ -8258,7 +8742,7 @@
         <v>373</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1377</v>
+        <v>1404</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
@@ -8273,7 +8757,7 @@
     </row>
     <row r="63" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>1370</v>
+        <v>1122</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>187</v>
@@ -8282,7 +8766,7 @@
         <v>188</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1378</v>
+        <v>1405</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>675</v>
@@ -8297,7 +8781,7 @@
         <v>373</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1379</v>
+        <v>1406</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
@@ -8312,7 +8796,7 @@
     </row>
     <row r="64" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>1370</v>
+        <v>1122</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>189</v>
@@ -8321,7 +8805,7 @@
         <v>190</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1380</v>
+        <v>1407</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>679</v>
@@ -8336,7 +8820,7 @@
         <v>373</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1381</v>
+        <v>1408</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
@@ -8351,7 +8835,7 @@
     </row>
     <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>1382</v>
+        <v>1409</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>191</v>
@@ -8360,7 +8844,7 @@
         <v>192</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1383</v>
+        <v>1410</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>683</v>
@@ -8375,10 +8859,10 @@
         <v>360</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1384</v>
+        <v>1411</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>1385</v>
+        <v>1412</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>1107</v>
@@ -8392,7 +8876,7 @@
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>1382</v>
+        <v>1409</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>193</v>
@@ -8401,7 +8885,7 @@
         <v>194</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1386</v>
+        <v>1413</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>688</v>
@@ -8416,10 +8900,10 @@
         <v>360</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1387</v>
+        <v>1414</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1388</v>
+        <v>1415</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1107</v>
@@ -8433,7 +8917,7 @@
     </row>
     <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>1382</v>
+        <v>1409</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>195</v>
@@ -8442,7 +8926,7 @@
         <v>196</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1389</v>
+        <v>1416</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>695</v>
@@ -8457,10 +8941,10 @@
         <v>360</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1390</v>
+        <v>1417</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1391</v>
+        <v>1418</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1107</v>
@@ -8474,7 +8958,7 @@
     </row>
     <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>1382</v>
+        <v>1409</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>197</v>
@@ -8483,7 +8967,7 @@
         <v>198</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1392</v>
+        <v>1419</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>702</v>
@@ -8498,7 +8982,7 @@
         <v>373</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
@@ -8513,7 +8997,7 @@
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>1382</v>
+        <v>1409</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>199</v>
@@ -8522,7 +9006,7 @@
         <v>200</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1394</v>
+        <v>1421</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>706</v>
@@ -8537,7 +9021,7 @@
         <v>373</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1395</v>
+        <v>1422</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
@@ -8552,7 +9036,7 @@
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>1382</v>
+        <v>1409</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>201</v>
@@ -8561,7 +9045,7 @@
         <v>202</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1396</v>
+        <v>1423</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>710</v>
@@ -8576,10 +9060,10 @@
         <v>360</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1397</v>
+        <v>1424</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>1398</v>
+        <v>1425</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>1107</v>
@@ -8593,7 +9077,7 @@
     </row>
     <row r="71" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>203</v>
@@ -8602,7 +9086,7 @@
         <v>204</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1400</v>
+        <v>1427</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>716</v>
@@ -8617,10 +9101,10 @@
         <v>360</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1401</v>
+        <v>1428</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>1402</v>
+        <v>1429</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>1107</v>
@@ -8634,7 +9118,7 @@
     </row>
     <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>203</v>
@@ -8643,7 +9127,7 @@
         <v>204</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1400</v>
+        <v>1427</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>723</v>
@@ -8658,10 +9142,10 @@
         <v>360</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1403</v>
+        <v>1430</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1402</v>
+        <v>1429</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1107</v>
@@ -8675,7 +9159,7 @@
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>205</v>
@@ -8684,7 +9168,7 @@
         <v>206</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1404</v>
+        <v>1431</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>729</v>
@@ -8699,7 +9183,7 @@
         <v>373</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1405</v>
+        <v>1432</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
@@ -8714,7 +9198,7 @@
     </row>
     <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>207</v>
@@ -8723,7 +9207,7 @@
         <v>208</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1406</v>
+        <v>1433</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>733</v>
@@ -8738,10 +9222,10 @@
         <v>360</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1407</v>
+        <v>1434</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1408</v>
+        <v>1435</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>1107</v>
@@ -8755,7 +9239,7 @@
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>207</v>
@@ -8764,7 +9248,7 @@
         <v>208</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1406</v>
+        <v>1433</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>740</v>
@@ -8779,10 +9263,10 @@
         <v>360</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1409</v>
+        <v>1436</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>1408</v>
+        <v>1435</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>1107</v>
@@ -8796,7 +9280,7 @@
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>207</v>
@@ -8805,7 +9289,7 @@
         <v>208</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1406</v>
+        <v>1433</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>746</v>
@@ -8820,10 +9304,10 @@
         <v>360</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>1410</v>
+        <v>1437</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>1408</v>
+        <v>1435</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>1107</v>
@@ -8837,7 +9321,7 @@
     </row>
     <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>209</v>
@@ -8846,7 +9330,7 @@
         <v>210</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1411</v>
+        <v>1438</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>752</v>
@@ -8861,10 +9345,10 @@
         <v>360</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>1412</v>
+        <v>1439</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>1413</v>
+        <v>1440</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>1107</v>
@@ -8878,7 +9362,7 @@
     </row>
     <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>211</v>
@@ -8887,7 +9371,7 @@
         <v>212</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1414</v>
+        <v>1441</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>759</v>
@@ -8902,7 +9386,7 @@
         <v>373</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1415</v>
+        <v>1442</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
@@ -8917,7 +9401,7 @@
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>213</v>
@@ -8926,7 +9410,7 @@
         <v>214</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1416</v>
+        <v>1443</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>763</v>
@@ -8941,7 +9425,7 @@
         <v>373</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1417</v>
+        <v>1444</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -8956,7 +9440,7 @@
     </row>
     <row r="80" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>1418</v>
+        <v>1130</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>215</v>
@@ -8965,7 +9449,7 @@
         <v>216</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1419</v>
+        <v>1445</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>767</v>
@@ -8980,10 +9464,10 @@
         <v>360</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1420</v>
+        <v>1446</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>1421</v>
+        <v>1447</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>1107</v>
@@ -8997,7 +9481,7 @@
     </row>
     <row r="81" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>1418</v>
+        <v>1130</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>217</v>
@@ -9006,7 +9490,7 @@
         <v>218</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1422</v>
+        <v>1448</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>773</v>
@@ -9021,10 +9505,10 @@
         <v>360</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1423</v>
+        <v>1449</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1424</v>
+        <v>1450</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1107</v>
@@ -9038,7 +9522,7 @@
     </row>
     <row r="82" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>1418</v>
+        <v>1130</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>219</v>
@@ -9047,7 +9531,7 @@
         <v>220</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1425</v>
+        <v>1451</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>779</v>
@@ -9062,10 +9546,10 @@
         <v>360</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1426</v>
+        <v>1452</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>1427</v>
+        <v>1453</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>1107</v>
@@ -9079,7 +9563,7 @@
     </row>
     <row r="83" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>1418</v>
+        <v>1130</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>221</v>
@@ -9088,7 +9572,7 @@
         <v>222</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1428</v>
+        <v>1454</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>785</v>
@@ -9103,7 +9587,7 @@
         <v>373</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1429</v>
+        <v>1455</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
@@ -9118,7 +9602,7 @@
     </row>
     <row r="84" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>1418</v>
+        <v>1130</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>223</v>
@@ -9127,7 +9611,7 @@
         <v>224</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1430</v>
+        <v>1456</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>789</v>
@@ -9142,7 +9626,7 @@
         <v>373</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1431</v>
+        <v>1457</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -9157,7 +9641,7 @@
     </row>
     <row r="85" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>1418</v>
+        <v>1130</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>225</v>
@@ -9166,7 +9650,7 @@
         <v>226</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1432</v>
+        <v>1458</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>793</v>
@@ -9181,7 +9665,7 @@
         <v>373</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1433</v>
+        <v>1459</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -9196,7 +9680,7 @@
     </row>
     <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>1434</v>
+        <v>1460</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>227</v>
@@ -9205,7 +9689,7 @@
         <v>228</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1435</v>
+        <v>1461</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>797</v>
@@ -9220,10 +9704,10 @@
         <v>360</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1436</v>
+        <v>1462</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>1437</v>
+        <v>1463</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>1107</v>
@@ -9237,7 +9721,7 @@
     </row>
     <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>1434</v>
+        <v>1460</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>229</v>
@@ -9246,7 +9730,7 @@
         <v>230</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1438</v>
+        <v>1464</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>803</v>
@@ -9261,10 +9745,10 @@
         <v>360</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1439</v>
+        <v>1465</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1440</v>
+        <v>1466</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1107</v>
@@ -9278,7 +9762,7 @@
     </row>
     <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>1434</v>
+        <v>1460</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>231</v>
@@ -9287,7 +9771,7 @@
         <v>232</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1441</v>
+        <v>1467</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>808</v>
@@ -9302,10 +9786,10 @@
         <v>360</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1442</v>
+        <v>1468</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>1443</v>
+        <v>1469</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>1107</v>
@@ -9319,7 +9803,7 @@
     </row>
     <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>1199</v>
+        <v>1229</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>233</v>
@@ -9328,7 +9812,7 @@
         <v>234</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1444</v>
+        <v>1470</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>814</v>
@@ -9343,10 +9827,10 @@
         <v>360</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1445</v>
+        <v>1471</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>1446</v>
+        <v>1472</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>1107</v>
@@ -9360,7 +9844,7 @@
     </row>
     <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>1199</v>
+        <v>1229</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>235</v>
@@ -9369,7 +9853,7 @@
         <v>236</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1447</v>
+        <v>1473</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>820</v>
@@ -9384,10 +9868,10 @@
         <v>360</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1448</v>
+        <v>1474</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>1449</v>
+        <v>1475</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>1107</v>
@@ -9401,7 +9885,7 @@
     </row>
     <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>1199</v>
+        <v>1229</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>239</v>
@@ -9410,7 +9894,7 @@
         <v>240</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>822</v>
@@ -9425,7 +9909,7 @@
         <v>373</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1451</v>
+        <v>1477</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
@@ -9440,7 +9924,7 @@
     </row>
     <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>1199</v>
+        <v>1229</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>241</v>
@@ -9449,7 +9933,7 @@
         <v>242</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1452</v>
+        <v>1478</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>826</v>
@@ -9464,10 +9948,10 @@
         <v>360</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1453</v>
+        <v>1479</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>1454</v>
+        <v>1480</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>1107</v>
@@ -9481,7 +9965,7 @@
     </row>
     <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>1201</v>
+        <v>1142</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>243</v>
@@ -9490,7 +9974,7 @@
         <v>244</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>828</v>
@@ -9505,7 +9989,7 @@
         <v>373</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1456</v>
+        <v>1482</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
@@ -9520,7 +10004,7 @@
     </row>
     <row r="94" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>1201</v>
+        <v>1142</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>245</v>
@@ -9529,7 +10013,7 @@
         <v>246</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1457</v>
+        <v>1483</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>832</v>
@@ -9544,10 +10028,10 @@
         <v>360</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1458</v>
+        <v>1484</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>1459</v>
+        <v>1485</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>1107</v>
@@ -9561,7 +10045,7 @@
     </row>
     <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>1201</v>
+        <v>1142</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>247</v>
@@ -9570,7 +10054,7 @@
         <v>248</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1460</v>
+        <v>1486</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>839</v>
@@ -9585,7 +10069,7 @@
         <v>373</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1461</v>
+        <v>1487</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -9600,7 +10084,7 @@
     </row>
     <row r="96" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>1201</v>
+        <v>1142</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>249</v>
@@ -9609,7 +10093,7 @@
         <v>250</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1462</v>
+        <v>1488</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>843</v>
@@ -9624,7 +10108,7 @@
         <v>373</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1463</v>
+        <v>1489</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -9639,7 +10123,7 @@
     </row>
     <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>1201</v>
+        <v>1142</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>251</v>
@@ -9648,7 +10132,7 @@
         <v>252</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1464</v>
+        <v>1490</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>847</v>
@@ -9663,7 +10147,7 @@
         <v>373</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1465</v>
+        <v>1491</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -9678,7 +10162,7 @@
     </row>
     <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>1203</v>
+        <v>1232</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>253</v>
@@ -9687,7 +10171,7 @@
         <v>254</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1466</v>
+        <v>1492</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>851</v>
@@ -9702,10 +10186,10 @@
         <v>360</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1467</v>
+        <v>1493</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>1468</v>
+        <v>1494</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>1107</v>
@@ -9719,7 +10203,7 @@
     </row>
     <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>1203</v>
+        <v>1232</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>255</v>
@@ -9728,7 +10212,7 @@
         <v>256</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1469</v>
+        <v>1495</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>857</v>
@@ -9743,7 +10227,7 @@
         <v>373</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1470</v>
+        <v>1496</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -9758,7 +10242,7 @@
     </row>
     <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>1203</v>
+        <v>1232</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>257</v>
@@ -9767,7 +10251,7 @@
         <v>258</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1471</v>
+        <v>1497</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>861</v>
@@ -9782,7 +10266,7 @@
         <v>373</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1472</v>
+        <v>1498</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -9797,7 +10281,7 @@
     </row>
     <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>1473</v>
+        <v>1499</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>259</v>
@@ -9806,7 +10290,7 @@
         <v>260</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1474</v>
+        <v>1500</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>865</v>
@@ -9821,7 +10305,7 @@
         <v>373</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1475</v>
+        <v>1501</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -9836,7 +10320,7 @@
     </row>
     <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>1473</v>
+        <v>1499</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>261</v>
@@ -9845,7 +10329,7 @@
         <v>262</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1476</v>
+        <v>1502</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>869</v>
@@ -9860,7 +10344,7 @@
         <v>373</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1477</v>
+        <v>1503</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
@@ -9875,7 +10359,7 @@
     </row>
     <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>1473</v>
+        <v>1499</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>263</v>
@@ -9884,7 +10368,7 @@
         <v>264</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1478</v>
+        <v>1504</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>873</v>
@@ -9899,7 +10383,7 @@
         <v>373</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1479</v>
+        <v>1505</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -9914,7 +10398,7 @@
     </row>
     <row r="104" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>1473</v>
+        <v>1499</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>265</v>
@@ -9923,7 +10407,7 @@
         <v>266</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1480</v>
+        <v>1506</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>877</v>
@@ -9938,10 +10422,10 @@
         <v>360</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1481</v>
+        <v>1507</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>1482</v>
+        <v>1508</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>1107</v>
@@ -9955,7 +10439,7 @@
     </row>
     <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>1473</v>
+        <v>1499</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>267</v>
@@ -9964,7 +10448,7 @@
         <v>268</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1483</v>
+        <v>1509</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>879</v>
@@ -9979,7 +10463,7 @@
         <v>373</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1484</v>
+        <v>1510</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -9994,7 +10478,7 @@
     </row>
     <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>1485</v>
+        <v>1511</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>269</v>
@@ -10003,7 +10487,7 @@
         <v>270</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1486</v>
+        <v>1512</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>883</v>
@@ -10018,10 +10502,10 @@
         <v>360</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1487</v>
+        <v>1513</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1488</v>
+        <v>1514</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1107</v>
@@ -10035,7 +10519,7 @@
     </row>
     <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>1485</v>
+        <v>1511</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>271</v>
@@ -10044,7 +10528,7 @@
         <v>272</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1489</v>
+        <v>1515</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>889</v>
@@ -10059,7 +10543,7 @@
         <v>373</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1490</v>
+        <v>1516</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2" t="s">
@@ -10074,7 +10558,7 @@
     </row>
     <row r="108" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>1485</v>
+        <v>1511</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>275</v>
@@ -10083,7 +10567,7 @@
         <v>276</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1491</v>
+        <v>1517</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>893</v>
@@ -10098,7 +10582,7 @@
         <v>373</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1492</v>
+        <v>1518</v>
       </c>
       <c r="J108" s="2"/>
       <c r="K108" s="2" t="s">
@@ -10113,7 +10597,7 @@
     </row>
     <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>1485</v>
+        <v>1511</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>277</v>
@@ -10122,7 +10606,7 @@
         <v>278</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1493</v>
+        <v>1519</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>897</v>
@@ -10137,7 +10621,7 @@
         <v>373</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1494</v>
+        <v>1520</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
@@ -10152,7 +10636,7 @@
     </row>
     <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>1485</v>
+        <v>1511</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>279</v>
@@ -10161,7 +10645,7 @@
         <v>280</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1495</v>
+        <v>1521</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>901</v>
@@ -10176,7 +10660,7 @@
         <v>373</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1496</v>
+        <v>1522</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2" t="s">
@@ -10191,7 +10675,7 @@
     </row>
     <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>1497</v>
+        <v>1523</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>283</v>
@@ -10200,7 +10684,7 @@
         <v>284</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1498</v>
+        <v>1524</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>905</v>
@@ -10215,7 +10699,7 @@
         <v>373</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1499</v>
+        <v>1525</v>
       </c>
       <c r="J111" s="2"/>
       <c r="K111" s="2" t="s">
@@ -10230,7 +10714,7 @@
     </row>
     <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>1497</v>
+        <v>1523</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>285</v>
@@ -10239,7 +10723,7 @@
         <v>286</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1500</v>
+        <v>1526</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>909</v>
@@ -10254,7 +10738,7 @@
         <v>373</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1501</v>
+        <v>1527</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2" t="s">
@@ -10269,7 +10753,7 @@
     </row>
     <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>1497</v>
+        <v>1523</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>287</v>
@@ -10278,7 +10762,7 @@
         <v>288</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1502</v>
+        <v>1528</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>913</v>
@@ -10293,10 +10777,10 @@
         <v>360</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1503</v>
+        <v>1529</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>1504</v>
+        <v>1530</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>1107</v>
@@ -10310,7 +10794,7 @@
     </row>
     <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>1505</v>
+        <v>1531</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>291</v>
@@ -10319,7 +10803,7 @@
         <v>292</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1506</v>
+        <v>1532</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>918</v>
@@ -10334,7 +10818,7 @@
         <v>373</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1507</v>
+        <v>1533</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
@@ -10349,7 +10833,7 @@
     </row>
     <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>1505</v>
+        <v>1531</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>293</v>
@@ -10358,7 +10842,7 @@
         <v>294</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1508</v>
+        <v>1534</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>922</v>
@@ -10373,7 +10857,7 @@
         <v>373</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2" t="s">
@@ -10388,7 +10872,7 @@
     </row>
     <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>1505</v>
+        <v>1531</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>295</v>
@@ -10397,7 +10881,7 @@
         <v>296</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1510</v>
+        <v>1536</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>926</v>
@@ -10412,7 +10896,7 @@
         <v>373</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1511</v>
+        <v>1537</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
@@ -10427,7 +10911,7 @@
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1187</v>
+        <v>1538</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>297</v>
@@ -10436,7 +10920,7 @@
         <v>298</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1512</v>
+        <v>1539</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>930</v>
@@ -10451,10 +10935,10 @@
         <v>360</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1513</v>
+        <v>1540</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1514</v>
+        <v>1541</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1107</v>
@@ -10468,7 +10952,7 @@
     </row>
     <row r="118" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>1515</v>
+        <v>1122</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>301</v>
@@ -10477,7 +10961,7 @@
         <v>302</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1516</v>
+        <v>1542</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>939</v>
@@ -10492,10 +10976,10 @@
         <v>360</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1517</v>
+        <v>1543</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1518</v>
+        <v>1544</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>1107</v>
@@ -10509,7 +10993,7 @@
     </row>
     <row r="119" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>1515</v>
+        <v>1122</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>301</v>
@@ -10518,7 +11002,7 @@
         <v>302</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1516</v>
+        <v>1542</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>946</v>
@@ -10533,16 +11017,16 @@
         <v>360</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1519</v>
+        <v>1545</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1518</v>
+        <v>1544</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>363</v>
+        <v>1119</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>363</v>
@@ -10550,7 +11034,7 @@
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1193</v>
+        <v>1546</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>303</v>
@@ -10559,7 +11043,7 @@
         <v>304</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1520</v>
+        <v>1547</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>952</v>
@@ -10574,10 +11058,10 @@
         <v>360</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1521</v>
+        <v>1548</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1522</v>
+        <v>1549</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>1107</v>
@@ -10591,7 +11075,7 @@
     </row>
     <row r="121" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>1523</v>
+        <v>1130</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>306</v>
@@ -10600,7 +11084,7 @@
         <v>307</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1524</v>
+        <v>1550</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>959</v>
@@ -10615,10 +11099,10 @@
         <v>360</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1525</v>
+        <v>1551</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1526</v>
+        <v>1552</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>1107</v>
@@ -10632,7 +11116,7 @@
     </row>
     <row r="122" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>1523</v>
+        <v>1130</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>306</v>
@@ -10641,7 +11125,7 @@
         <v>307</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1524</v>
+        <v>1550</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>965</v>
@@ -10656,16 +11140,16 @@
         <v>360</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1527</v>
+        <v>1553</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1526</v>
+        <v>1552</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>363</v>
+        <v>1128</v>
       </c>
       <c r="M122" s="2" t="s">
         <v>363</v>
@@ -10673,7 +11157,7 @@
     </row>
     <row r="123" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>1523</v>
+        <v>1130</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>306</v>
@@ -10682,7 +11166,7 @@
         <v>307</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1524</v>
+        <v>1550</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>969</v>
@@ -10697,10 +11181,10 @@
         <v>360</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1528</v>
+        <v>1554</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>1526</v>
+        <v>1552</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>1107</v>
@@ -10714,7 +11198,7 @@
     </row>
     <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>1121</v>
+        <v>1555</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>308</v>
@@ -10723,7 +11207,7 @@
         <v>309</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1529</v>
+        <v>1556</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>974</v>
@@ -10738,10 +11222,10 @@
         <v>360</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1530</v>
+        <v>1557</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1531</v>
+        <v>1558</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>1107</v>
@@ -10755,7 +11239,7 @@
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>1121</v>
+        <v>1555</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>308</v>
@@ -10764,7 +11248,7 @@
         <v>309</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1529</v>
+        <v>1556</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>982</v>
@@ -10779,10 +11263,10 @@
         <v>360</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1532</v>
+        <v>1559</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1531</v>
+        <v>1558</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1107</v>
@@ -10796,7 +11280,7 @@
     </row>
     <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>1121</v>
+        <v>1555</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>308</v>
@@ -10805,7 +11289,7 @@
         <v>309</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1529</v>
+        <v>1556</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>988</v>
@@ -10820,10 +11304,10 @@
         <v>360</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>1533</v>
+        <v>1560</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>1531</v>
+        <v>1558</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1107</v>
@@ -10837,7 +11321,7 @@
     </row>
     <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>1121</v>
+        <v>1555</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>308</v>
@@ -10846,7 +11330,7 @@
         <v>309</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1529</v>
+        <v>1556</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>994</v>
@@ -10861,16 +11345,16 @@
         <v>360</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1534</v>
+        <v>1561</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1531</v>
+        <v>1558</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>1110</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>1119</v>
+        <v>1135</v>
       </c>
       <c r="M127" s="2" t="s">
         <v>363</v>
@@ -10878,7 +11362,7 @@
     </row>
     <row r="128" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>1535</v>
+        <v>1151</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>311</v>
@@ -10887,7 +11371,7 @@
         <v>312</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1536</v>
+        <v>1562</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>1000</v>
@@ -10902,10 +11386,10 @@
         <v>360</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1537</v>
+        <v>1563</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1538</v>
+        <v>1564</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1107</v>
@@ -10919,7 +11403,7 @@
     </row>
     <row r="129" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>1535</v>
+        <v>1151</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>311</v>
@@ -10928,7 +11412,7 @@
         <v>312</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1536</v>
+        <v>1562</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>1006</v>
@@ -10943,10 +11427,10 @@
         <v>360</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1539</v>
+        <v>1565</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1538</v>
+        <v>1564</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1107</v>
@@ -10960,7 +11444,7 @@
     </row>
     <row r="130" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>1535</v>
+        <v>1151</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>311</v>
@@ -10969,7 +11453,7 @@
         <v>312</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1536</v>
+        <v>1562</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>1012</v>
@@ -10984,10 +11468,10 @@
         <v>360</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>1540</v>
+        <v>1566</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>1538</v>
+        <v>1564</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1107</v>
@@ -11001,7 +11485,7 @@
     </row>
     <row r="131" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>1535</v>
+        <v>1151</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>311</v>
@@ -11010,7 +11494,7 @@
         <v>312</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1536</v>
+        <v>1562</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>1018</v>
@@ -11025,10 +11509,10 @@
         <v>360</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1541</v>
+        <v>1567</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1538</v>
+        <v>1564</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>1107</v>
@@ -11042,7 +11526,7 @@
     </row>
     <row r="132" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>1535</v>
+        <v>1151</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>313</v>
@@ -11051,7 +11535,7 @@
         <v>314</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1542</v>
+        <v>1568</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>1024</v>
@@ -11066,10 +11550,10 @@
         <v>360</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1543</v>
+        <v>1569</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1544</v>
+        <v>1570</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1107</v>
@@ -11083,7 +11567,7 @@
     </row>
     <row r="133" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>1535</v>
+        <v>1151</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>313</v>
@@ -11092,7 +11576,7 @@
         <v>314</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1542</v>
+        <v>1568</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>1030</v>
@@ -11107,10 +11591,10 @@
         <v>360</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1545</v>
+        <v>1571</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1544</v>
+        <v>1570</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1107</v>
@@ -11124,7 +11608,7 @@
     </row>
     <row r="134" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>315</v>
@@ -11133,7 +11617,7 @@
         <v>316</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1546</v>
+        <v>1572</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>1036</v>
@@ -11148,7 +11632,7 @@
         <v>373</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>1547</v>
+        <v>1573</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2" t="s">
@@ -11163,7 +11647,7 @@
     </row>
     <row r="135" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>318</v>
@@ -11172,7 +11656,7 @@
         <v>319</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1548</v>
+        <v>1574</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>1041</v>
@@ -11187,7 +11671,7 @@
         <v>373</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>1549</v>
+        <v>1575</v>
       </c>
       <c r="J135" s="2"/>
       <c r="K135" s="2" t="s">
@@ -11202,7 +11686,7 @@
     </row>
     <row r="136" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>1195</v>
+        <v>1225</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>320</v>
@@ -11211,7 +11695,7 @@
         <v>321</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1550</v>
+        <v>1576</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>1045</v>
@@ -11226,10 +11710,10 @@
         <v>360</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>1551</v>
+        <v>1577</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1552</v>
+        <v>1578</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1107</v>
@@ -11243,7 +11727,7 @@
     </row>
     <row r="137" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>1195</v>
+        <v>1225</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>320</v>
@@ -11252,7 +11736,7 @@
         <v>321</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1550</v>
+        <v>1576</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>1051</v>
@@ -11267,10 +11751,10 @@
         <v>360</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1553</v>
+        <v>1579</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>1552</v>
+        <v>1578</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>1107</v>
@@ -11284,7 +11768,7 @@
     </row>
     <row r="138" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>1195</v>
+        <v>1225</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>322</v>
@@ -11293,7 +11777,7 @@
         <v>323</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1554</v>
+        <v>1580</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>1057</v>
@@ -11308,10 +11792,10 @@
         <v>360</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>1555</v>
+        <v>1581</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>1556</v>
+        <v>1582</v>
       </c>
       <c r="K138" s="2" t="s">
         <v>1107</v>
@@ -11325,7 +11809,7 @@
     </row>
     <row r="139" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>1195</v>
+        <v>1225</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>324</v>
@@ -11334,7 +11818,7 @@
         <v>325</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1557</v>
+        <v>1583</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>1063</v>
@@ -11349,10 +11833,10 @@
         <v>360</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>1558</v>
+        <v>1584</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>1559</v>
+        <v>1585</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>1107</v>
@@ -11366,7 +11850,7 @@
     </row>
     <row r="140" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>1199</v>
+        <v>1229</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>326</v>
@@ -11375,7 +11859,7 @@
         <v>327</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1560</v>
+        <v>1586</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>1069</v>
@@ -11390,10 +11874,10 @@
         <v>360</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>1561</v>
+        <v>1587</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>1107</v>
@@ -11407,7 +11891,7 @@
     </row>
     <row r="141" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>1199</v>
+        <v>1229</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>326</v>
@@ -11416,7 +11900,7 @@
         <v>327</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1560</v>
+        <v>1586</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>1075</v>
@@ -11431,10 +11915,10 @@
         <v>360</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>1563</v>
+        <v>1589</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>1107</v>
@@ -11448,7 +11932,7 @@
     </row>
     <row r="142" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>1201</v>
+        <v>1142</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>328</v>
@@ -11457,7 +11941,7 @@
         <v>329</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1564</v>
+        <v>1590</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>1080</v>
@@ -11472,16 +11956,16 @@
         <v>360</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>1565</v>
+        <v>1591</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>1566</v>
+        <v>1592</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>363</v>
+        <v>1140</v>
       </c>
       <c r="M142" s="2" t="s">
         <v>363</v>
@@ -11489,7 +11973,7 @@
     </row>
     <row r="143" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>1205</v>
+        <v>1234</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>330</v>
@@ -11498,7 +11982,7 @@
         <v>331</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1567</v>
+        <v>1593</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>1086</v>
@@ -11513,10 +11997,10 @@
         <v>360</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>1568</v>
+        <v>1594</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>1569</v>
+        <v>1595</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>1107</v>
@@ -11530,7 +12014,7 @@
     </row>
     <row r="144" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>1205</v>
+        <v>1234</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>332</v>
@@ -11539,7 +12023,7 @@
         <v>333</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1570</v>
+        <v>1596</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>1092</v>
@@ -11554,10 +12038,10 @@
         <v>360</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>1571</v>
+        <v>1597</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>1572</v>
+        <v>1598</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>1107</v>
@@ -11571,7 +12055,7 @@
     </row>
     <row r="145" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>1205</v>
+        <v>1234</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>334</v>
@@ -11580,7 +12064,7 @@
         <v>335</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1573</v>
+        <v>1599</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>1099</v>
@@ -11595,7 +12079,7 @@
         <v>373</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>1574</v>
+        <v>1600</v>
       </c>
       <c r="J145" s="2"/>
       <c r="K145" s="2" t="s">
@@ -11614,7 +12098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -11628,53 +12112,53 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1575</v>
+        <v>1601</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1576</v>
+        <v>1602</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1577</v>
+        <v>1603</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1578</v>
+        <v>1604</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1579</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1580</v>
+        <v>1606</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1581</v>
+        <v>1607</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1582</v>
+        <v>1608</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1583</v>
+        <v>1609</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1584</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1585</v>
+        <v>1611</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1581</v>
+        <v>1607</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1586</v>
+        <v>1612</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1587</v>
+        <v>1613</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1588</v>
+        <v>1614</v>
       </c>
     </row>
   </sheetData>
@@ -11683,7 +12167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -11697,189 +12181,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1589</v>
+        <v>1615</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>337</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1134</v>
+        <v>1164</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1590</v>
+        <v>1616</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1591</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1592</v>
+        <v>1618</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1593</v>
+        <v>1619</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1594</v>
+        <v>1620</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1595</v>
+        <v>1621</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1596</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1597</v>
+        <v>1623</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1598</v>
+        <v>1624</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1599</v>
+        <v>1625</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1600</v>
+        <v>1626</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1601</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1602</v>
+        <v>1628</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1603</v>
+        <v>1629</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1604</v>
+        <v>1630</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1605</v>
+        <v>1631</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1606</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1607</v>
+        <v>1633</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1608</v>
+        <v>1634</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1609</v>
+        <v>1635</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1610</v>
+        <v>1636</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1611</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1612</v>
+        <v>1638</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1613</v>
+        <v>1639</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1614</v>
+        <v>1640</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1615</v>
+        <v>1641</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1616</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1617</v>
+        <v>1643</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1618</v>
+        <v>1644</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1619</v>
+        <v>1645</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1620</v>
+        <v>1646</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1621</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1622</v>
+        <v>1648</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1623</v>
+        <v>1649</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1625</v>
+        <v>1651</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1626</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1627</v>
+        <v>1653</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1628</v>
+        <v>1654</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1629</v>
+        <v>1655</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1630</v>
+        <v>1656</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1631</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1632</v>
+        <v>1658</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1633</v>
+        <v>1659</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1634</v>
+        <v>1660</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1635</v>
+        <v>1661</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1636</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1637</v>
+        <v>1663</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1638</v>
+        <v>1664</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1639</v>
+        <v>1665</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1640</v>
+        <v>1666</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1641</v>
+        <v>1667</v>
       </c>
     </row>
   </sheetData>
@@ -11888,7 +12372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -11902,203 +12386,203 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1642</v>
+        <v>1668</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1643</v>
+        <v>1669</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1644</v>
+        <v>1670</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1645</v>
+        <v>1671</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1646</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1647</v>
+        <v>1673</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1648</v>
+        <v>1674</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1650</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1617</v>
+        <v>1643</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1651</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1652</v>
+        <v>1678</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1607</v>
+        <v>1633</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1653</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1654</v>
+        <v>1680</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1637</v>
+        <v>1663</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1655</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1656</v>
+        <v>1682</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1657</v>
+        <v>1683</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1658</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1659</v>
+        <v>1685</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1660</v>
+        <v>1686</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1661</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1662</v>
+        <v>1688</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1663</v>
+        <v>1689</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1664</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1665</v>
+        <v>1691</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1666</v>
+        <v>1692</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1667</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1668</v>
+        <v>1694</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1669</v>
+        <v>1695</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1670</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1671</v>
+        <v>1697</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1672</v>
+        <v>1698</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1673</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1674</v>
+        <v>1700</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>1675</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>1649</v>
-      </c>
       <c r="D12" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1676</v>
+        <v>1702</v>
       </c>
     </row>
   </sheetData>
@@ -21595,7 +22079,7 @@
         <v>1107</v>
       </c>
       <c r="E2" s="2">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -21713,7 +22197,7 @@
         <v>1107</v>
       </c>
       <c r="E8" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -21731,7 +22215,7 @@
         <v>1107</v>
       </c>
       <c r="E9" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -21749,7 +22233,7 @@
         <v>1107</v>
       </c>
       <c r="E10" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -21785,7 +22269,7 @@
         <v>1107</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -21881,7 +22365,7 @@
         <v>1107</v>
       </c>
       <c r="E17" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -21899,7 +22383,7 @@
         <v>1107</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -21957,7 +22441,7 @@
         <v>1107</v>
       </c>
       <c r="E21" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -21995,7 +22479,7 @@
         <v>1107</v>
       </c>
       <c r="E23" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -22013,7 +22497,7 @@
         <v>1107</v>
       </c>
       <c r="E24" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -22031,7 +22515,7 @@
         <v>1107</v>
       </c>
       <c r="E25" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -22049,7 +22533,7 @@
         <v>1107</v>
       </c>
       <c r="E26" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -22085,7 +22569,7 @@
         <v>1107</v>
       </c>
       <c r="E28" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -22103,7 +22587,7 @@
         <v>1107</v>
       </c>
       <c r="E29" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -22121,7 +22605,7 @@
         <v>1107</v>
       </c>
       <c r="E30" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -22139,7 +22623,7 @@
         <v>1107</v>
       </c>
       <c r="E31" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -22177,7 +22661,7 @@
         <v>1107</v>
       </c>
       <c r="E33" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -22195,7 +22679,7 @@
         <v>1107</v>
       </c>
       <c r="E34" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -22253,7 +22737,7 @@
         <v>1107</v>
       </c>
       <c r="E37" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -22291,7 +22775,7 @@
         <v>1107</v>
       </c>
       <c r="E39" s="2">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -22309,7 +22793,7 @@
         <v>1107</v>
       </c>
       <c r="E40" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -22407,7 +22891,7 @@
         <v>1107</v>
       </c>
       <c r="E45" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -22425,7 +22909,7 @@
         <v>1107</v>
       </c>
       <c r="E46" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -22443,7 +22927,7 @@
         <v>1107</v>
       </c>
       <c r="E47" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -22481,7 +22965,7 @@
         <v>1107</v>
       </c>
       <c r="E49" s="2">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -22499,7 +22983,7 @@
         <v>1107</v>
       </c>
       <c r="E50" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -22517,7 +23001,7 @@
         <v>1107</v>
       </c>
       <c r="E51" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -22635,7 +23119,7 @@
         <v>1107</v>
       </c>
       <c r="E57" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -22653,7 +23137,7 @@
         <v>1107</v>
       </c>
       <c r="E58" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -22691,7 +23175,7 @@
         <v>1107</v>
       </c>
       <c r="E60" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -22789,7 +23273,7 @@
         <v>1107</v>
       </c>
       <c r="E65" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -22807,7 +23291,7 @@
         <v>1107</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -22825,7 +23309,7 @@
         <v>1107</v>
       </c>
       <c r="E67" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -22883,7 +23367,7 @@
         <v>1107</v>
       </c>
       <c r="E70" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -22901,7 +23385,7 @@
         <v>1107</v>
       </c>
       <c r="E71" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -22919,7 +23403,7 @@
         <v>1107</v>
       </c>
       <c r="E72" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -22957,7 +23441,7 @@
         <v>1107</v>
       </c>
       <c r="E74" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -22975,7 +23459,7 @@
         <v>1107</v>
       </c>
       <c r="E75" s="2">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -22993,7 +23477,7 @@
         <v>1107</v>
       </c>
       <c r="E76" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -23011,7 +23495,7 @@
         <v>1107</v>
       </c>
       <c r="E77" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -23069,7 +23553,7 @@
         <v>1107</v>
       </c>
       <c r="E80" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -23087,7 +23571,7 @@
         <v>1107</v>
       </c>
       <c r="E81" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -23105,7 +23589,7 @@
         <v>1107</v>
       </c>
       <c r="E82" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -23183,7 +23667,7 @@
         <v>1107</v>
       </c>
       <c r="E86" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -23201,7 +23685,7 @@
         <v>1107</v>
       </c>
       <c r="E87" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -23219,7 +23703,7 @@
         <v>1107</v>
       </c>
       <c r="E88" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -23255,7 +23739,7 @@
         <v>1107</v>
       </c>
       <c r="E90" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -23293,7 +23777,7 @@
         <v>1107</v>
       </c>
       <c r="E92" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -23331,7 +23815,7 @@
         <v>1107</v>
       </c>
       <c r="E94" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -23409,7 +23893,7 @@
         <v>1107</v>
       </c>
       <c r="E98" s="2">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -23527,7 +24011,7 @@
         <v>1107</v>
       </c>
       <c r="E104" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -23565,7 +24049,7 @@
         <v>1107</v>
       </c>
       <c r="E106" s="2">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -23703,7 +24187,7 @@
         <v>1107</v>
       </c>
       <c r="E113" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -23781,7 +24265,7 @@
         <v>1107</v>
       </c>
       <c r="E117" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -23799,7 +24283,7 @@
         <v>1107</v>
       </c>
       <c r="E118" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -23814,10 +24298,10 @@
         <v>947</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="E119" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -23835,7 +24319,7 @@
         <v>1107</v>
       </c>
       <c r="E120" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -23853,7 +24337,7 @@
         <v>1107</v>
       </c>
       <c r="E121" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -23868,10 +24352,10 @@
         <v>966</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="E122" s="2">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -23889,7 +24373,7 @@
         <v>1107</v>
       </c>
       <c r="E123" s="2">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -23907,7 +24391,7 @@
         <v>1107</v>
       </c>
       <c r="E124" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -23925,7 +24409,7 @@
         <v>1107</v>
       </c>
       <c r="E125" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -23943,7 +24427,7 @@
         <v>1107</v>
       </c>
       <c r="E126" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -23961,7 +24445,7 @@
         <v>1110</v>
       </c>
       <c r="E127" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -23979,7 +24463,7 @@
         <v>1107</v>
       </c>
       <c r="E128" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -23997,7 +24481,7 @@
         <v>1107</v>
       </c>
       <c r="E129" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -24015,7 +24499,7 @@
         <v>1107</v>
       </c>
       <c r="E130" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -24033,7 +24517,7 @@
         <v>1107</v>
       </c>
       <c r="E131" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -24051,7 +24535,7 @@
         <v>1107</v>
       </c>
       <c r="E132" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -24069,7 +24553,7 @@
         <v>1107</v>
       </c>
       <c r="E133" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -24127,7 +24611,7 @@
         <v>1107</v>
       </c>
       <c r="E136" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -24145,7 +24629,7 @@
         <v>1107</v>
       </c>
       <c r="E137" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -24181,7 +24665,7 @@
         <v>1107</v>
       </c>
       <c r="E139" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F139" s="2"/>
     </row>
@@ -24199,7 +24683,7 @@
         <v>1107</v>
       </c>
       <c r="E140" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F140" s="2"/>
     </row>
@@ -24217,7 +24701,7 @@
         <v>1107</v>
       </c>
       <c r="E141" s="2">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F141" s="2"/>
     </row>
@@ -24232,10 +24716,10 @@
         <v>1081</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="E142" s="2">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="F142" s="2"/>
     </row>
@@ -24253,7 +24737,7 @@
         <v>1107</v>
       </c>
       <c r="E143" s="2">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="F143" s="2"/>
     </row>
@@ -24271,7 +24755,7 @@
         <v>1107</v>
       </c>
       <c r="E144" s="2">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F144" s="2"/>
     </row>
@@ -24303,7 +24787,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -24359,30 +24843,135 @@
         <v>1120</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>317</v>
       </c>
     </row>
@@ -24393,6 +24982,82 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="11" customWidth="1"/>
+    <col min="9" max="9" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G139"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -24410,16 +25075,16 @@
         <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1126</v>
+        <v>1156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1127</v>
+        <v>1157</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>360</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1128</v>
+        <v>1158</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -24448,7 +25113,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24471,7 +25136,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24494,7 +25159,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24517,7 +25182,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24540,7 +25205,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24563,7 +25228,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24586,7 +25251,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24609,7 +25274,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24632,7 +25297,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24655,7 +25320,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24678,7 +25343,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24701,7 +25366,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24724,7 +25389,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24747,7 +25412,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24770,7 +25435,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24793,7 +25458,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24816,7 +25481,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24839,7 +25504,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24862,7 +25527,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24885,7 +25550,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24908,7 +25573,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24931,7 +25596,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24954,7 +25619,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24977,7 +25642,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25000,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25023,7 +25688,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25046,7 +25711,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25069,7 +25734,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25092,7 +25757,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25115,7 +25780,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25138,7 +25803,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25161,7 +25826,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25184,7 +25849,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25207,7 +25872,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25230,7 +25895,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25253,7 +25918,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25276,7 +25941,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25299,7 +25964,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25322,7 +25987,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25345,7 +26010,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25368,7 +26033,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25391,7 +26056,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25414,7 +26079,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25437,7 +26102,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25460,7 +26125,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25483,7 +26148,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25506,7 +26171,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25529,7 +26194,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25552,7 +26217,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25575,7 +26240,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25598,7 +26263,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25621,7 +26286,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25644,7 +26309,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25667,7 +26332,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25690,7 +26355,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25713,7 +26378,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25736,7 +26401,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25759,7 +26424,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25782,7 +26447,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25805,7 +26470,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25828,7 +26493,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25851,7 +26516,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25874,7 +26539,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25897,7 +26562,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25920,7 +26585,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25943,7 +26608,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25966,7 +26631,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25989,7 +26654,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26012,7 +26677,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26035,7 +26700,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26058,7 +26723,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26081,7 +26746,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26104,7 +26769,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26127,7 +26792,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26150,7 +26815,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26173,7 +26838,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26196,7 +26861,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26219,7 +26884,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26242,7 +26907,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26265,7 +26930,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26288,7 +26953,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26311,7 +26976,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26334,7 +26999,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26357,7 +27022,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26380,7 +27045,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26403,7 +27068,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26426,7 +27091,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26449,7 +27114,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26472,7 +27137,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26495,7 +27160,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26518,7 +27183,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26541,7 +27206,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26564,7 +27229,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26587,7 +27252,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26610,7 +27275,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26633,7 +27298,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26656,7 +27321,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26679,7 +27344,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26702,7 +27367,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26725,7 +27390,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26748,7 +27413,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26771,7 +27436,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26794,7 +27459,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26817,7 +27482,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26840,7 +27505,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26863,7 +27528,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26886,7 +27551,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26909,7 +27574,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26932,7 +27597,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26955,7 +27620,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26978,7 +27643,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27001,7 +27666,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27024,7 +27689,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27047,7 +27712,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27070,7 +27735,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27093,7 +27758,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27116,7 +27781,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27139,7 +27804,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1129</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27162,7 +27827,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27185,7 +27850,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27208,7 +27873,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27231,7 +27896,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27251,10 +27916,10 @@
         <v>2</v>
       </c>
       <c r="F124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1130</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27277,7 +27942,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27297,10 +27962,10 @@
         <v>3</v>
       </c>
       <c r="F126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1130</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27323,7 +27988,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1132</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27346,7 +28011,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27369,7 +28034,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27392,7 +28057,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27415,7 +28080,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27438,7 +28103,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="133" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27461,7 +28126,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="134" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27484,7 +28149,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="135" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27507,7 +28172,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="136" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27527,10 +28192,10 @@
         <v>1</v>
       </c>
       <c r="F136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1130</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="137" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27553,7 +28218,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="138" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27576,7 +28241,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="139" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27599,7 +28264,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1131</v>
+        <v>1161</v>
       </c>
     </row>
   </sheetData>
@@ -27608,7 +28273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -27621,13 +28286,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1133</v>
+        <v>1163</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1134</v>
+        <v>1164</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1135</v>
+        <v>1165</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -27635,616 +28300,211 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1136</v>
+        <v>1166</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1137</v>
+        <v>1167</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1138</v>
+        <v>1168</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1139</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1140</v>
+        <v>1170</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1141</v>
+        <v>1171</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1142</v>
+        <v>1172</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1146</v>
+        <v>1176</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1139</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1147</v>
+        <v>1177</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1148</v>
+        <v>1178</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1149</v>
+        <v>1179</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1151</v>
+        <v>1181</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1152</v>
+        <v>1182</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1153</v>
+        <v>1183</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1154</v>
+        <v>1184</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1012</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1155</v>
+        <v>1185</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1156</v>
+        <v>1186</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1157</v>
+        <v>1187</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1158</v>
+        <v>1188</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1159</v>
+        <v>1189</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>363</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1160</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1161</v>
+        <v>1191</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1162</v>
+        <v>1192</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1163</v>
+        <v>1193</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1143</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1164</v>
+        <v>1194</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1165</v>
+        <v>1195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1166</v>
+        <v>1196</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1167</v>
+        <v>1197</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1168</v>
+        <v>1198</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>643</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>1169</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1172</v>
+        <v>1202</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>1173</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1176</v>
+        <v>1206</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>695</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1143</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1177</v>
+        <v>1207</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1178</v>
+        <v>1208</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>363</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1189</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2">
-        <v>3</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2">
-        <v>4</v>
-      </c>
-      <c r="H6" s="2">
-        <v>4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1198</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2">
-        <v>4</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1200</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5</v>
-      </c>
-      <c r="H8" s="2">
-        <v>5</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="E9" s="2">
-        <v>6</v>
-      </c>
-      <c r="F9" s="2">
-        <v>6</v>
-      </c>
-      <c r="G9" s="2">
-        <v>2</v>
-      </c>
-      <c r="H9" s="2">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1204</v>
-      </c>
-      <c r="E10" s="2">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2">
-        <v>3</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E11" s="2">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2">
-        <v>3</v>
-      </c>
-      <c r="G11" s="2">
-        <v>2</v>
-      </c>
-      <c r="H11" s="2">
-        <v>2</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K11" s="2" t="s">
         <v>1190</v>
       </c>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6007" uniqueCount="1703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6207" uniqueCount="1740">
   <si>
     <t>Metric</t>
   </si>
@@ -213,7 +213,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-02T20:05:18.310Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-02T20:26:22.186Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3778,6 +3778,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>Scope</t>
+  </si>
+  <si>
     <t>Parent</t>
   </si>
   <si>
@@ -3790,6 +3793,9 @@
     <t>epic</t>
   </si>
   <si>
+    <t>this cycle</t>
+  </si>
+  <si>
     <t>[Epic 8] Release 2.0 – Booking Rule Changes and Free Cancellation</t>
   </si>
   <si>
@@ -3853,6 +3859,165 @@
     <t>8.4 Send a cancellation e-mail</t>
   </si>
   <si>
+    <t>AQPI-1</t>
+  </si>
+  <si>
+    <t>initiative</t>
+  </si>
+  <si>
+    <t>baseline</t>
+  </si>
+  <si>
+    <t>[Initiative] Intelligent Hotel Shopping and Reservation Experience</t>
+  </si>
+  <si>
+    <t>AQPI-2</t>
+  </si>
+  <si>
+    <t>[Epic 1] Search and Availability</t>
+  </si>
+  <si>
+    <t>AQPI-3</t>
+  </si>
+  <si>
+    <t>3.1 Search hotels by destination and date range</t>
+  </si>
+  <si>
+    <t>3.2 Validate occupancy and stay criteria</t>
+  </si>
+  <si>
+    <t>AQPI-5</t>
+  </si>
+  <si>
+    <t>3.3 Handle unavailable or failed searches</t>
+  </si>
+  <si>
+    <t>AQPI-6</t>
+  </si>
+  <si>
+    <t>[Epic 2] Hotel Results and Selection</t>
+  </si>
+  <si>
+    <t>AQPI-7</t>
+  </si>
+  <si>
+    <t>4.1 Display available hotels</t>
+  </si>
+  <si>
+    <t>AQPI-8</t>
+  </si>
+  <si>
+    <t>4.2 Sort and filter hotel results</t>
+  </si>
+  <si>
+    <t>AQPI-9</t>
+  </si>
+  <si>
+    <t>4.3 View hotel and room details</t>
+  </si>
+  <si>
+    <t>AQPI-10</t>
+  </si>
+  <si>
+    <t>[Epic 3] Personalized Ancillary Offers</t>
+  </si>
+  <si>
+    <t>AQPI-11</t>
+  </si>
+  <si>
+    <t>5.1 Determine eligible ancillary offers</t>
+  </si>
+  <si>
+    <t>AQPI-12</t>
+  </si>
+  <si>
+    <t>5.2 Display ancillary offers</t>
+  </si>
+  <si>
+    <t>AQPI-13</t>
+  </si>
+  <si>
+    <t>5.3 Explain and control personalization</t>
+  </si>
+  <si>
+    <t>AQPI-14</t>
+  </si>
+  <si>
+    <t>[Epic 4] Cart Management</t>
+  </si>
+  <si>
+    <t>AQPI-15</t>
+  </si>
+  <si>
+    <t>6.1 Add room selection to cart</t>
+  </si>
+  <si>
+    <t>AQPI-16</t>
+  </si>
+  <si>
+    <t>6.2 Add, update, and remove ancillaries</t>
+  </si>
+  <si>
+    <t>6.3 Review cart and total price</t>
+  </si>
+  <si>
+    <t>AQPI-18</t>
+  </si>
+  <si>
+    <t>[Epic 5] Checkout and Reservation</t>
+  </si>
+  <si>
+    <t>AQPI-19</t>
+  </si>
+  <si>
+    <t>7.1 Capture guest and contact information</t>
+  </si>
+  <si>
+    <t>AQPI-20</t>
+  </si>
+  <si>
+    <t>7.2 Capture and authorize payment</t>
+  </si>
+  <si>
+    <t>7.3 Create reservation idempotently</t>
+  </si>
+  <si>
+    <t>AQPI-22</t>
+  </si>
+  <si>
+    <t>7.4 Show booking outcome</t>
+  </si>
+  <si>
+    <t>AQPI-27</t>
+  </si>
+  <si>
+    <t>[Epic 7] Cross-Cutting Quality, Privacy and Observability</t>
+  </si>
+  <si>
+    <t>AQPI-28</t>
+  </si>
+  <si>
+    <t>9.1 Protect sensitive data</t>
+  </si>
+  <si>
+    <t>AQPI-29</t>
+  </si>
+  <si>
+    <t>9.2 Provide end-to-end observability</t>
+  </si>
+  <si>
+    <t>AQPI-30</t>
+  </si>
+  <si>
+    <t>9.3 Meet accessibility requirements</t>
+  </si>
+  <si>
+    <t>AQPI-31</t>
+  </si>
+  <si>
+    <t>9.4 Meet performance and reliability objectives</t>
+  </si>
+  <si>
     <t>Jira</t>
   </si>
   <si>
@@ -3877,9 +4042,6 @@
     <t>Defect</t>
   </si>
   <si>
-    <t>AQPI-1</t>
-  </si>
-  <si>
     <t>BR-003</t>
   </si>
   <si>
@@ -3922,9 +4084,6 @@
     <t>TD-F-006</t>
   </si>
   <si>
-    <t>AQPI-3</t>
-  </si>
-  <si>
     <t>BR-013</t>
   </si>
   <si>
@@ -4015,9 +4174,6 @@
     <t>TD-F-018</t>
   </si>
   <si>
-    <t>AQPI-5</t>
-  </si>
-  <si>
     <t>BR-025</t>
   </si>
   <si>
@@ -4042,9 +4198,6 @@
     <t>br-027-search-session.spec.js</t>
   </si>
   <si>
-    <t>AQPI-7</t>
-  </si>
-  <si>
     <t>BR-028</t>
   </si>
   <si>
@@ -4090,9 +4243,6 @@
     <t>br-032-starting-price.spec.js</t>
   </si>
   <si>
-    <t>AQPI-8</t>
-  </si>
-  <si>
     <t>BR-033</t>
   </si>
   <si>
@@ -4129,9 +4279,6 @@
     <t>br-036-filter-reset.spec.js</t>
   </si>
   <si>
-    <t>AQPI-9</t>
-  </si>
-  <si>
     <t>BR-037</t>
   </si>
   <si>
@@ -4162,9 +4309,6 @@
     <t>br-040-rate-conditions.spec.js</t>
   </si>
   <si>
-    <t>AQPI-11</t>
-  </si>
-  <si>
     <t>BR-041</t>
   </si>
   <si>
@@ -4213,9 +4357,6 @@
     <t>TD-F-041</t>
   </si>
   <si>
-    <t>AQPI-12</t>
-  </si>
-  <si>
     <t>BR-048</t>
   </si>
   <si>
@@ -4243,9 +4384,6 @@
     <t>br-050-offer-content.spec.js</t>
   </si>
   <si>
-    <t>AQPI-13</t>
-  </si>
-  <si>
     <t>BR-052</t>
   </si>
   <si>
@@ -4270,9 +4408,6 @@
     <t>br-054-consent-personalization.spec.js</t>
   </si>
   <si>
-    <t>AQPI-15</t>
-  </si>
-  <si>
     <t>BR-055</t>
   </si>
   <si>
@@ -4306,9 +4441,6 @@
     <t>TD-F-052</t>
   </si>
   <si>
-    <t>AQPI-16</t>
-  </si>
-  <si>
     <t>BR-060</t>
   </si>
   <si>
@@ -4372,9 +4504,6 @@
     <t>TD-F-061</t>
   </si>
   <si>
-    <t>AQPI-19</t>
-  </si>
-  <si>
     <t>BR-069</t>
   </si>
   <si>
@@ -4423,9 +4552,6 @@
     <t>br-074-support-masking.spec.js</t>
   </si>
   <si>
-    <t>AQPI-20</t>
-  </si>
-  <si>
     <t>BR-075</t>
   </si>
   <si>
@@ -4525,9 +4651,6 @@
     <t>TD-F-081</t>
   </si>
   <si>
-    <t>AQPI-22</t>
-  </si>
-  <si>
     <t>BR-087</t>
   </si>
   <si>
@@ -4642,9 +4765,6 @@
     <t>TD-F-096</t>
   </si>
   <si>
-    <t>AQPI-28</t>
-  </si>
-  <si>
     <t>BR-103</t>
   </si>
   <si>
@@ -4678,9 +4798,6 @@
     <t>TD-F-101</t>
   </si>
   <si>
-    <t>AQPI-29</t>
-  </si>
-  <si>
     <t>BR-108</t>
   </si>
   <si>
@@ -4714,9 +4831,6 @@
     <t>TD-F-106</t>
   </si>
   <si>
-    <t>AQPI-30</t>
-  </si>
-  <si>
     <t>BR-115</t>
   </si>
   <si>
@@ -4738,9 +4852,6 @@
     <t>br-117-email-accessible.spec.js</t>
   </si>
   <si>
-    <t>AQPI-31</t>
-  </si>
-  <si>
     <t>BR-119</t>
   </si>
   <si>
@@ -4972,7 +5083,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T20:05:20.214Z</t>
+    <t>2026-10-02T20:26:23.937Z</t>
   </si>
   <si>
     <t>33 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -4984,7 +5095,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-02T20:05:20.255Z</t>
+    <t>2026-10-02T20:26:23.982Z</t>
   </si>
   <si>
     <t>13 requirements, 18 test cases, 10 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -5848,19 +5959,19 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="1" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1209</v>
       </c>
@@ -5874,48 +5985,51 @@
         <v>1212</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>363</v>
+        <v>1216</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2</v>
+        <v>363</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1217</v>
       </c>
       <c r="F2" s="2">
         <v>2</v>
       </c>
       <c r="G2" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -5923,28 +6037,31 @@
       <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>363</v>
+      <c r="J2" s="2">
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>1216</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1213</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
+        <v>1214</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1221</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -5956,103 +6073,112 @@
         <v>1</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>363</v>
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1137</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
+        <v>1214</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1223</v>
       </c>
       <c r="F4" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
         <v>4</v>
       </c>
       <c r="H4" s="2">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2">
         <v>3</v>
       </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>1222</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1224</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K5" s="2" t="s">
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1220</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1218</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="E6" s="2">
+        <v>1214</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F6" s="2">
         <v>3</v>
-      </c>
-      <c r="F6" s="2">
-        <v>4</v>
       </c>
       <c r="G6" s="2">
         <v>4</v>
@@ -6061,36 +6187,39 @@
         <v>4</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>363</v>
+        <v>4</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>363</v>
+        <v>1216</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1228</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4</v>
+        <v>363</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1230</v>
       </c>
       <c r="F7" s="2">
         <v>4</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -6098,151 +6227,1192 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>363</v>
+      <c r="J7" s="2">
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>1216</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1230</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="E8" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F8" s="2">
         <v>5</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>6</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5</v>
       </c>
       <c r="H8" s="2">
         <v>5</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>363</v>
+        <v>5</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1142</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1227</v>
+        <v>1216</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E9" s="2">
-        <v>6</v>
+        <v>1229</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1233</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2">
+        <v>6</v>
+      </c>
+      <c r="H9" s="2">
         <v>2</v>
       </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
       <c r="I9" s="2">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L9" s="2" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1227</v>
+        <v>1216</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4</v>
+        <v>1229</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1235</v>
       </c>
       <c r="F10" s="2">
         <v>4</v>
       </c>
       <c r="G10" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2">
         <v>2</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>363</v>
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>1220</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1218</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>1227</v>
+        <v>1216</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E11" s="2">
-        <v>3</v>
+        <v>1229</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1237</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
       </c>
       <c r="G11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2">
         <v>2</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>363</v>
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F13" s="2">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2">
+        <v>4</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1220</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F14" s="2">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2">
+        <v>9</v>
+      </c>
+      <c r="H14" s="2">
+        <v>6</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F15" s="2">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2">
+        <v>14</v>
+      </c>
+      <c r="H15" s="2">
+        <v>12</v>
+      </c>
+      <c r="I15" s="2">
+        <v>11</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>4</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F18" s="2">
+        <v>5</v>
+      </c>
+      <c r="G18" s="2">
+        <v>5</v>
+      </c>
+      <c r="H18" s="2">
+        <v>5</v>
+      </c>
+      <c r="I18" s="2">
+        <v>5</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2">
+        <v>5</v>
+      </c>
+      <c r="H19" s="2">
+        <v>4</v>
+      </c>
+      <c r="I19" s="2">
+        <v>4</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F20" s="2">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2">
+        <v>2</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F21" s="2">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F22" s="2">
+        <v>7</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="2">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2">
+        <v>3</v>
+      </c>
+      <c r="H23" s="2">
+        <v>3</v>
+      </c>
+      <c r="I23" s="2">
+        <v>3</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3</v>
+      </c>
+      <c r="G24" s="2">
+        <v>3</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2</v>
+      </c>
+      <c r="I24" s="2">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F26" s="2">
+        <v>6</v>
+      </c>
+      <c r="G26" s="2">
+        <v>6</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2</v>
+      </c>
+      <c r="I26" s="2">
+        <v>2</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F27" s="2">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F28" s="2">
+        <v>6</v>
+      </c>
+      <c r="G28" s="2">
+        <v>7</v>
+      </c>
+      <c r="H28" s="2">
+        <v>3</v>
+      </c>
+      <c r="I28" s="2">
+        <v>2</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F29" s="2">
+        <v>4</v>
+      </c>
+      <c r="G29" s="2">
+        <v>4</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F30" s="2">
+        <v>6</v>
+      </c>
+      <c r="G30" s="2">
+        <v>6</v>
+      </c>
+      <c r="H30" s="2">
+        <v>4</v>
+      </c>
+      <c r="I30" s="2">
+        <v>4</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F31" s="2">
+        <v>6</v>
+      </c>
+      <c r="G31" s="2">
+        <v>9</v>
+      </c>
+      <c r="H31" s="2">
+        <v>6</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F32" s="2">
+        <v>7</v>
+      </c>
+      <c r="G32" s="2">
+        <v>9</v>
+      </c>
+      <c r="H32" s="2">
+        <v>6</v>
+      </c>
+      <c r="I32" s="2">
+        <v>5</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F33" s="2">
+        <v>3</v>
+      </c>
+      <c r="G33" s="2">
+        <v>3</v>
+      </c>
+      <c r="H33" s="2">
+        <v>3</v>
+      </c>
+      <c r="I33" s="2">
+        <v>3</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F34" s="2">
+        <v>4</v>
+      </c>
+      <c r="G34" s="2">
+        <v>4</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F35" s="2">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2">
+        <v>5</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F36" s="2">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2">
+        <v>5</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F37" s="2">
+        <v>3</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3</v>
+      </c>
+      <c r="H37" s="2">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3</v>
+      </c>
+      <c r="G38" s="2">
+        <v>3</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>1218</v>
       </c>
     </row>
   </sheetData>
@@ -6271,19 +7441,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1236</v>
+        <v>1291</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1237</v>
+        <v>1292</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1238</v>
+        <v>1293</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1239</v>
+        <v>1294</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>337</v>
@@ -6292,19 +7462,19 @@
         <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1240</v>
+        <v>1295</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1241</v>
+        <v>1296</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1242</v>
+        <v>1297</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1104</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1243</v>
+        <v>1298</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1114</v>
@@ -6312,7 +7482,7 @@
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>57</v>
@@ -6321,7 +7491,7 @@
         <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1245</v>
+        <v>1299</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>349</v>
@@ -6336,10 +7506,10 @@
         <v>360</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1246</v>
+        <v>1300</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1247</v>
+        <v>1301</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1107</v>
@@ -6353,7 +7523,7 @@
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>67</v>
@@ -6362,7 +7532,7 @@
         <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1248</v>
+        <v>1302</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>364</v>
@@ -6377,7 +7547,7 @@
         <v>373</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1249</v>
+        <v>1303</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -6392,7 +7562,7 @@
     </row>
     <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1250</v>
+        <v>1304</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>69</v>
@@ -6401,7 +7571,7 @@
         <v>70</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1251</v>
+        <v>1305</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>374</v>
@@ -6416,7 +7586,7 @@
         <v>373</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1252</v>
+        <v>1306</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -6431,7 +7601,7 @@
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1250</v>
+        <v>1304</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>72</v>
@@ -6440,7 +7610,7 @@
         <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1253</v>
+        <v>1307</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>378</v>
@@ -6455,7 +7625,7 @@
         <v>373</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1254</v>
+        <v>1308</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -6470,7 +7640,7 @@
     </row>
     <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1250</v>
+        <v>1304</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>74</v>
@@ -6479,7 +7649,7 @@
         <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1255</v>
+        <v>1309</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>382</v>
@@ -6494,7 +7664,7 @@
         <v>373</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1256</v>
+        <v>1310</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -6509,7 +7679,7 @@
     </row>
     <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1250</v>
+        <v>1304</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>76</v>
@@ -6518,7 +7688,7 @@
         <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1257</v>
+        <v>1311</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>386</v>
@@ -6533,7 +7703,7 @@
         <v>373</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1258</v>
+        <v>1312</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -6548,7 +7718,7 @@
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>78</v>
@@ -6557,7 +7727,7 @@
         <v>79</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1260</v>
+        <v>1313</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>390</v>
@@ -6572,10 +7742,10 @@
         <v>360</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1261</v>
+        <v>1314</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1262</v>
+        <v>1315</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1107</v>
@@ -6589,7 +7759,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>80</v>
@@ -6598,7 +7768,7 @@
         <v>81</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1263</v>
+        <v>1316</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>398</v>
@@ -6613,10 +7783,10 @@
         <v>360</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1264</v>
+        <v>1317</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1265</v>
+        <v>1318</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1107</v>
@@ -6630,7 +7800,7 @@
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>82</v>
@@ -6639,7 +7809,7 @@
         <v>83</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1266</v>
+        <v>1319</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>404</v>
@@ -6654,10 +7824,10 @@
         <v>360</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1267</v>
+        <v>1320</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1268</v>
+        <v>1321</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1107</v>
@@ -6671,7 +7841,7 @@
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>82</v>
@@ -6680,7 +7850,7 @@
         <v>83</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1266</v>
+        <v>1319</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>411</v>
@@ -6695,10 +7865,10 @@
         <v>360</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1269</v>
+        <v>1322</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1268</v>
+        <v>1321</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1107</v>
@@ -6712,7 +7882,7 @@
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>82</v>
@@ -6721,7 +7891,7 @@
         <v>83</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1266</v>
+        <v>1319</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>417</v>
@@ -6736,10 +7906,10 @@
         <v>360</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1270</v>
+        <v>1323</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1268</v>
+        <v>1321</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1107</v>
@@ -6753,7 +7923,7 @@
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>84</v>
@@ -6762,7 +7932,7 @@
         <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1271</v>
+        <v>1324</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>423</v>
@@ -6777,10 +7947,10 @@
         <v>360</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1272</v>
+        <v>1325</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1273</v>
+        <v>1326</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1107</v>
@@ -6794,7 +7964,7 @@
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>87</v>
@@ -6803,7 +7973,7 @@
         <v>88</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1274</v>
+        <v>1327</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>432</v>
@@ -6818,7 +7988,7 @@
         <v>373</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1275</v>
+        <v>1328</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -6833,7 +8003,7 @@
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>89</v>
@@ -6842,7 +8012,7 @@
         <v>90</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1276</v>
+        <v>1329</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>436</v>
@@ -6857,7 +8027,7 @@
         <v>373</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1277</v>
+        <v>1330</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -6872,7 +8042,7 @@
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>91</v>
@@ -6881,7 +8051,7 @@
         <v>92</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1278</v>
+        <v>1331</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>440</v>
@@ -6896,7 +8066,7 @@
         <v>373</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1279</v>
+        <v>1332</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -6920,7 +8090,7 @@
         <v>94</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1280</v>
+        <v>1333</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>444</v>
@@ -6935,10 +8105,10 @@
         <v>360</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1281</v>
+        <v>1334</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1282</v>
+        <v>1335</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1107</v>
@@ -6961,7 +8131,7 @@
         <v>96</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1283</v>
+        <v>1336</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>450</v>
@@ -6976,10 +8146,10 @@
         <v>360</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1284</v>
+        <v>1337</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1285</v>
+        <v>1338</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1107</v>
@@ -7002,7 +8172,7 @@
         <v>98</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1286</v>
+        <v>1339</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>457</v>
@@ -7017,7 +8187,7 @@
         <v>373</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1287</v>
+        <v>1340</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -7041,7 +8211,7 @@
         <v>102</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1288</v>
+        <v>1341</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>461</v>
@@ -7056,7 +8226,7 @@
         <v>373</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1289</v>
+        <v>1342</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -7071,7 +8241,7 @@
     </row>
     <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1290</v>
+        <v>1247</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>103</v>
@@ -7080,7 +8250,7 @@
         <v>104</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1291</v>
+        <v>1343</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>465</v>
@@ -7095,10 +8265,10 @@
         <v>360</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1292</v>
+        <v>1344</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1293</v>
+        <v>1345</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>1107</v>
@@ -7112,7 +8282,7 @@
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1290</v>
+        <v>1247</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>105</v>
@@ -7121,7 +8291,7 @@
         <v>106</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1294</v>
+        <v>1346</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>467</v>
@@ -7136,7 +8306,7 @@
         <v>373</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1295</v>
+        <v>1347</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
@@ -7151,7 +8321,7 @@
     </row>
     <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1290</v>
+        <v>1247</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>107</v>
@@ -7160,7 +8330,7 @@
         <v>108</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1296</v>
+        <v>1348</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>471</v>
@@ -7175,10 +8345,10 @@
         <v>360</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1297</v>
+        <v>1349</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1298</v>
+        <v>1350</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>1107</v>
@@ -7192,7 +8362,7 @@
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1299</v>
+        <v>1251</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>109</v>
@@ -7201,7 +8371,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1300</v>
+        <v>1351</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>477</v>
@@ -7216,10 +8386,10 @@
         <v>360</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1301</v>
+        <v>1352</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1302</v>
+        <v>1353</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1107</v>
@@ -7233,7 +8403,7 @@
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1299</v>
+        <v>1251</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>111</v>
@@ -7242,7 +8412,7 @@
         <v>112</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1303</v>
+        <v>1354</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>483</v>
@@ -7257,10 +8427,10 @@
         <v>360</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1304</v>
+        <v>1355</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1305</v>
+        <v>1356</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1107</v>
@@ -7274,7 +8444,7 @@
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>1299</v>
+        <v>1251</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>113</v>
@@ -7283,7 +8453,7 @@
         <v>114</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1306</v>
+        <v>1357</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>488</v>
@@ -7298,10 +8468,10 @@
         <v>360</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1307</v>
+        <v>1358</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1308</v>
+        <v>1359</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1107</v>
@@ -7315,7 +8485,7 @@
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>1299</v>
+        <v>1251</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>115</v>
@@ -7324,7 +8494,7 @@
         <v>116</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1309</v>
+        <v>1360</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>496</v>
@@ -7339,10 +8509,10 @@
         <v>360</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1310</v>
+        <v>1361</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1311</v>
+        <v>1362</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1107</v>
@@ -7356,7 +8526,7 @@
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>1299</v>
+        <v>1251</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>117</v>
@@ -7365,7 +8535,7 @@
         <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1312</v>
+        <v>1363</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>502</v>
@@ -7380,10 +8550,10 @@
         <v>360</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1313</v>
+        <v>1364</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1314</v>
+        <v>1365</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1107</v>
@@ -7397,7 +8567,7 @@
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1315</v>
+        <v>1253</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>119</v>
@@ -7406,7 +8576,7 @@
         <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1316</v>
+        <v>1366</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>509</v>
@@ -7421,10 +8591,10 @@
         <v>360</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1317</v>
+        <v>1367</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1318</v>
+        <v>1368</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1107</v>
@@ -7438,7 +8608,7 @@
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1315</v>
+        <v>1253</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>121</v>
@@ -7447,7 +8617,7 @@
         <v>122</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1319</v>
+        <v>1369</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>515</v>
@@ -7462,10 +8632,10 @@
         <v>360</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1320</v>
+        <v>1370</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>1321</v>
+        <v>1371</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>1107</v>
@@ -7479,7 +8649,7 @@
     </row>
     <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1315</v>
+        <v>1253</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>121</v>
@@ -7488,7 +8658,7 @@
         <v>122</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1319</v>
+        <v>1369</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>521</v>
@@ -7503,10 +8673,10 @@
         <v>360</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1322</v>
+        <v>1372</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1321</v>
+        <v>1371</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>1107</v>
@@ -7520,7 +8690,7 @@
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>1315</v>
+        <v>1253</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>123</v>
@@ -7529,7 +8699,7 @@
         <v>124</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1323</v>
+        <v>1373</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>526</v>
@@ -7544,7 +8714,7 @@
         <v>373</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1324</v>
+        <v>1374</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
@@ -7559,7 +8729,7 @@
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1315</v>
+        <v>1253</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>125</v>
@@ -7568,7 +8738,7 @@
         <v>126</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1325</v>
+        <v>1375</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>530</v>
@@ -7583,10 +8753,10 @@
         <v>360</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1326</v>
+        <v>1376</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>1327</v>
+        <v>1377</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>1107</v>
@@ -7600,7 +8770,7 @@
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1328</v>
+        <v>1255</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>127</v>
@@ -7609,7 +8779,7 @@
         <v>128</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1329</v>
+        <v>1378</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>536</v>
@@ -7624,10 +8794,10 @@
         <v>360</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1330</v>
+        <v>1379</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1331</v>
+        <v>1380</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1107</v>
@@ -7641,7 +8811,7 @@
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1328</v>
+        <v>1255</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>129</v>
@@ -7650,7 +8820,7 @@
         <v>130</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1332</v>
+        <v>1381</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>542</v>
@@ -7665,7 +8835,7 @@
         <v>373</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1333</v>
+        <v>1382</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
@@ -7680,7 +8850,7 @@
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>1328</v>
+        <v>1255</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>131</v>
@@ -7689,7 +8859,7 @@
         <v>132</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1334</v>
+        <v>1383</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>546</v>
@@ -7704,7 +8874,7 @@
         <v>373</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1335</v>
+        <v>1384</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -7719,7 +8889,7 @@
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1328</v>
+        <v>1255</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>133</v>
@@ -7728,7 +8898,7 @@
         <v>134</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1336</v>
+        <v>1385</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>550</v>
@@ -7743,10 +8913,10 @@
         <v>360</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1337</v>
+        <v>1386</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>1338</v>
+        <v>1387</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>1107</v>
@@ -7760,7 +8930,7 @@
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>1339</v>
+        <v>1259</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>135</v>
@@ -7769,7 +8939,7 @@
         <v>136</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1340</v>
+        <v>1388</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>556</v>
@@ -7784,7 +8954,7 @@
         <v>373</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1341</v>
+        <v>1389</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -7799,7 +8969,7 @@
     </row>
     <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1339</v>
+        <v>1259</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>137</v>
@@ -7808,7 +8978,7 @@
         <v>138</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1342</v>
+        <v>1390</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>560</v>
@@ -7823,10 +8993,10 @@
         <v>360</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1343</v>
+        <v>1391</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>1344</v>
+        <v>1392</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>1107</v>
@@ -7840,7 +9010,7 @@
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>1339</v>
+        <v>1259</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>139</v>
@@ -7849,7 +9019,7 @@
         <v>140</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1345</v>
+        <v>1393</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>566</v>
@@ -7864,10 +9034,10 @@
         <v>360</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1346</v>
+        <v>1394</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1347</v>
+        <v>1395</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1107</v>
@@ -7881,7 +9051,7 @@
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1339</v>
+        <v>1259</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>141</v>
@@ -7890,7 +9060,7 @@
         <v>142</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1348</v>
+        <v>1396</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>572</v>
@@ -7905,7 +9075,7 @@
         <v>373</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1349</v>
+        <v>1397</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
@@ -7920,7 +9090,7 @@
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>1339</v>
+        <v>1259</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>143</v>
@@ -7929,7 +9099,7 @@
         <v>144</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1350</v>
+        <v>1398</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>576</v>
@@ -7944,7 +9114,7 @@
         <v>373</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1351</v>
+        <v>1399</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
@@ -7959,7 +9129,7 @@
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>1339</v>
+        <v>1259</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>145</v>
@@ -7968,7 +9138,7 @@
         <v>146</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1352</v>
+        <v>1400</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>580</v>
@@ -7983,7 +9153,7 @@
         <v>373</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1353</v>
+        <v>1401</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
@@ -7998,7 +9168,7 @@
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>1339</v>
+        <v>1259</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>147</v>
@@ -8007,7 +9177,7 @@
         <v>148</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1354</v>
+        <v>1402</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>584</v>
@@ -8022,7 +9192,7 @@
         <v>373</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1355</v>
+        <v>1403</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -8037,7 +9207,7 @@
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1356</v>
+        <v>1261</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>149</v>
@@ -8046,7 +9216,7 @@
         <v>150</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1357</v>
+        <v>1404</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>588</v>
@@ -8061,10 +9231,10 @@
         <v>360</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1358</v>
+        <v>1405</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>1359</v>
+        <v>1406</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>1107</v>
@@ -8078,7 +9248,7 @@
     </row>
     <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>1356</v>
+        <v>1261</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>151</v>
@@ -8087,7 +9257,7 @@
         <v>152</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1360</v>
+        <v>1407</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>593</v>
@@ -8102,10 +9272,10 @@
         <v>360</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1361</v>
+        <v>1408</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>1362</v>
+        <v>1409</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>1107</v>
@@ -8119,7 +9289,7 @@
     </row>
     <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>1356</v>
+        <v>1261</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>153</v>
@@ -8128,7 +9298,7 @@
         <v>154</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1363</v>
+        <v>1410</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>599</v>
@@ -8143,10 +9313,10 @@
         <v>360</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1364</v>
+        <v>1411</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>1365</v>
+        <v>1412</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>1107</v>
@@ -8160,7 +9330,7 @@
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>1366</v>
+        <v>1263</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>157</v>
@@ -8169,7 +9339,7 @@
         <v>158</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1367</v>
+        <v>1413</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>601</v>
@@ -8184,7 +9354,7 @@
         <v>373</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1368</v>
+        <v>1414</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
@@ -8199,7 +9369,7 @@
     </row>
     <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>1366</v>
+        <v>1263</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>159</v>
@@ -8208,7 +9378,7 @@
         <v>160</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1369</v>
+        <v>1415</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>605</v>
@@ -8223,10 +9393,10 @@
         <v>360</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1370</v>
+        <v>1416</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>1371</v>
+        <v>1417</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>1107</v>
@@ -8240,7 +9410,7 @@
     </row>
     <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>1366</v>
+        <v>1263</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>161</v>
@@ -8249,7 +9419,7 @@
         <v>162</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1372</v>
+        <v>1418</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>611</v>
@@ -8264,10 +9434,10 @@
         <v>360</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1373</v>
+        <v>1419</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1374</v>
+        <v>1420</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1107</v>
@@ -8281,7 +9451,7 @@
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1375</v>
+        <v>1267</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>163</v>
@@ -8290,7 +9460,7 @@
         <v>164</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1376</v>
+        <v>1421</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>617</v>
@@ -8305,10 +9475,10 @@
         <v>360</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1377</v>
+        <v>1422</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>1378</v>
+        <v>1423</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>1107</v>
@@ -8322,7 +9492,7 @@
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>1375</v>
+        <v>1267</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>165</v>
@@ -8331,7 +9501,7 @@
         <v>166</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1379</v>
+        <v>1424</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>623</v>
@@ -8346,7 +9516,7 @@
         <v>373</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1380</v>
+        <v>1425</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
@@ -8361,7 +9531,7 @@
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1375</v>
+        <v>1267</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>167</v>
@@ -8370,7 +9540,7 @@
         <v>168</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1381</v>
+        <v>1426</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>627</v>
@@ -8385,7 +9555,7 @@
         <v>373</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1382</v>
+        <v>1427</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -8400,7 +9570,7 @@
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>1375</v>
+        <v>1267</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>169</v>
@@ -8409,7 +9579,7 @@
         <v>170</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1383</v>
+        <v>1428</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>631</v>
@@ -8424,7 +9594,7 @@
         <v>373</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -8439,7 +9609,7 @@
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>1375</v>
+        <v>1267</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>171</v>
@@ -8448,7 +9618,7 @@
         <v>172</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1385</v>
+        <v>1430</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>635</v>
@@ -8463,7 +9633,7 @@
         <v>373</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1386</v>
+        <v>1431</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -8478,7 +9648,7 @@
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>1387</v>
+        <v>1269</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>173</v>
@@ -8487,7 +9657,7 @@
         <v>174</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1388</v>
+        <v>1432</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>639</v>
@@ -8502,7 +9672,7 @@
         <v>373</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1389</v>
+        <v>1433</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -8517,7 +9687,7 @@
     </row>
     <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>1387</v>
+        <v>1269</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>175</v>
@@ -8526,7 +9696,7 @@
         <v>176</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1390</v>
+        <v>1434</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>643</v>
@@ -8541,10 +9711,10 @@
         <v>360</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1391</v>
+        <v>1435</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1392</v>
+        <v>1436</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>1107</v>
@@ -8558,7 +9728,7 @@
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>1387</v>
+        <v>1269</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>177</v>
@@ -8567,7 +9737,7 @@
         <v>178</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1393</v>
+        <v>1437</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>650</v>
@@ -8582,10 +9752,10 @@
         <v>360</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1394</v>
+        <v>1438</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1395</v>
+        <v>1439</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1107</v>
@@ -8599,7 +9769,7 @@
     </row>
     <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>1387</v>
+        <v>1269</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>179</v>
@@ -8608,7 +9778,7 @@
         <v>180</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1396</v>
+        <v>1440</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>657</v>
@@ -8623,7 +9793,7 @@
         <v>373</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1397</v>
+        <v>1441</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
@@ -8647,7 +9817,7 @@
         <v>182</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1398</v>
+        <v>1442</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>661</v>
@@ -8662,10 +9832,10 @@
         <v>360</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1399</v>
+        <v>1443</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>1400</v>
+        <v>1444</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>1107</v>
@@ -8688,7 +9858,7 @@
         <v>184</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1401</v>
+        <v>1445</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>667</v>
@@ -8703,7 +9873,7 @@
         <v>373</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1402</v>
+        <v>1446</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
@@ -8727,7 +9897,7 @@
         <v>186</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1403</v>
+        <v>1447</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>671</v>
@@ -8742,7 +9912,7 @@
         <v>373</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1404</v>
+        <v>1448</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
@@ -8766,7 +9936,7 @@
         <v>188</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1405</v>
+        <v>1449</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>675</v>
@@ -8781,7 +9951,7 @@
         <v>373</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1406</v>
+        <v>1450</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
@@ -8805,7 +9975,7 @@
         <v>190</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1407</v>
+        <v>1451</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>679</v>
@@ -8820,7 +9990,7 @@
         <v>373</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1408</v>
+        <v>1452</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
@@ -8835,7 +10005,7 @@
     </row>
     <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>1409</v>
+        <v>1274</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>191</v>
@@ -8844,7 +10014,7 @@
         <v>192</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>683</v>
@@ -8859,10 +10029,10 @@
         <v>360</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1411</v>
+        <v>1454</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>1107</v>
@@ -8876,7 +10046,7 @@
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>1409</v>
+        <v>1274</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>193</v>
@@ -8885,7 +10055,7 @@
         <v>194</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1413</v>
+        <v>1456</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>688</v>
@@ -8900,10 +10070,10 @@
         <v>360</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1414</v>
+        <v>1457</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1415</v>
+        <v>1458</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1107</v>
@@ -8917,7 +10087,7 @@
     </row>
     <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>1409</v>
+        <v>1274</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>195</v>
@@ -8926,7 +10096,7 @@
         <v>196</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1416</v>
+        <v>1459</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>695</v>
@@ -8941,10 +10111,10 @@
         <v>360</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1417</v>
+        <v>1460</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1418</v>
+        <v>1461</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1107</v>
@@ -8958,7 +10128,7 @@
     </row>
     <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>1409</v>
+        <v>1274</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>197</v>
@@ -8967,7 +10137,7 @@
         <v>198</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1419</v>
+        <v>1462</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>702</v>
@@ -8982,7 +10152,7 @@
         <v>373</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1420</v>
+        <v>1463</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
@@ -8997,7 +10167,7 @@
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>1409</v>
+        <v>1274</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>199</v>
@@ -9006,7 +10176,7 @@
         <v>200</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1421</v>
+        <v>1464</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>706</v>
@@ -9021,7 +10191,7 @@
         <v>373</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1422</v>
+        <v>1465</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
@@ -9036,7 +10206,7 @@
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>1409</v>
+        <v>1274</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>201</v>
@@ -9045,7 +10215,7 @@
         <v>202</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1423</v>
+        <v>1466</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>710</v>
@@ -9060,10 +10230,10 @@
         <v>360</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1424</v>
+        <v>1467</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>1425</v>
+        <v>1468</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>1107</v>
@@ -9077,7 +10247,7 @@
     </row>
     <row r="71" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>203</v>
@@ -9086,7 +10256,7 @@
         <v>204</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1427</v>
+        <v>1469</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>716</v>
@@ -9101,10 +10271,10 @@
         <v>360</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1428</v>
+        <v>1470</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>1429</v>
+        <v>1471</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>1107</v>
@@ -9118,7 +10288,7 @@
     </row>
     <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>203</v>
@@ -9127,7 +10297,7 @@
         <v>204</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1427</v>
+        <v>1469</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>723</v>
@@ -9142,10 +10312,10 @@
         <v>360</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1430</v>
+        <v>1472</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1429</v>
+        <v>1471</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1107</v>
@@ -9159,7 +10329,7 @@
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>205</v>
@@ -9168,7 +10338,7 @@
         <v>206</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1431</v>
+        <v>1473</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>729</v>
@@ -9183,7 +10353,7 @@
         <v>373</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1432</v>
+        <v>1474</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
@@ -9198,7 +10368,7 @@
     </row>
     <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>207</v>
@@ -9207,7 +10377,7 @@
         <v>208</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1433</v>
+        <v>1475</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>733</v>
@@ -9222,10 +10392,10 @@
         <v>360</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1434</v>
+        <v>1476</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1435</v>
+        <v>1477</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>1107</v>
@@ -9239,7 +10409,7 @@
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>207</v>
@@ -9248,7 +10418,7 @@
         <v>208</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1433</v>
+        <v>1475</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>740</v>
@@ -9263,10 +10433,10 @@
         <v>360</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1436</v>
+        <v>1478</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>1435</v>
+        <v>1477</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>1107</v>
@@ -9280,7 +10450,7 @@
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>207</v>
@@ -9289,7 +10459,7 @@
         <v>208</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1433</v>
+        <v>1475</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>746</v>
@@ -9304,10 +10474,10 @@
         <v>360</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>1437</v>
+        <v>1479</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>1435</v>
+        <v>1477</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>1107</v>
@@ -9321,7 +10491,7 @@
     </row>
     <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>209</v>
@@ -9330,7 +10500,7 @@
         <v>210</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1438</v>
+        <v>1480</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>752</v>
@@ -9345,10 +10515,10 @@
         <v>360</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>1439</v>
+        <v>1481</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>1440</v>
+        <v>1482</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>1107</v>
@@ -9362,7 +10532,7 @@
     </row>
     <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>211</v>
@@ -9371,7 +10541,7 @@
         <v>212</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1441</v>
+        <v>1483</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>759</v>
@@ -9386,7 +10556,7 @@
         <v>373</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1442</v>
+        <v>1484</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
@@ -9401,7 +10571,7 @@
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>1426</v>
+        <v>1276</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>213</v>
@@ -9410,7 +10580,7 @@
         <v>214</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1443</v>
+        <v>1485</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>763</v>
@@ -9425,7 +10595,7 @@
         <v>373</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1444</v>
+        <v>1486</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -9449,7 +10619,7 @@
         <v>216</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1445</v>
+        <v>1487</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>767</v>
@@ -9464,10 +10634,10 @@
         <v>360</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>1447</v>
+        <v>1489</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>1107</v>
@@ -9490,7 +10660,7 @@
         <v>218</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1448</v>
+        <v>1490</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>773</v>
@@ -9505,10 +10675,10 @@
         <v>360</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1449</v>
+        <v>1491</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1450</v>
+        <v>1492</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1107</v>
@@ -9531,7 +10701,7 @@
         <v>220</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1451</v>
+        <v>1493</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>779</v>
@@ -9546,10 +10716,10 @@
         <v>360</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1452</v>
+        <v>1494</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>1453</v>
+        <v>1495</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>1107</v>
@@ -9572,7 +10742,7 @@
         <v>222</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1454</v>
+        <v>1496</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>785</v>
@@ -9587,7 +10757,7 @@
         <v>373</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1455</v>
+        <v>1497</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
@@ -9611,7 +10781,7 @@
         <v>224</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1456</v>
+        <v>1498</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>789</v>
@@ -9626,7 +10796,7 @@
         <v>373</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1457</v>
+        <v>1499</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -9650,7 +10820,7 @@
         <v>226</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1458</v>
+        <v>1500</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>793</v>
@@ -9665,7 +10835,7 @@
         <v>373</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1459</v>
+        <v>1501</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -9680,7 +10850,7 @@
     </row>
     <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>1460</v>
+        <v>1279</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>227</v>
@@ -9689,7 +10859,7 @@
         <v>228</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1461</v>
+        <v>1502</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>797</v>
@@ -9704,10 +10874,10 @@
         <v>360</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1462</v>
+        <v>1503</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>1463</v>
+        <v>1504</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>1107</v>
@@ -9721,7 +10891,7 @@
     </row>
     <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>1460</v>
+        <v>1279</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>229</v>
@@ -9730,7 +10900,7 @@
         <v>230</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1464</v>
+        <v>1505</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>803</v>
@@ -9745,10 +10915,10 @@
         <v>360</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1465</v>
+        <v>1506</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1466</v>
+        <v>1507</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1107</v>
@@ -9762,7 +10932,7 @@
     </row>
     <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>1460</v>
+        <v>1279</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>231</v>
@@ -9771,7 +10941,7 @@
         <v>232</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1467</v>
+        <v>1508</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>808</v>
@@ -9786,10 +10956,10 @@
         <v>360</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1468</v>
+        <v>1509</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>1469</v>
+        <v>1510</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>1107</v>
@@ -9803,7 +10973,7 @@
     </row>
     <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>233</v>
@@ -9812,7 +10982,7 @@
         <v>234</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1470</v>
+        <v>1511</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>814</v>
@@ -9827,10 +10997,10 @@
         <v>360</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1471</v>
+        <v>1512</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>1472</v>
+        <v>1513</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>1107</v>
@@ -9844,7 +11014,7 @@
     </row>
     <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>235</v>
@@ -9853,7 +11023,7 @@
         <v>236</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1473</v>
+        <v>1514</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>820</v>
@@ -9868,10 +11038,10 @@
         <v>360</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1474</v>
+        <v>1515</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>1475</v>
+        <v>1516</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>1107</v>
@@ -9885,7 +11055,7 @@
     </row>
     <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>239</v>
@@ -9894,7 +11064,7 @@
         <v>240</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1476</v>
+        <v>1517</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>822</v>
@@ -9909,7 +11079,7 @@
         <v>373</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1477</v>
+        <v>1518</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
@@ -9924,7 +11094,7 @@
     </row>
     <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>241</v>
@@ -9933,7 +11103,7 @@
         <v>242</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1478</v>
+        <v>1519</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>826</v>
@@ -9948,10 +11118,10 @@
         <v>360</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1479</v>
+        <v>1520</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>1480</v>
+        <v>1521</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>1107</v>
@@ -9974,7 +11144,7 @@
         <v>244</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1481</v>
+        <v>1522</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>828</v>
@@ -9989,7 +11159,7 @@
         <v>373</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1482</v>
+        <v>1523</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
@@ -10013,7 +11183,7 @@
         <v>246</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1483</v>
+        <v>1524</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>832</v>
@@ -10028,10 +11198,10 @@
         <v>360</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1484</v>
+        <v>1525</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>1485</v>
+        <v>1526</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>1107</v>
@@ -10054,7 +11224,7 @@
         <v>248</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1486</v>
+        <v>1527</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>839</v>
@@ -10069,7 +11239,7 @@
         <v>373</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1487</v>
+        <v>1528</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -10093,7 +11263,7 @@
         <v>250</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1488</v>
+        <v>1529</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>843</v>
@@ -10108,7 +11278,7 @@
         <v>373</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1489</v>
+        <v>1530</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -10132,7 +11302,7 @@
         <v>252</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1490</v>
+        <v>1531</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>847</v>
@@ -10147,7 +11317,7 @@
         <v>373</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1491</v>
+        <v>1532</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -10162,7 +11332,7 @@
     </row>
     <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>253</v>
@@ -10171,7 +11341,7 @@
         <v>254</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1492</v>
+        <v>1533</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>851</v>
@@ -10186,10 +11356,10 @@
         <v>360</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1493</v>
+        <v>1534</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>1494</v>
+        <v>1535</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>1107</v>
@@ -10203,7 +11373,7 @@
     </row>
     <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>255</v>
@@ -10212,7 +11382,7 @@
         <v>256</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1495</v>
+        <v>1536</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>857</v>
@@ -10227,7 +11397,7 @@
         <v>373</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1496</v>
+        <v>1537</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -10242,7 +11412,7 @@
     </row>
     <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>257</v>
@@ -10251,7 +11421,7 @@
         <v>258</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1497</v>
+        <v>1538</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>861</v>
@@ -10266,7 +11436,7 @@
         <v>373</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1498</v>
+        <v>1539</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -10281,7 +11451,7 @@
     </row>
     <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>1499</v>
+        <v>1283</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>259</v>
@@ -10290,7 +11460,7 @@
         <v>260</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1500</v>
+        <v>1540</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>865</v>
@@ -10305,7 +11475,7 @@
         <v>373</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1501</v>
+        <v>1541</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -10320,7 +11490,7 @@
     </row>
     <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>1499</v>
+        <v>1283</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>261</v>
@@ -10329,7 +11499,7 @@
         <v>262</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1502</v>
+        <v>1542</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>869</v>
@@ -10344,7 +11514,7 @@
         <v>373</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1503</v>
+        <v>1543</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
@@ -10359,7 +11529,7 @@
     </row>
     <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>1499</v>
+        <v>1283</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>263</v>
@@ -10368,7 +11538,7 @@
         <v>264</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1504</v>
+        <v>1544</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>873</v>
@@ -10383,7 +11553,7 @@
         <v>373</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1505</v>
+        <v>1545</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -10398,7 +11568,7 @@
     </row>
     <row r="104" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>1499</v>
+        <v>1283</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>265</v>
@@ -10407,7 +11577,7 @@
         <v>266</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1506</v>
+        <v>1546</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>877</v>
@@ -10422,10 +11592,10 @@
         <v>360</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1507</v>
+        <v>1547</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>1508</v>
+        <v>1548</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>1107</v>
@@ -10439,7 +11609,7 @@
     </row>
     <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>1499</v>
+        <v>1283</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>267</v>
@@ -10448,7 +11618,7 @@
         <v>268</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1509</v>
+        <v>1549</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>879</v>
@@ -10463,7 +11633,7 @@
         <v>373</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1510</v>
+        <v>1550</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -10478,7 +11648,7 @@
     </row>
     <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>1511</v>
+        <v>1285</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>269</v>
@@ -10487,7 +11657,7 @@
         <v>270</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1512</v>
+        <v>1551</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>883</v>
@@ -10502,10 +11672,10 @@
         <v>360</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1513</v>
+        <v>1552</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1514</v>
+        <v>1553</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1107</v>
@@ -10519,7 +11689,7 @@
     </row>
     <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>1511</v>
+        <v>1285</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>271</v>
@@ -10528,7 +11698,7 @@
         <v>272</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1515</v>
+        <v>1554</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>889</v>
@@ -10543,7 +11713,7 @@
         <v>373</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1516</v>
+        <v>1555</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2" t="s">
@@ -10558,7 +11728,7 @@
     </row>
     <row r="108" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>1511</v>
+        <v>1285</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>275</v>
@@ -10567,7 +11737,7 @@
         <v>276</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1517</v>
+        <v>1556</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>893</v>
@@ -10582,7 +11752,7 @@
         <v>373</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1518</v>
+        <v>1557</v>
       </c>
       <c r="J108" s="2"/>
       <c r="K108" s="2" t="s">
@@ -10597,7 +11767,7 @@
     </row>
     <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>1511</v>
+        <v>1285</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>277</v>
@@ -10606,7 +11776,7 @@
         <v>278</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1519</v>
+        <v>1558</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>897</v>
@@ -10621,7 +11791,7 @@
         <v>373</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1520</v>
+        <v>1559</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
@@ -10636,7 +11806,7 @@
     </row>
     <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>1511</v>
+        <v>1285</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>279</v>
@@ -10645,7 +11815,7 @@
         <v>280</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1521</v>
+        <v>1560</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>901</v>
@@ -10660,7 +11830,7 @@
         <v>373</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1522</v>
+        <v>1561</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2" t="s">
@@ -10675,7 +11845,7 @@
     </row>
     <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>1523</v>
+        <v>1287</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>283</v>
@@ -10684,7 +11854,7 @@
         <v>284</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1524</v>
+        <v>1562</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>905</v>
@@ -10699,7 +11869,7 @@
         <v>373</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1525</v>
+        <v>1563</v>
       </c>
       <c r="J111" s="2"/>
       <c r="K111" s="2" t="s">
@@ -10714,7 +11884,7 @@
     </row>
     <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>1523</v>
+        <v>1287</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>285</v>
@@ -10723,7 +11893,7 @@
         <v>286</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1526</v>
+        <v>1564</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>909</v>
@@ -10738,7 +11908,7 @@
         <v>373</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1527</v>
+        <v>1565</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2" t="s">
@@ -10753,7 +11923,7 @@
     </row>
     <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>1523</v>
+        <v>1287</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>287</v>
@@ -10762,7 +11932,7 @@
         <v>288</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1528</v>
+        <v>1566</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>913</v>
@@ -10777,10 +11947,10 @@
         <v>360</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1529</v>
+        <v>1567</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>1530</v>
+        <v>1568</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>1107</v>
@@ -10794,7 +11964,7 @@
     </row>
     <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>1531</v>
+        <v>1289</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>291</v>
@@ -10803,7 +11973,7 @@
         <v>292</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1532</v>
+        <v>1569</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>918</v>
@@ -10818,7 +11988,7 @@
         <v>373</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1533</v>
+        <v>1570</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
@@ -10833,7 +12003,7 @@
     </row>
     <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>1531</v>
+        <v>1289</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>293</v>
@@ -10842,7 +12012,7 @@
         <v>294</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1534</v>
+        <v>1571</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>922</v>
@@ -10857,7 +12027,7 @@
         <v>373</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1535</v>
+        <v>1572</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2" t="s">
@@ -10872,7 +12042,7 @@
     </row>
     <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>1531</v>
+        <v>1289</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>295</v>
@@ -10881,7 +12051,7 @@
         <v>296</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1536</v>
+        <v>1573</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>926</v>
@@ -10896,7 +12066,7 @@
         <v>373</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1537</v>
+        <v>1574</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
@@ -10911,7 +12081,7 @@
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1538</v>
+        <v>1575</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>297</v>
@@ -10920,7 +12090,7 @@
         <v>298</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1539</v>
+        <v>1576</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>930</v>
@@ -10935,10 +12105,10 @@
         <v>360</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1540</v>
+        <v>1577</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1541</v>
+        <v>1578</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1107</v>
@@ -10961,7 +12131,7 @@
         <v>302</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1542</v>
+        <v>1579</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>939</v>
@@ -10976,10 +12146,10 @@
         <v>360</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1543</v>
+        <v>1580</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1544</v>
+        <v>1581</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>1107</v>
@@ -11002,7 +12172,7 @@
         <v>302</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1542</v>
+        <v>1579</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>946</v>
@@ -11017,10 +12187,10 @@
         <v>360</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1545</v>
+        <v>1582</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1544</v>
+        <v>1581</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>1110</v>
@@ -11034,7 +12204,7 @@
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1546</v>
+        <v>1583</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>303</v>
@@ -11043,7 +12213,7 @@
         <v>304</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1547</v>
+        <v>1584</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>952</v>
@@ -11058,10 +12228,10 @@
         <v>360</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1548</v>
+        <v>1585</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1549</v>
+        <v>1586</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>1107</v>
@@ -11084,7 +12254,7 @@
         <v>307</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1550</v>
+        <v>1587</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>959</v>
@@ -11099,10 +12269,10 @@
         <v>360</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1551</v>
+        <v>1588</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1552</v>
+        <v>1589</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>1107</v>
@@ -11125,7 +12295,7 @@
         <v>307</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1550</v>
+        <v>1587</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>965</v>
@@ -11140,10 +12310,10 @@
         <v>360</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1553</v>
+        <v>1590</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1552</v>
+        <v>1589</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>1110</v>
@@ -11166,7 +12336,7 @@
         <v>307</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1550</v>
+        <v>1587</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>969</v>
@@ -11181,10 +12351,10 @@
         <v>360</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1554</v>
+        <v>1591</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>1552</v>
+        <v>1589</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>1107</v>
@@ -11198,7 +12368,7 @@
     </row>
     <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>1555</v>
+        <v>1592</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>308</v>
@@ -11207,7 +12377,7 @@
         <v>309</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1556</v>
+        <v>1593</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>974</v>
@@ -11222,10 +12392,10 @@
         <v>360</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1557</v>
+        <v>1594</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1558</v>
+        <v>1595</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>1107</v>
@@ -11239,7 +12409,7 @@
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>1555</v>
+        <v>1592</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>308</v>
@@ -11248,7 +12418,7 @@
         <v>309</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1556</v>
+        <v>1593</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>982</v>
@@ -11263,10 +12433,10 @@
         <v>360</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1559</v>
+        <v>1596</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1558</v>
+        <v>1595</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1107</v>
@@ -11280,7 +12450,7 @@
     </row>
     <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>1555</v>
+        <v>1592</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>308</v>
@@ -11289,7 +12459,7 @@
         <v>309</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1556</v>
+        <v>1593</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>988</v>
@@ -11304,10 +12474,10 @@
         <v>360</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>1560</v>
+        <v>1597</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>1558</v>
+        <v>1595</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1107</v>
@@ -11321,7 +12491,7 @@
     </row>
     <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>1555</v>
+        <v>1592</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>308</v>
@@ -11330,7 +12500,7 @@
         <v>309</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1556</v>
+        <v>1593</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>994</v>
@@ -11345,10 +12515,10 @@
         <v>360</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1561</v>
+        <v>1598</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1558</v>
+        <v>1595</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>1110</v>
@@ -11371,7 +12541,7 @@
         <v>312</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1562</v>
+        <v>1599</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>1000</v>
@@ -11386,10 +12556,10 @@
         <v>360</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1563</v>
+        <v>1600</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1564</v>
+        <v>1601</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1107</v>
@@ -11412,7 +12582,7 @@
         <v>312</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1562</v>
+        <v>1599</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>1006</v>
@@ -11427,10 +12597,10 @@
         <v>360</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1565</v>
+        <v>1602</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1564</v>
+        <v>1601</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1107</v>
@@ -11453,7 +12623,7 @@
         <v>312</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1562</v>
+        <v>1599</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>1012</v>
@@ -11468,10 +12638,10 @@
         <v>360</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>1566</v>
+        <v>1603</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>1564</v>
+        <v>1601</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1107</v>
@@ -11494,7 +12664,7 @@
         <v>312</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1562</v>
+        <v>1599</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>1018</v>
@@ -11509,10 +12679,10 @@
         <v>360</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1567</v>
+        <v>1604</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1564</v>
+        <v>1601</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>1107</v>
@@ -11535,7 +12705,7 @@
         <v>314</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1568</v>
+        <v>1605</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>1024</v>
@@ -11550,10 +12720,10 @@
         <v>360</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1569</v>
+        <v>1606</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1570</v>
+        <v>1607</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1107</v>
@@ -11576,7 +12746,7 @@
         <v>314</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1568</v>
+        <v>1605</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>1030</v>
@@ -11591,10 +12761,10 @@
         <v>360</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1571</v>
+        <v>1608</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1570</v>
+        <v>1607</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1107</v>
@@ -11608,7 +12778,7 @@
     </row>
     <row r="134" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>315</v>
@@ -11617,7 +12787,7 @@
         <v>316</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1572</v>
+        <v>1609</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>1036</v>
@@ -11632,7 +12802,7 @@
         <v>373</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>1573</v>
+        <v>1610</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2" t="s">
@@ -11647,7 +12817,7 @@
     </row>
     <row r="135" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>318</v>
@@ -11656,7 +12826,7 @@
         <v>319</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1574</v>
+        <v>1611</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>1041</v>
@@ -11671,7 +12841,7 @@
         <v>373</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>1575</v>
+        <v>1612</v>
       </c>
       <c r="J135" s="2"/>
       <c r="K135" s="2" t="s">
@@ -11686,7 +12856,7 @@
     </row>
     <row r="136" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>320</v>
@@ -11695,7 +12865,7 @@
         <v>321</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1576</v>
+        <v>1613</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>1045</v>
@@ -11710,10 +12880,10 @@
         <v>360</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>1577</v>
+        <v>1614</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1578</v>
+        <v>1615</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1107</v>
@@ -11727,7 +12897,7 @@
     </row>
     <row r="137" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>320</v>
@@ -11736,7 +12906,7 @@
         <v>321</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1576</v>
+        <v>1613</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>1051</v>
@@ -11751,10 +12921,10 @@
         <v>360</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1579</v>
+        <v>1616</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>1578</v>
+        <v>1615</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>1107</v>
@@ -11768,7 +12938,7 @@
     </row>
     <row r="138" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>322</v>
@@ -11777,7 +12947,7 @@
         <v>323</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1580</v>
+        <v>1617</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>1057</v>
@@ -11792,10 +12962,10 @@
         <v>360</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>1581</v>
+        <v>1618</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>1582</v>
+        <v>1619</v>
       </c>
       <c r="K138" s="2" t="s">
         <v>1107</v>
@@ -11809,7 +12979,7 @@
     </row>
     <row r="139" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>324</v>
@@ -11818,7 +12988,7 @@
         <v>325</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1583</v>
+        <v>1620</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>1063</v>
@@ -11833,10 +13003,10 @@
         <v>360</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>1584</v>
+        <v>1621</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>1585</v>
+        <v>1622</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>1107</v>
@@ -11850,7 +13020,7 @@
     </row>
     <row r="140" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>326</v>
@@ -11859,7 +13029,7 @@
         <v>327</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1586</v>
+        <v>1623</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>1069</v>
@@ -11874,10 +13044,10 @@
         <v>360</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>1587</v>
+        <v>1624</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>1588</v>
+        <v>1625</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>1107</v>
@@ -11891,7 +13061,7 @@
     </row>
     <row r="141" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>326</v>
@@ -11900,7 +13070,7 @@
         <v>327</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1586</v>
+        <v>1623</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>1075</v>
@@ -11915,10 +13085,10 @@
         <v>360</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>1589</v>
+        <v>1626</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>1588</v>
+        <v>1625</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>1107</v>
@@ -11941,7 +13111,7 @@
         <v>329</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1590</v>
+        <v>1627</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>1080</v>
@@ -11956,10 +13126,10 @@
         <v>360</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>1591</v>
+        <v>1628</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>1592</v>
+        <v>1629</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>1110</v>
@@ -11973,7 +13143,7 @@
     </row>
     <row r="143" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>330</v>
@@ -11982,7 +13152,7 @@
         <v>331</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1593</v>
+        <v>1630</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>1086</v>
@@ -11997,10 +13167,10 @@
         <v>360</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>1594</v>
+        <v>1631</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>1595</v>
+        <v>1632</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>1107</v>
@@ -12014,7 +13184,7 @@
     </row>
     <row r="144" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>332</v>
@@ -12023,7 +13193,7 @@
         <v>333</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1596</v>
+        <v>1633</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>1092</v>
@@ -12038,10 +13208,10 @@
         <v>360</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>1597</v>
+        <v>1634</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>1598</v>
+        <v>1635</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>1107</v>
@@ -12055,7 +13225,7 @@
     </row>
     <row r="145" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>334</v>
@@ -12064,7 +13234,7 @@
         <v>335</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1599</v>
+        <v>1636</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>1099</v>
@@ -12079,7 +13249,7 @@
         <v>373</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>1600</v>
+        <v>1637</v>
       </c>
       <c r="J145" s="2"/>
       <c r="K145" s="2" t="s">
@@ -12112,53 +13282,53 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1601</v>
+        <v>1638</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1602</v>
+        <v>1639</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1603</v>
+        <v>1640</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1604</v>
+        <v>1641</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1605</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1606</v>
+        <v>1643</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1607</v>
+        <v>1644</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1608</v>
+        <v>1645</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1609</v>
+        <v>1646</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1610</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1611</v>
+        <v>1648</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1607</v>
+        <v>1644</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1612</v>
+        <v>1649</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1613</v>
+        <v>1650</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1614</v>
+        <v>1651</v>
       </c>
     </row>
   </sheetData>
@@ -12181,7 +13351,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1615</v>
+        <v>1652</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>337</v>
@@ -12190,180 +13360,180 @@
         <v>1164</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1616</v>
+        <v>1653</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1617</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1618</v>
+        <v>1655</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1619</v>
+        <v>1656</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1620</v>
+        <v>1657</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1621</v>
+        <v>1658</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1622</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1623</v>
+        <v>1660</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1624</v>
+        <v>1661</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1625</v>
+        <v>1662</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1626</v>
+        <v>1663</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1627</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1628</v>
+        <v>1665</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1629</v>
+        <v>1666</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1630</v>
+        <v>1667</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1631</v>
+        <v>1668</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1632</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1633</v>
+        <v>1670</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1634</v>
+        <v>1671</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1635</v>
+        <v>1672</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1636</v>
+        <v>1673</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1637</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1638</v>
+        <v>1675</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1639</v>
+        <v>1676</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1640</v>
+        <v>1677</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1641</v>
+        <v>1678</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1642</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1643</v>
+        <v>1680</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1644</v>
+        <v>1681</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1645</v>
+        <v>1682</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1646</v>
+        <v>1683</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1647</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1648</v>
+        <v>1685</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1649</v>
+        <v>1686</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1650</v>
+        <v>1687</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1651</v>
+        <v>1688</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1652</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1653</v>
+        <v>1690</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1654</v>
+        <v>1691</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1655</v>
+        <v>1692</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1656</v>
+        <v>1693</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1657</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1658</v>
+        <v>1695</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1659</v>
+        <v>1696</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1660</v>
+        <v>1697</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1661</v>
+        <v>1698</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1662</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1663</v>
+        <v>1700</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1664</v>
+        <v>1701</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1665</v>
+        <v>1702</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1666</v>
+        <v>1703</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1667</v>
+        <v>1704</v>
       </c>
     </row>
   </sheetData>
@@ -12386,203 +13556,203 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1668</v>
+        <v>1705</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1669</v>
+        <v>1706</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1670</v>
+        <v>1707</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1671</v>
+        <v>1708</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1672</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1673</v>
+        <v>1710</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1674</v>
+        <v>1711</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1676</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1643</v>
+        <v>1680</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1677</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1678</v>
+        <v>1715</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1633</v>
+        <v>1670</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1679</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1680</v>
+        <v>1717</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1663</v>
+        <v>1700</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1681</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1682</v>
+        <v>1719</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1683</v>
+        <v>1720</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1684</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1685</v>
+        <v>1722</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1686</v>
+        <v>1723</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1687</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1688</v>
+        <v>1725</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1689</v>
+        <v>1726</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1690</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1691</v>
+        <v>1728</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1692</v>
+        <v>1729</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1693</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1694</v>
+        <v>1731</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1695</v>
+        <v>1732</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1696</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1697</v>
+        <v>1734</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1698</v>
+        <v>1735</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1699</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1700</v>
+        <v>1737</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1701</v>
+        <v>1738</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1675</v>
+        <v>1712</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1702</v>
+        <v>1739</v>
       </c>
     </row>
   </sheetData>
@@ -22079,7 +23249,7 @@
         <v>1107</v>
       </c>
       <c r="E2" s="2">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -22197,7 +23367,7 @@
         <v>1107</v>
       </c>
       <c r="E8" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -22215,7 +23385,7 @@
         <v>1107</v>
       </c>
       <c r="E9" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -22233,7 +23403,7 @@
         <v>1107</v>
       </c>
       <c r="E10" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -22251,7 +23421,7 @@
         <v>1107</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -22269,7 +23439,7 @@
         <v>1107</v>
       </c>
       <c r="E12" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -22287,7 +23457,7 @@
         <v>1107</v>
       </c>
       <c r="E13" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -22441,7 +23611,7 @@
         <v>1107</v>
       </c>
       <c r="E21" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -22479,7 +23649,7 @@
         <v>1107</v>
       </c>
       <c r="E23" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -22497,7 +23667,7 @@
         <v>1107</v>
       </c>
       <c r="E24" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -22515,7 +23685,7 @@
         <v>1107</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -22533,7 +23703,7 @@
         <v>1107</v>
       </c>
       <c r="E26" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -22551,7 +23721,7 @@
         <v>1107</v>
       </c>
       <c r="E27" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -22569,7 +23739,7 @@
         <v>1107</v>
       </c>
       <c r="E28" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -22605,7 +23775,7 @@
         <v>1107</v>
       </c>
       <c r="E30" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -22623,7 +23793,7 @@
         <v>1107</v>
       </c>
       <c r="E31" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -22661,7 +23831,7 @@
         <v>1107</v>
       </c>
       <c r="E33" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -22737,7 +23907,7 @@
         <v>1107</v>
       </c>
       <c r="E37" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -22775,7 +23945,7 @@
         <v>1107</v>
       </c>
       <c r="E39" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -22793,7 +23963,7 @@
         <v>1107</v>
       </c>
       <c r="E40" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -22891,7 +24061,7 @@
         <v>1107</v>
       </c>
       <c r="E45" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -22909,7 +24079,7 @@
         <v>1107</v>
       </c>
       <c r="E46" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -22927,7 +24097,7 @@
         <v>1107</v>
       </c>
       <c r="E47" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -22965,7 +24135,7 @@
         <v>1107</v>
       </c>
       <c r="E49" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -22983,7 +24153,7 @@
         <v>1107</v>
       </c>
       <c r="E50" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -23119,7 +24289,7 @@
         <v>1107</v>
       </c>
       <c r="E57" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -23137,7 +24307,7 @@
         <v>1107</v>
       </c>
       <c r="E58" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -23175,7 +24345,7 @@
         <v>1107</v>
       </c>
       <c r="E60" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -23273,7 +24443,7 @@
         <v>1107</v>
       </c>
       <c r="E65" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -23291,7 +24461,7 @@
         <v>1107</v>
       </c>
       <c r="E66" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -23309,7 +24479,7 @@
         <v>1107</v>
       </c>
       <c r="E67" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -23385,7 +24555,7 @@
         <v>1107</v>
       </c>
       <c r="E71" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -23403,7 +24573,7 @@
         <v>1107</v>
       </c>
       <c r="E72" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -23441,7 +24611,7 @@
         <v>1107</v>
       </c>
       <c r="E74" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -23459,7 +24629,7 @@
         <v>1107</v>
       </c>
       <c r="E75" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -23477,7 +24647,7 @@
         <v>1107</v>
       </c>
       <c r="E76" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -23553,7 +24723,7 @@
         <v>1107</v>
       </c>
       <c r="E80" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -23571,7 +24741,7 @@
         <v>1107</v>
       </c>
       <c r="E81" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -23589,7 +24759,7 @@
         <v>1107</v>
       </c>
       <c r="E82" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -23667,7 +24837,7 @@
         <v>1107</v>
       </c>
       <c r="E86" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -23685,7 +24855,7 @@
         <v>1107</v>
       </c>
       <c r="E87" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -23703,7 +24873,7 @@
         <v>1107</v>
       </c>
       <c r="E88" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -23721,7 +24891,7 @@
         <v>1107</v>
       </c>
       <c r="E89" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -23777,7 +24947,7 @@
         <v>1107</v>
       </c>
       <c r="E92" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -23815,7 +24985,7 @@
         <v>1107</v>
       </c>
       <c r="E94" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -23893,7 +25063,7 @@
         <v>1107</v>
       </c>
       <c r="E98" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -24011,7 +25181,7 @@
         <v>1107</v>
       </c>
       <c r="E104" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -24049,7 +25219,7 @@
         <v>1107</v>
       </c>
       <c r="E106" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -24187,7 +25357,7 @@
         <v>1107</v>
       </c>
       <c r="E113" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -24283,7 +25453,7 @@
         <v>1107</v>
       </c>
       <c r="E118" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -24301,7 +25471,7 @@
         <v>1110</v>
       </c>
       <c r="E119" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -24319,7 +25489,7 @@
         <v>1107</v>
       </c>
       <c r="E120" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -24337,7 +25507,7 @@
         <v>1107</v>
       </c>
       <c r="E121" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -24355,7 +25525,7 @@
         <v>1110</v>
       </c>
       <c r="E122" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -24373,7 +25543,7 @@
         <v>1107</v>
       </c>
       <c r="E123" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -24391,7 +25561,7 @@
         <v>1107</v>
       </c>
       <c r="E124" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -24409,7 +25579,7 @@
         <v>1107</v>
       </c>
       <c r="E125" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -24427,7 +25597,7 @@
         <v>1107</v>
       </c>
       <c r="E126" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -24445,7 +25615,7 @@
         <v>1110</v>
       </c>
       <c r="E127" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -24463,7 +25633,7 @@
         <v>1107</v>
       </c>
       <c r="E128" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -24481,7 +25651,7 @@
         <v>1107</v>
       </c>
       <c r="E129" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -24499,7 +25669,7 @@
         <v>1107</v>
       </c>
       <c r="E130" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -24517,7 +25687,7 @@
         <v>1107</v>
       </c>
       <c r="E131" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -24535,7 +25705,7 @@
         <v>1107</v>
       </c>
       <c r="E132" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -24553,7 +25723,7 @@
         <v>1107</v>
       </c>
       <c r="E133" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -24611,7 +25781,7 @@
         <v>1107</v>
       </c>
       <c r="E136" s="2">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -24629,7 +25799,7 @@
         <v>1107</v>
       </c>
       <c r="E137" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -24647,7 +25817,7 @@
         <v>1107</v>
       </c>
       <c r="E138" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F138" s="2"/>
     </row>
@@ -24665,7 +25835,7 @@
         <v>1107</v>
       </c>
       <c r="E139" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F139" s="2"/>
     </row>
@@ -24683,7 +25853,7 @@
         <v>1107</v>
       </c>
       <c r="E140" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F140" s="2"/>
     </row>
@@ -24701,7 +25871,7 @@
         <v>1107</v>
       </c>
       <c r="E141" s="2">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F141" s="2"/>
     </row>
@@ -24719,7 +25889,7 @@
         <v>1110</v>
       </c>
       <c r="E142" s="2">
-        <v>313</v>
+        <v>394</v>
       </c>
       <c r="F142" s="2"/>
     </row>
@@ -24737,7 +25907,7 @@
         <v>1107</v>
       </c>
       <c r="E143" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F143" s="2"/>
     </row>
@@ -24755,7 +25925,7 @@
         <v>1107</v>
       </c>
       <c r="E144" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F144" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/09-report/CYC-4-cycle-report.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6207" uniqueCount="1740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6207" uniqueCount="1737">
   <si>
     <t>Metric</t>
   </si>
@@ -213,7 +213,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-02T20:26:22.186Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-02T20:29:03.996Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2928,7 +2928,7 @@
     <t>functional, automation</t>
   </si>
   <si>
-    <t>AQPI-15, AQPI-33, REQ-122, BR-122</t>
+    <t>AQPI-33, REQ-122, BR-122</t>
   </si>
   <si>
     <t>Changed</t>
@@ -2999,7 +2999,7 @@
     <t>First 5 resends HTTP 202, the next HTTP 429; still one reservation</t>
   </si>
   <si>
-    <t>AQPI-26, AQPI-35, REQ-124, BR-124</t>
+    <t>AQPI-35, REQ-124, BR-124</t>
   </si>
   <si>
     <t>v2 (CYC-4): name was "The 4th resend within 24 hours is refused"; expected was "First 3 resends HTTP 202, the next HTTP 429; still one reservation"</t>
@@ -3071,7 +3071,7 @@
     <t>HTTP 200 with a searchId</t>
   </si>
   <si>
-    <t>AQPI-4, AQPI-34, REQ-126, BR-126</t>
+    <t>AQPI-34, REQ-126, BR-126</t>
   </si>
   <si>
     <t>v2 (CYC-4): re-designed because a rule it depends on changed; case text unchanged</t>
@@ -4870,9 +4870,6 @@
     <t>TD-F-111</t>
   </si>
   <si>
-    <t>AQPI-15, AQPI-33</t>
-  </si>
-  <si>
     <t>BR-122</t>
   </si>
   <si>
@@ -4894,9 +4891,6 @@
     <t>TD-F-114</t>
   </si>
   <si>
-    <t>AQPI-26, AQPI-35</t>
-  </si>
-  <si>
     <t>BR-124</t>
   </si>
   <si>
@@ -4921,9 +4915,6 @@
     <t>TD-F-118</t>
   </si>
   <si>
-    <t>AQPI-4, AQPI-34</t>
-  </si>
-  <si>
     <t>BR-126</t>
   </si>
   <si>
@@ -5083,7 +5074,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T20:26:23.937Z</t>
+    <t>2026-10-02T20:29:06.424Z</t>
   </si>
   <si>
     <t>33 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5095,7 +5086,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-02T20:26:23.982Z</t>
+    <t>2026-10-02T20:29:06.464Z</t>
   </si>
   <si>
     <t>13 requirements, 18 test cases, 10 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -6330,16 +6321,16 @@
         <v>1235</v>
       </c>
       <c r="F10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2">
         <v>0</v>
@@ -6520,25 +6511,25 @@
         <v>1246</v>
       </c>
       <c r="F15" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H15" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>1135</v>
+        <v>363</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6938,16 +6929,16 @@
         <v>1268</v>
       </c>
       <c r="F26" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2">
         <v>0</v>
@@ -12081,7 +12072,7 @@
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1575</v>
+        <v>1219</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>297</v>
@@ -12090,7 +12081,7 @@
         <v>298</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>930</v>
@@ -12105,10 +12096,10 @@
         <v>360</v>
       </c>
       <c r="I117" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="J117" s="2" t="s">
         <v>1577</v>
-      </c>
-      <c r="J117" s="2" t="s">
-        <v>1578</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1107</v>
@@ -12131,7 +12122,7 @@
         <v>302</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>939</v>
@@ -12146,10 +12137,10 @@
         <v>360</v>
       </c>
       <c r="I118" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J118" s="2" t="s">
         <v>1580</v>
-      </c>
-      <c r="J118" s="2" t="s">
-        <v>1581</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>1107</v>
@@ -12172,7 +12163,7 @@
         <v>302</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>946</v>
@@ -12187,10 +12178,10 @@
         <v>360</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>1110</v>
@@ -12204,7 +12195,7 @@
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1583</v>
+        <v>1225</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>303</v>
@@ -12213,7 +12204,7 @@
         <v>304</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>952</v>
@@ -12228,10 +12219,10 @@
         <v>360</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>1107</v>
@@ -12254,7 +12245,7 @@
         <v>307</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>959</v>
@@ -12269,10 +12260,10 @@
         <v>360</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>1107</v>
@@ -12295,7 +12286,7 @@
         <v>307</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>965</v>
@@ -12310,10 +12301,10 @@
         <v>360</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>1110</v>
@@ -12336,7 +12327,7 @@
         <v>307</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>969</v>
@@ -12351,10 +12342,10 @@
         <v>360</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>1107</v>
@@ -12368,7 +12359,7 @@
     </row>
     <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>1592</v>
+        <v>1137</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>308</v>
@@ -12377,7 +12368,7 @@
         <v>309</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>974</v>
@@ -12392,10 +12383,10 @@
         <v>360</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>1107</v>
@@ -12409,7 +12400,7 @@
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>1592</v>
+        <v>1137</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>308</v>
@@ -12418,7 +12409,7 @@
         <v>309</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>982</v>
@@ -12433,10 +12424,10 @@
         <v>360</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1107</v>
@@ -12450,7 +12441,7 @@
     </row>
     <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>1592</v>
+        <v>1137</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>308</v>
@@ -12459,7 +12450,7 @@
         <v>309</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>988</v>
@@ -12474,10 +12465,10 @@
         <v>360</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1107</v>
@@ -12491,7 +12482,7 @@
     </row>
     <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>1592</v>
+        <v>1137</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>308</v>
@@ -12500,7 +12491,7 @@
         <v>309</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>994</v>
@@ -12515,10 +12506,10 @@
         <v>360</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>1110</v>
@@ -12541,7 +12532,7 @@
         <v>312</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>1000</v>
@@ -12556,10 +12547,10 @@
         <v>360</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1107</v>
@@ -12582,7 +12573,7 @@
         <v>312</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>1006</v>
@@ -12597,10 +12588,10 @@
         <v>360</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1107</v>
@@ -12623,7 +12614,7 @@
         <v>312</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>1012</v>
@@ -12638,10 +12629,10 @@
         <v>360</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1107</v>
@@ -12664,7 +12655,7 @@
         <v>312</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>1018</v>
@@ -12679,10 +12670,10 @@
         <v>360</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>1107</v>
@@ -12705,7 +12696,7 @@
         <v>314</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>1024</v>
@@ -12720,10 +12711,10 @@
         <v>360</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1107</v>
@@ -12746,7 +12737,7 @@
         <v>314</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>1030</v>
@@ -12761,10 +12752,10 @@
         <v>360</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1107</v>
@@ -12787,7 +12778,7 @@
         <v>316</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>1036</v>
@@ -12802,7 +12793,7 @@
         <v>373</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2" t="s">
@@ -12826,7 +12817,7 @@
         <v>319</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>1041</v>
@@ -12841,7 +12832,7 @@
         <v>373</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="J135" s="2"/>
       <c r="K135" s="2" t="s">
@@ -12865,7 +12856,7 @@
         <v>321</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>1045</v>
@@ -12880,10 +12871,10 @@
         <v>360</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1107</v>
@@ -12906,7 +12897,7 @@
         <v>321</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>1051</v>
@@ -12921,10 +12912,10 @@
         <v>360</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>1107</v>
@@ -12947,7 +12938,7 @@
         <v>323</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>1057</v>
@@ -12962,10 +12953,10 @@
         <v>360</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="K138" s="2" t="s">
         <v>1107</v>
@@ -12988,7 +12979,7 @@
         <v>325</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>1063</v>
@@ -13003,10 +12994,10 @@
         <v>360</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>1107</v>
@@ -13029,7 +13020,7 @@
         <v>327</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>1069</v>
@@ -13044,10 +13035,10 @@
         <v>360</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>1107</v>
@@ -13070,7 +13061,7 @@
         <v>327</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>1075</v>
@@ -13085,10 +13076,10 @@
         <v>360</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>1107</v>
@@ -13111,7 +13102,7 @@
         <v>329</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>1080</v>
@@ -13126,10 +13117,10 @@
         <v>360</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>1110</v>
@@ -13152,7 +13143,7 @@
         <v>331</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>1086</v>
@@ -13167,10 +13158,10 @@
         <v>360</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>1107</v>
@@ -13193,7 +13184,7 @@
         <v>333</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>1092</v>
@@ -13208,10 +13199,10 @@
         <v>360</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>1107</v>
@@ -13234,7 +13225,7 @@
         <v>335</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>1099</v>
@@ -13249,7 +13240,7 @@
         <v>373</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="J145" s="2"/>
       <c r="K145" s="2" t="s">
@@ -13282,53 +13273,53 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1638</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1639</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1640</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1641</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>1643</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>1644</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1645</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1646</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1648</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1644</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1649</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1651</v>
       </c>
     </row>
   </sheetData>
@@ -13351,7 +13342,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>337</v>
@@ -13360,180 +13351,180 @@
         <v>1164</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>1655</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1657</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1658</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>1660</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>1661</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1662</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1663</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>1665</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1666</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1668</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1671</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1672</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>1675</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1676</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1677</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1678</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1679</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1680</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>1681</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1683</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1684</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>1685</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>1686</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1687</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1688</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>1690</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>1691</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1692</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1693</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>1695</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>1696</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1698</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1699</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>1700</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>1701</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1702</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1703</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>1704</v>
       </c>
     </row>
   </sheetData>
@@ -13556,203 +13547,203 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1705</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1706</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1707</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1709</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>1710</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1711</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1712</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
     </row>
   </sheetData>
@@ -23249,7 +23240,7 @@
         <v>1107</v>
       </c>
       <c r="E2" s="2">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -23367,7 +23358,7 @@
         <v>1107</v>
       </c>
       <c r="E8" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -23385,7 +23376,7 @@
         <v>1107</v>
       </c>
       <c r="E9" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -23403,7 +23394,7 @@
         <v>1107</v>
       </c>
       <c r="E10" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -23421,7 +23412,7 @@
         <v>1107</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -23439,7 +23430,7 @@
         <v>1107</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -23457,7 +23448,7 @@
         <v>1107</v>
       </c>
       <c r="E13" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -23535,7 +23526,7 @@
         <v>1107</v>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -23553,7 +23544,7 @@
         <v>1107</v>
       </c>
       <c r="E18" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -23649,7 +23640,7 @@
         <v>1107</v>
       </c>
       <c r="E23" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -23667,7 +23658,7 @@
         <v>1107</v>
       </c>
       <c r="E24" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -23685,7 +23676,7 @@
         <v>1107</v>
       </c>
       <c r="E25" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -23703,7 +23694,7 @@
         <v>1107</v>
       </c>
       <c r="E26" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -23721,7 +23712,7 @@
         <v>1107</v>
       </c>
       <c r="E27" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -23757,7 +23748,7 @@
         <v>1107</v>
       </c>
       <c r="E29" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -23775,7 +23766,7 @@
         <v>1107</v>
       </c>
       <c r="E30" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -23793,7 +23784,7 @@
         <v>1107</v>
       </c>
       <c r="E31" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -23831,7 +23822,7 @@
         <v>1107</v>
       </c>
       <c r="E33" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -23907,7 +23898,7 @@
         <v>1107</v>
       </c>
       <c r="E37" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -23945,7 +23936,7 @@
         <v>1107</v>
       </c>
       <c r="E39" s="2">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -23963,7 +23954,7 @@
         <v>1107</v>
       </c>
       <c r="E40" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -24061,7 +24052,7 @@
         <v>1107</v>
       </c>
       <c r="E45" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -24079,7 +24070,7 @@
         <v>1107</v>
       </c>
       <c r="E46" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -24097,7 +24088,7 @@
         <v>1107</v>
       </c>
       <c r="E47" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -24153,7 +24144,7 @@
         <v>1107</v>
       </c>
       <c r="E50" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -24171,7 +24162,7 @@
         <v>1107</v>
       </c>
       <c r="E51" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -24289,7 +24280,7 @@
         <v>1107</v>
       </c>
       <c r="E57" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -24307,7 +24298,7 @@
         <v>1107</v>
       </c>
       <c r="E58" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -24345,7 +24336,7 @@
         <v>1107</v>
       </c>
       <c r="E60" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -24443,7 +24434,7 @@
         <v>1107</v>
       </c>
       <c r="E65" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -24461,7 +24452,7 @@
         <v>1107</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -24537,7 +24528,7 @@
         <v>1107</v>
       </c>
       <c r="E70" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -24555,7 +24546,7 @@
         <v>1107</v>
       </c>
       <c r="E71" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -24573,7 +24564,7 @@
         <v>1107</v>
       </c>
       <c r="E72" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -24611,7 +24602,7 @@
         <v>1107</v>
       </c>
       <c r="E74" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -24629,7 +24620,7 @@
         <v>1107</v>
       </c>
       <c r="E75" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -24647,7 +24638,7 @@
         <v>1107</v>
       </c>
       <c r="E76" s="2">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -24665,7 +24656,7 @@
         <v>1107</v>
       </c>
       <c r="E77" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -24741,7 +24732,7 @@
         <v>1107</v>
       </c>
       <c r="E81" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -24759,7 +24750,7 @@
         <v>1107</v>
       </c>
       <c r="E82" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -24837,7 +24828,7 @@
         <v>1107</v>
       </c>
       <c r="E86" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -24855,7 +24846,7 @@
         <v>1107</v>
       </c>
       <c r="E87" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -24873,7 +24864,7 @@
         <v>1107</v>
       </c>
       <c r="E88" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -24891,7 +24882,7 @@
         <v>1107</v>
       </c>
       <c r="E89" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -24947,7 +24938,7 @@
         <v>1107</v>
       </c>
       <c r="E92" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -24985,7 +24976,7 @@
         <v>1107</v>
       </c>
       <c r="E94" s="2">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -25063,7 +25054,7 @@
         <v>1107</v>
       </c>
       <c r="E98" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -25181,7 +25172,7 @@
         <v>1107</v>
       </c>
       <c r="E104" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -25357,7 +25348,7 @@
         <v>1107</v>
       </c>
       <c r="E113" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -25453,7 +25444,7 @@
         <v>1107</v>
       </c>
       <c r="E118" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -25489,7 +25480,7 @@
         <v>1107</v>
       </c>
       <c r="E120" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -25525,7 +25516,7 @@
         <v>1110</v>
       </c>
       <c r="E122" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -25543,7 +25534,7 @@
         <v>1107</v>
       </c>
       <c r="E123" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -25561,7 +25552,7 @@
         <v>1107</v>
       </c>
       <c r="E124" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -25579,7 +25570,7 @@
         <v>1107</v>
       </c>
       <c r="E125" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -25597,7 +25588,7 @@
         <v>1107</v>
       </c>
       <c r="E126" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -25615,7 +25606,7 @@
         <v>1110</v>
       </c>
       <c r="E127" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -25633,7 +25624,7 @@
         <v>1107</v>
       </c>
       <c r="E128" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -25651,7 +25642,7 @@
         <v>1107</v>
       </c>
       <c r="E129" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -25687,7 +25678,7 @@
         <v>1107</v>
       </c>
       <c r="E131" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -25705,7 +25696,7 @@
         <v>1107</v>
       </c>
       <c r="E132" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -25781,7 +25772,7 @@
         <v>1107</v>
       </c>
       <c r="E136" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -25817,7 +25808,7 @@
         <v>1107</v>
       </c>
       <c r="E138" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F138" s="2"/>
     </row>
@@ -25835,7 +25826,7 @@
         <v>1107</v>
       </c>
       <c r="E139" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F139" s="2"/>
     </row>
@@ -25853,7 +25844,7 @@
         <v>1107</v>
       </c>
       <c r="E140" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F140" s="2"/>
     </row>
@@ -25871,7 +25862,7 @@
         <v>1107</v>
       </c>
       <c r="E141" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F141" s="2"/>
     </row>
@@ -25889,7 +25880,7 @@
         <v>1110</v>
       </c>
       <c r="E142" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="F142" s="2"/>
     </row>
@@ -25907,7 +25898,7 @@
         <v>1107</v>
       </c>
       <c r="E143" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F143" s="2"/>
     </row>
@@ -25925,7 +25916,7 @@
         <v>1107</v>
       </c>
       <c r="E144" s="2">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F144" s="2"/>
     </row>
